--- a/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5929EC5E-62DF-47AA-8DD8-52FF6DB4E4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270D843D-F984-4927-AC9D-CB43F15BFC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12773" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12772" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -18,25 +18,25 @@
     <sheet name="fuel_prices" sheetId="4" r:id="rId3"/>
     <sheet name="iea_data" sheetId="2" r:id="rId4"/>
     <sheet name="ar6_r10" sheetId="3" r:id="rId5"/>
-    <sheet name="Veda_BEL" sheetId="6" r:id="rId6"/>
-    <sheet name="Veda_GBR" sheetId="7" r:id="rId7"/>
-    <sheet name="Veda_NLD" sheetId="8" r:id="rId8"/>
-    <sheet name="Veda_DEU" sheetId="9" r:id="rId9"/>
-    <sheet name="Veda_CHE" sheetId="10" r:id="rId10"/>
-    <sheet name="Veda_ITA" sheetId="11" r:id="rId11"/>
-    <sheet name="Veda_ESP" sheetId="12" r:id="rId12"/>
+    <sheet name="Veda_GBR" sheetId="6" r:id="rId6"/>
+    <sheet name="Veda_BEL" sheetId="7" r:id="rId7"/>
+    <sheet name="Veda_DEU" sheetId="8" r:id="rId8"/>
+    <sheet name="Veda_CHE" sheetId="9" r:id="rId9"/>
+    <sheet name="Veda_ITA" sheetId="10" r:id="rId10"/>
+    <sheet name="Veda_ESP" sheetId="11" r:id="rId11"/>
+    <sheet name="Veda_NLD" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ar6_r10!$A$10:$M$395</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">controller!$B$17:$E$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Veda_BEL!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Veda_CHE!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Veda_DEU!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Veda_ESP!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Veda_BEL!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Veda_CHE!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Veda_DEU!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Veda_ESP!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Veda_FRA!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Veda_GBR!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Veda_ITA!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Veda_NLD!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Veda_GBR!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Veda_ITA!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Veda_NLD!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +97,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{8F691C2E-A741-4E19-8AAF-5827588C80AD}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{27D0141E-412D-4488-B3F7-2ED3FBFE68E1}">
       <text>
         <r>
           <rPr>
@@ -133,7 +133,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{5443B7F0-9701-4426-B01F-3972A2557A42}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{F8DF6196-9C5A-4963-A28C-7EA98A59582D}">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{8BB7AC2B-AFB8-40FF-9625-C82A85672C67}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{2670D142-9752-4CB8-BAA7-910D3FAB3F9B}">
       <text>
         <r>
           <rPr>
@@ -205,7 +205,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{8531C2F4-2750-4DBE-A6CF-CD1353B505A5}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{6BDB09D6-754A-4AB5-B728-BBDAEF8A94BC}">
       <text>
         <r>
           <rPr>
@@ -241,7 +241,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{8401FA9D-23FE-4242-8118-F0ADC6F118BF}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{335A2160-FE8A-4101-AFE0-9EB3FD1A9FE7}">
       <text>
         <r>
           <rPr>
@@ -277,7 +277,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{BF4CC657-17CC-442B-A66A-5FD936CFF44E}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{E2983891-3593-4751-A37F-3442B8D2103E}">
       <text>
         <r>
           <rPr>
@@ -313,7 +313,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{02B05DE3-A2EC-4356-9694-5F2E5E19EAB4}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{EE75EE4C-17D4-4205-B9C8-DBB554EC5EC7}">
       <text>
         <r>
           <rPr>
@@ -673,13 +673,10 @@
     <t>cap_bnd</t>
   </si>
   <si>
-    <t>BEL</t>
-  </si>
-  <si>
     <t>GBR</t>
   </si>
   <si>
-    <t>NLD</t>
+    <t>BEL</t>
   </si>
   <si>
     <t>DEU</t>
@@ -694,13 +691,13 @@
     <t>ESP</t>
   </si>
   <si>
-    <t>~tfm_ins-ts: region=BEL</t>
+    <t>NLD</t>
   </si>
   <si>
     <t>~tfm_ins-ts: region=GBR</t>
   </si>
   <si>
-    <t>~tfm_ins-ts: region=NLD</t>
+    <t>~tfm_ins-ts: region=BEL</t>
   </si>
   <si>
     <t>~tfm_ins-ts: region=DEU</t>
@@ -715,13 +712,13 @@
     <t>~tfm_ins-ts: region=ESP</t>
   </si>
   <si>
-    <t>Zeebrugge LNG, pellet imports</t>
+    <t>~tfm_ins-ts: region=NLD</t>
   </si>
   <si>
     <t>NBP gas hub, Drax biomass plants</t>
   </si>
   <si>
-    <t>TTF hub, major pellet importer</t>
+    <t>Zeebrugge LNG, pellet imports</t>
   </si>
   <si>
     <t>TTF gas hub, imported coal via ARA</t>
@@ -734,6 +731,9 @@
   </si>
   <si>
     <t>Iberian market, olive &amp; agricultural waste</t>
+  </si>
+  <si>
+    <t>TTF hub, major pellet importer</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1455,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_DEU!$D$18:$J$18</c:f>
+              <c:f>Veda_CHE!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1485,7 +1485,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_DEU!$D$26:$J$26</c:f>
+              <c:f>Veda_CHE!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1516,7 +1516,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C65C-477F-95D4-071F36614D37}"/>
+              <c16:uniqueId val="{00000000-3F8A-4A78-99A8-1BD3CC3910A3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1750,7 +1750,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_CHE!$O$18:$U$18</c:f>
+              <c:f>Veda_ITA!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1780,30 +1780,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_CHE!$O$15:$U$15</c:f>
+              <c:f>Veda_ITA!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>65.39</c:v>
+                  <c:v>325.06</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>68.659500000000008</c:v>
+                  <c:v>341.31300000000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76.506299999999996</c:v>
+                  <c:v>380.3202</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84.353099999999998</c:v>
+                  <c:v>419.32740000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>92.853799999999993</c:v>
+                  <c:v>461.58519999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>103.9701</c:v>
+                  <c:v>516.84540000000004</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>113.1247</c:v>
+                  <c:v>562.35379999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,7 +1811,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-72A2-4C4C-9DFF-F9DCA2401516}"/>
+              <c16:uniqueId val="{00000000-5907-4820-8E39-BD4AD7F7204D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2045,7 +2045,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_CHE!$D$18:$J$18</c:f>
+              <c:f>Veda_ITA!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2075,7 +2075,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_CHE!$D$26:$J$26</c:f>
+              <c:f>Veda_ITA!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2106,7 +2106,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-08DC-43EA-AAC2-9A7FF48B09C9}"/>
+              <c16:uniqueId val="{00000000-5395-446B-BB5A-B6FC5E44F9C1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2340,7 +2340,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ITA!$O$18:$U$18</c:f>
+              <c:f>Veda_ESP!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2370,30 +2370,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ITA!$O$15:$U$15</c:f>
+              <c:f>Veda_ESP!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>325.06</c:v>
+                  <c:v>268.14</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>341.31300000000005</c:v>
+                  <c:v>281.54700000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>380.3202</c:v>
+                  <c:v>313.72379999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>419.32740000000001</c:v>
+                  <c:v>345.9006</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>461.58519999999999</c:v>
+                  <c:v>380.75879999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>516.84540000000004</c:v>
+                  <c:v>426.3426</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>562.35379999999998</c:v>
+                  <c:v>463.88219999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2401,7 +2401,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-08DF-483C-9F67-7675CA058408}"/>
+              <c16:uniqueId val="{00000000-3CD0-40CF-8FED-E2A82BF70BD7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2635,7 +2635,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ITA!$D$18:$J$18</c:f>
+              <c:f>Veda_ESP!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2665,7 +2665,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ITA!$D$26:$J$26</c:f>
+              <c:f>Veda_ESP!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2696,7 +2696,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3823-486A-BF1F-3A939203E222}"/>
+              <c16:uniqueId val="{00000000-FE1F-4176-B610-B01AA4DDD131}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2930,7 +2930,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ESP!$O$18:$U$18</c:f>
+              <c:f>Veda_NLD!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2960,30 +2960,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ESP!$O$15:$U$15</c:f>
+              <c:f>Veda_NLD!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>268.14</c:v>
+                  <c:v>117.29999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>281.54700000000003</c:v>
+                  <c:v>123.16499999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>313.72379999999998</c:v>
+                  <c:v>137.24099999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>345.9006</c:v>
+                  <c:v>151.31699999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>380.75879999999995</c:v>
+                  <c:v>166.56599999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>426.3426</c:v>
+                  <c:v>186.50699999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>463.88219999999995</c:v>
+                  <c:v>202.92899999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2991,7 +2991,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BC15-433A-A9EB-6610612DD0FE}"/>
+              <c16:uniqueId val="{00000000-7EA7-4C5B-908C-896430F6F6A0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3225,7 +3225,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ESP!$D$18:$J$18</c:f>
+              <c:f>Veda_NLD!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3255,7 +3255,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ESP!$D$26:$J$26</c:f>
+              <c:f>Veda_NLD!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3286,7 +3286,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A01F-4137-B4F9-6DF4E9A35D81}"/>
+              <c16:uniqueId val="{00000000-5000-4638-8947-5D775E73C6C9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3808,7 +3808,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_BEL!$O$18:$U$18</c:f>
+              <c:f>Veda_GBR!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3838,30 +3838,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_BEL!$O$15:$U$15</c:f>
+              <c:f>Veda_GBR!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>86.65</c:v>
+                  <c:v>317.63</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>90.982500000000016</c:v>
+                  <c:v>333.51150000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>101.3805</c:v>
+                  <c:v>371.62709999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>111.77850000000001</c:v>
+                  <c:v>409.74270000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>123.04300000000001</c:v>
+                  <c:v>451.03459999999995</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>137.77350000000001</c:v>
+                  <c:v>505.0317</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>149.90450000000001</c:v>
+                  <c:v>549.49990000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3869,7 +3869,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7985-448F-A2DE-60DDD273218D}"/>
+              <c16:uniqueId val="{00000000-CF5D-4E01-B09B-620306FCE61E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4103,7 +4103,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_BEL!$D$18:$J$18</c:f>
+              <c:f>Veda_GBR!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4133,7 +4133,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_BEL!$D$26:$J$26</c:f>
+              <c:f>Veda_GBR!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4164,7 +4164,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F56E-4A8A-91D4-C5812AE8C2E9}"/>
+              <c16:uniqueId val="{00000000-2B1D-4100-9C47-A5AC1DAC5B75}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4398,7 +4398,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_GBR!$O$18:$U$18</c:f>
+              <c:f>Veda_BEL!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4428,30 +4428,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_GBR!$O$15:$U$15</c:f>
+              <c:f>Veda_BEL!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>317.63</c:v>
+                  <c:v>86.65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>333.51150000000001</c:v>
+                  <c:v>90.982500000000016</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>371.62709999999998</c:v>
+                  <c:v>101.3805</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>409.74270000000001</c:v>
+                  <c:v>111.77850000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>451.03459999999995</c:v>
+                  <c:v>123.04300000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>505.0317</c:v>
+                  <c:v>137.77350000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>549.49990000000003</c:v>
+                  <c:v>149.90450000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4459,7 +4459,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-57EC-4DC0-A1C1-5ED3E5351477}"/>
+              <c16:uniqueId val="{00000000-E771-4111-9F9C-8738BD11DEC0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4693,7 +4693,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_GBR!$D$18:$J$18</c:f>
+              <c:f>Veda_BEL!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4723,7 +4723,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_GBR!$D$26:$J$26</c:f>
+              <c:f>Veda_BEL!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4754,7 +4754,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F9E5-472D-A2BB-BD6CEBE9A027}"/>
+              <c16:uniqueId val="{00000000-7FF4-4A68-8839-4A53CD832D77}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4988,7 +4988,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_NLD!$O$18:$U$18</c:f>
+              <c:f>Veda_DEU!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5018,30 +5018,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_NLD!$O$15:$U$15</c:f>
+              <c:f>Veda_DEU!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>117.29999999999998</c:v>
+                  <c:v>545.74</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>123.16499999999999</c:v>
+                  <c:v>573.02700000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>137.24099999999999</c:v>
+                  <c:v>638.51580000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>151.31699999999998</c:v>
+                  <c:v>704.00459999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>166.56599999999997</c:v>
+                  <c:v>774.95079999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>186.50699999999998</c:v>
+                  <c:v>867.72660000000008</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.92899999999997</c:v>
+                  <c:v>944.13020000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5049,7 +5049,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2A0D-4662-8D55-48C72A1DDA37}"/>
+              <c16:uniqueId val="{00000000-697D-4429-8F90-C5F51044988B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5283,7 +5283,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_NLD!$D$18:$J$18</c:f>
+              <c:f>Veda_DEU!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5313,7 +5313,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_NLD!$D$26:$J$26</c:f>
+              <c:f>Veda_DEU!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5344,7 +5344,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8210-4F53-B71A-8A12B75762D1}"/>
+              <c16:uniqueId val="{00000000-1722-45BF-8ACD-AD2F2FCB836D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5578,7 +5578,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_DEU!$O$18:$U$18</c:f>
+              <c:f>Veda_CHE!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5608,30 +5608,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_DEU!$O$15:$U$15</c:f>
+              <c:f>Veda_CHE!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>545.74</c:v>
+                  <c:v>65.39</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>573.02700000000004</c:v>
+                  <c:v>68.659500000000008</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>638.51580000000001</c:v>
+                  <c:v>76.506299999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>704.00459999999998</c:v>
+                  <c:v>84.353099999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>774.95079999999996</c:v>
+                  <c:v>92.853799999999993</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>867.72660000000008</c:v>
+                  <c:v>103.9701</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>944.13020000000006</c:v>
+                  <c:v>113.1247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5639,7 +5639,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4485-45A2-8BF9-4494A447708B}"/>
+              <c16:uniqueId val="{00000000-E5B8-45DD-9969-A2964661E862}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5858,7 +5858,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7DB6A89-A6C3-440C-983C-9B99A5165891}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A175B626-6655-4E0F-AA3D-D5D07715368C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5896,7 +5896,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23AE0515-2990-444D-AB73-073B117B8ED4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{36546A0C-BF44-4067-AA7F-8BAA4D70E351}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5939,7 +5939,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A74F3631-D153-4471-92B9-B90F738E232C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5C45748-1A7E-43CD-90DB-41BFC794A5AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5977,7 +5977,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DFF0482-AD79-4779-84FD-327106A8CA7C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC39B72E-FB02-4BAC-9DBA-3ECDD8BC98B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10235,7 +10235,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{874BCCEF-B237-4EB0-AB74-EDC56D5B6CA7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0961D50C-833D-4D91-BBB0-1BEEA5C8EF0E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10273,7 +10273,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8609E9F9-AF2F-4D72-AEB9-42FA44BB6106}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{974A010B-3852-40FC-B6E2-0612CD8391F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10316,7 +10316,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{548F5171-CDBF-42FD-917C-D632D101A764}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A919E2C7-241A-421B-BC14-DD1C49548314}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10354,7 +10354,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F5FA957-E382-4CF3-B1F4-BC6FDA03DC18}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DFF0A6B-865E-4118-8F25-EE70AF23BE1D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10397,7 +10397,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDAF6BCA-3D1D-442F-A6F6-4EB10DDD1996}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{999590F5-B6DD-4DED-8532-19EB0DEA3F18}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10435,7 +10435,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F99FE2-1EED-4A4E-B0DD-E95372EB6037}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{793C8F27-D027-4F7F-ADFC-3CC65606BB7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10478,7 +10478,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{399D033B-55C8-42DF-99E6-BF4C6D70CE52}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FF8516C-F462-40E3-A1A2-6DD10145D576}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10516,7 +10516,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE1380E8-AF54-4D78-BFB1-391762762992}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ACBC974-D045-4711-98FC-DEBBC20FC944}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10559,7 +10559,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69AF40C4-8754-4B0F-A464-B02DB80DB098}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B38C914E-6948-450B-9D4C-3FBAB9C2358E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10597,7 +10597,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5624BDE8-EC62-498D-82C7-9048412525DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CC7290F-F668-45D8-B01E-820C8F16380F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11159,7 +11159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA04568C-24C0-41F8-84B5-177680444F54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8667E81-9478-4B0C-95ED-33B34736F560}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -11278,7 +11278,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>65.39</v>
+        <v>325.06</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -11296,7 +11296,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>2.5449999999999999</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -11311,7 +11311,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.4509999999999996</v>
+        <v>10.842000000000001</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -11362,31 +11362,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>65.39</v>
+        <v>325.06</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>68.659500000000008</v>
+        <v>341.31300000000005</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>76.506299999999996</v>
+        <v>380.3202</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>84.353099999999998</v>
+        <v>419.32740000000001</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>92.853799999999993</v>
+        <v>461.58519999999999</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>103.9701</v>
+        <v>516.84540000000004</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>113.1247</v>
+        <v>562.35379999999998</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -11425,7 +11425,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=CHE</v>
+        <v>~TFM_INS-TS: region=ITA</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11589,31 +11589,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>24.194299999999998</v>
+        <v>120.2722</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>24.030825</v>
+        <v>119.45955000000001</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>26.012142000000001</v>
+        <v>129.30886800000002</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>27.836523</v>
+        <v>138.37804200000002</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>27.856139999999996</v>
+        <v>138.47556</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>30.151328999999997</v>
+        <v>149.885166</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>33.93741</v>
+        <v>168.70613999999998</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -11656,31 +11656,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>38.580100000000002</v>
+        <v>191.78539999999998</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>40.509105000000005</v>
+        <v>201.37467000000001</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>45.138716999999993</v>
+        <v>224.38891799999999</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>48.924797999999996</v>
+        <v>243.209892</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>53.855203999999993</v>
+        <v>267.71941599999997</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>58.223256000000006</v>
+        <v>289.43342400000006</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>61.08733800000001</v>
+        <v>303.67105200000003</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -11723,31 +11723,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>1.9617</v>
+        <v>9.7517999999999994</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -11762,31 +11762,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>0.65390000000000725</v>
+        <v>3.2506000000000199</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>2.1578700000000168</v>
+        <v>10.726980000000026</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>3.3937410000000057</v>
+        <v>16.870613999999989</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>5.6300790000000092</v>
+        <v>27.98766599999999</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>9.1807560000000024</v>
+        <v>45.638423999999986</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>13.633815000000013</v>
+        <v>67.775009999999952</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>16.138251999999994</v>
+        <v>80.224807999999939</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -11798,31 +11798,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>2.5449999999999999</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>2.4941</v>
+        <v>6.4003799999999993</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>2.4432</v>
+        <v>6.2697599999999998</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>2.3414000000000001</v>
+        <v>6.0085199999999999</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>2.1377999999999999</v>
+        <v>5.4860399999999991</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>2.1123499999999997</v>
+        <v>5.4207299999999998</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>2.036</v>
+        <v>5.2248000000000001</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -11834,31 +11834,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>4.4509999999999996</v>
+        <v>10.842000000000001</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>4.36198</v>
+        <v>10.625160000000001</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>4.2729599999999994</v>
+        <v>10.40832</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>4.0949200000000001</v>
+        <v>9.9746400000000008</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>3.7388399999999997</v>
+        <v>9.1072799999999994</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>3.6943299999999994</v>
+        <v>8.9988600000000005</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>3.5608</v>
+        <v>8.6736000000000004</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -11933,7 +11933,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=CHE</v>
+        <v>~TFM_INS-TS: region=ITA</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11978,14 +11978,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>33.119999999999997</v>
+        <v>47.39</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>33.119999999999997</v>
+        <v>47.39</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -12002,14 +12002,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>29.73</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>29.73</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -12164,7 +12164,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=CHE; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=ITA; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -12353,19 +12353,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -12401,13 +12401,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2.5049999999999999</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -12421,13 +12421,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>1.2</v>
+        <v>1.125</v>
       </c>
       <c r="D57">
-        <v>1.2</v>
+        <v>1.375</v>
       </c>
       <c r="E57">
-        <v>1.2</v>
+        <v>2.875</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
@@ -12442,7 +12442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA3A2CC-59E0-431B-A77A-032B4B896887}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9940B810-5208-4E83-8946-31C309AD0CDB}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12561,7 +12561,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>325.06</v>
+        <v>268.14</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -12579,7 +12579,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>6.5309999999999997</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -12594,7 +12594,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>10.842000000000001</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -12645,31 +12645,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>325.06</v>
+        <v>268.14</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>341.31300000000005</v>
+        <v>281.54700000000003</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>380.3202</v>
+        <v>313.72379999999998</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>419.32740000000001</v>
+        <v>345.9006</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>461.58519999999999</v>
+        <v>380.75879999999995</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>516.84540000000004</v>
+        <v>426.3426</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>562.35379999999998</v>
+        <v>463.88219999999995</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -12708,7 +12708,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ITA</v>
+        <v>~TFM_INS-TS: region=ESP</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -12872,31 +12872,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>120.2722</v>
+        <v>99.211799999999997</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>119.45955000000001</v>
+        <v>98.541449999999998</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>129.30886800000002</v>
+        <v>106.66609200000001</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>138.37804200000002</v>
+        <v>114.147198</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>138.47556</v>
+        <v>114.22763999999998</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>149.885166</v>
+        <v>123.639354</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>168.70613999999998</v>
+        <v>139.16465999999997</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -12939,31 +12939,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>191.78539999999998</v>
+        <v>158.20259999999999</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>201.37467000000001</v>
+        <v>166.11273</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>224.38891799999999</v>
+        <v>185.09704199999999</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>243.209892</v>
+        <v>200.62234799999999</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>267.71941599999997</v>
+        <v>220.84010399999997</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>289.43342400000006</v>
+        <v>238.75185600000003</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>303.67105200000003</v>
+        <v>250.496388</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -13006,31 +13006,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>9.7517999999999994</v>
+        <v>8.0442</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -13045,31 +13045,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>3.2506000000000199</v>
+        <v>2.6813999999999965</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>10.726980000000026</v>
+        <v>8.8486200000000395</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>16.870613999999989</v>
+        <v>13.916466000000014</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>27.98766599999999</v>
+        <v>23.086854000000017</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>45.638423999999986</v>
+        <v>37.646856000000014</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>67.775009999999952</v>
+        <v>55.907190000000014</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>80.224807999999939</v>
+        <v>66.176952000000028</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -13081,31 +13081,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>6.5309999999999997</v>
+        <v>0</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>6.4003799999999993</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>6.2697599999999998</v>
+        <v>0</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>6.0085199999999999</v>
+        <v>0</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>5.4860399999999991</v>
+        <v>0</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>5.4207299999999998</v>
+        <v>0</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>5.2248000000000001</v>
+        <v>0</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -13117,31 +13117,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>10.842000000000001</v>
+        <v>0</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>10.625160000000001</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>10.40832</v>
+        <v>0</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>9.9746400000000008</v>
+        <v>0</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>9.1072799999999994</v>
+        <v>0</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>8.9988600000000005</v>
+        <v>0</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>8.6736000000000004</v>
+        <v>0</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -13216,7 +13216,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ITA</v>
+        <v>~TFM_INS-TS: region=ESP</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -13261,14 +13261,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>47.39</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>47.39</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -13285,14 +13285,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.4000000000000004</v>
+        <v>27.83</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>4.4000000000000004</v>
+        <v>27.83</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -13447,7 +13447,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=ITA; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=ESP; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -13546,39 +13546,39 @@
       </c>
       <c r="D48">
         <f t="shared" si="9"/>
-        <v>16.75</v>
+        <v>15.2</v>
       </c>
       <c r="E48">
         <f t="shared" si="9"/>
-        <v>17.085000000000001</v>
+        <v>15.504</v>
       </c>
       <c r="F48">
         <f t="shared" si="9"/>
-        <v>17.755000000000003</v>
+        <v>16.111999999999998</v>
       </c>
       <c r="G48">
         <f t="shared" si="9"/>
-        <v>17.922499999999999</v>
+        <v>16.263999999999999</v>
       </c>
       <c r="H48">
         <f t="shared" si="9"/>
-        <v>18.09</v>
+        <v>16.416</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>18.425000000000001</v>
+        <v>16.72</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>18.760000000000002</v>
+        <v>17.024000000000001</v>
       </c>
       <c r="M48">
         <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="N48">
         <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
@@ -13636,19 +13636,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -13684,13 +13684,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>1.5049999999999999</v>
+        <v>4.38</v>
       </c>
       <c r="D56">
-        <v>2.5049999999999999</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="E56">
-        <v>3.93</v>
+        <v>5.75</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -13704,13 +13704,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>1.125</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>1.375</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>2.875</v>
+        <v>0</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
@@ -13725,7 +13725,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDA3FD70-24A8-44C8-9AD8-45775D2D1D5C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225690C2-0A03-45C5-9F6D-A119DCFD75B1}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -13844,7 +13844,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>268.14</v>
+        <v>117.29999999999998</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -13862,7 +13862,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
+        <v>14.882</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -13877,7 +13877,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
+        <v>4.665</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -13928,31 +13928,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>268.14</v>
+        <v>117.29999999999998</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>281.54700000000003</v>
+        <v>123.16499999999999</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>313.72379999999998</v>
+        <v>137.24099999999999</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>345.9006</v>
+        <v>151.31699999999998</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>380.75879999999995</v>
+        <v>166.56599999999997</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>426.3426</v>
+        <v>186.50699999999998</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>463.88219999999995</v>
+        <v>202.92899999999997</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -13991,7 +13991,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ESP</v>
+        <v>~TFM_INS-TS: region=NLD</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -14155,31 +14155,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>99.211799999999997</v>
+        <v>43.400999999999996</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>98.541449999999998</v>
+        <v>43.107749999999996</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>106.66609200000001</v>
+        <v>46.661940000000001</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>114.147198</v>
+        <v>49.934609999999992</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>114.22763999999998</v>
+        <v>49.969799999999992</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>123.639354</v>
+        <v>54.087029999999992</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>139.16465999999997</v>
+        <v>60.878699999999988</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -14222,31 +14222,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>158.20259999999999</v>
+        <v>69.206999999999979</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>166.11273</v>
+        <v>72.667349999999985</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>185.09704199999999</v>
+        <v>80.972189999999983</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>200.62234799999999</v>
+        <v>87.76385999999998</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>220.84010399999997</v>
+        <v>96.608279999999979</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>238.75185600000003</v>
+        <v>104.44391999999999</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>250.496388</v>
+        <v>109.58166</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -14289,31 +14289,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>8.0442</v>
+        <v>3.5189999999999992</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -14328,31 +14328,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>2.6813999999999965</v>
+        <v>1.1730000000000018</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>8.8486200000000395</v>
+        <v>3.870900000000006</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>13.916466000000014</v>
+        <v>6.0878700000000094</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>23.086854000000017</v>
+        <v>10.099529999999987</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>37.646856000000014</v>
+        <v>16.468919999999997</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>55.907190000000014</v>
+        <v>24.457049999999981</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>66.176952000000028</v>
+        <v>28.949639999999988</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -14364,31 +14364,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>0</v>
+        <v>14.882</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>0</v>
+        <v>14.58436</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>0</v>
+        <v>14.286719999999999</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>0</v>
+        <v>13.69144</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12.500879999999999</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12.35206</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>11.9056</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -14400,31 +14400,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>0</v>
+        <v>4.665</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>0</v>
+        <v>4.5716999999999999</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>0</v>
+        <v>4.4783999999999997</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4.2918000000000003</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.9186000000000001</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.87195</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3.7320000000000002</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -14499,7 +14499,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ESP</v>
+        <v>~TFM_INS-TS: region=NLD</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -14544,14 +14544,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>8.0299999999999994</v>
+        <v>18.54</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>8.0299999999999994</v>
+        <v>18.54</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -14568,14 +14568,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>27.83</v>
+        <v>22.81</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>27.83</v>
+        <v>22.81</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -14730,7 +14730,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=ESP; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=NLD; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -14874,39 +14874,39 @@
       </c>
       <c r="D49">
         <f t="shared" si="9"/>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E49">
         <f t="shared" si="9"/>
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
       <c r="F49">
         <f t="shared" si="9"/>
-        <v>61.050000000000004</v>
+        <v>58.830000000000005</v>
       </c>
       <c r="G49">
         <f t="shared" si="9"/>
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
       <c r="H49">
         <f t="shared" si="9"/>
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
       <c r="I49">
         <f t="shared" si="9"/>
-        <v>57.2</v>
+        <v>55.120000000000005</v>
       </c>
       <c r="J49">
         <f t="shared" si="9"/>
-        <v>62.699999999999996</v>
+        <v>60.419999999999995</v>
       </c>
       <c r="M49">
         <f>HLOOKUP($B49&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N49">
         <f>HLOOKUP($B49&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
@@ -14919,19 +14919,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -14967,13 +14967,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>4.38</v>
+        <v>0.64</v>
       </c>
       <c r="D56">
-        <v>5.0999999999999996</v>
+        <v>0.7</v>
       </c>
       <c r="E56">
-        <v>5.75</v>
+        <v>0.7</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -14987,13 +14987,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
@@ -16376,10 +16376,10 @@
         <v>109</v>
       </c>
       <c r="B12">
-        <v>29.1</v>
+        <v>27.4</v>
       </c>
       <c r="C12">
-        <v>41.1</v>
+        <v>39.4</v>
       </c>
       <c r="D12">
         <v>13.7</v>
@@ -16408,10 +16408,10 @@
         <v>110</v>
       </c>
       <c r="B13">
-        <v>27.4</v>
+        <v>29.1</v>
       </c>
       <c r="C13">
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
       <c r="D13">
         <v>13.7</v>
@@ -16458,10 +16458,10 @@
         <v>58</v>
       </c>
       <c r="H14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
         <v>125</v>
@@ -16478,22 +16478,22 @@
         <v>41.1</v>
       </c>
       <c r="D15">
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
       <c r="E15">
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
       <c r="F15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J15" t="s">
         <v>126</v>
@@ -16522,10 +16522,10 @@
         <v>60</v>
       </c>
       <c r="H16">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J16" t="s">
         <v>127</v>
@@ -16542,10 +16542,10 @@
         <v>41.1</v>
       </c>
       <c r="D17">
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="E17">
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -16554,10 +16554,10 @@
         <v>60</v>
       </c>
       <c r="H17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I17">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
         <v>128</v>
@@ -16580,16 +16580,16 @@
         <v>16.7</v>
       </c>
       <c r="F18">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G18">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H18">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I18">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
         <v>129</v>
@@ -17082,37 +17082,37 @@
         <v>2015</v>
       </c>
       <c r="C21">
-        <v>47.7</v>
+        <v>138.44</v>
       </c>
       <c r="D21">
-        <v>41.35</v>
+        <v>206.03</v>
       </c>
       <c r="E21">
-        <v>1.56</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="F21">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="G21">
-        <v>23.71</v>
+        <v>22.96</v>
       </c>
       <c r="H21">
-        <v>2.72</v>
+        <v>1.86</v>
       </c>
       <c r="I21">
-        <v>68.150000000000006</v>
+        <v>335.3</v>
       </c>
       <c r="J21">
-        <v>7.2930000000000001</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>6.1239999999999997</v>
+        <v>14.38</v>
       </c>
       <c r="L21">
-        <v>5.1959999999999997</v>
+        <v>7.89</v>
       </c>
       <c r="M21">
-        <v>0.92800000000000005</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.45">
@@ -17123,37 +17123,37 @@
         <v>2016</v>
       </c>
       <c r="C22">
-        <v>48.36</v>
+        <v>141.4</v>
       </c>
       <c r="D22">
-        <v>41.37</v>
+        <v>206.03</v>
       </c>
       <c r="E22">
-        <v>1.6</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="F22">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="G22">
-        <v>14.65</v>
+        <v>20.02</v>
       </c>
       <c r="H22">
-        <v>8.4700000000000006</v>
+        <v>2.27</v>
       </c>
       <c r="I22">
-        <v>83.97</v>
+        <v>334.29</v>
       </c>
       <c r="J22">
-        <v>6.976</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>5.9649999999999999</v>
+        <v>14.414</v>
       </c>
       <c r="L22">
-        <v>5.0940000000000003</v>
+        <v>7.7569999999999997</v>
       </c>
       <c r="M22">
-        <v>0.871</v>
+        <v>6.657</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.45">
@@ -17164,37 +17164,37 @@
         <v>2017</v>
       </c>
       <c r="C23">
-        <v>49.62</v>
+        <v>145.15</v>
       </c>
       <c r="D23">
-        <v>40.98</v>
+        <v>202.51</v>
       </c>
       <c r="E23">
-        <v>1.66</v>
+        <v>4.83</v>
       </c>
       <c r="F23">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="G23">
-        <v>14.19</v>
+        <v>18.170000000000002</v>
       </c>
       <c r="H23">
-        <v>8.17</v>
+        <v>3.41</v>
       </c>
       <c r="I23">
-        <v>84.95</v>
+        <v>334.56</v>
       </c>
       <c r="J23">
-        <v>6.069</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>5.0659999999999998</v>
+        <v>14.78</v>
       </c>
       <c r="L23">
-        <v>4.2640000000000002</v>
+        <v>8.2469999999999999</v>
       </c>
       <c r="M23">
-        <v>0.80200000000000005</v>
+        <v>6.5330000000000004</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.45">
@@ -17205,37 +17205,37 @@
         <v>2018</v>
       </c>
       <c r="C24">
-        <v>50.77</v>
+        <v>149.49</v>
       </c>
       <c r="D24">
-        <v>40.99</v>
+        <v>203.07</v>
       </c>
       <c r="E24">
-        <v>1.68</v>
+        <v>5.05</v>
       </c>
       <c r="F24">
-        <v>7.0000000000000007E-2</v>
+        <v>0.61</v>
       </c>
       <c r="G24">
-        <v>21.64</v>
+        <v>21.33</v>
       </c>
       <c r="H24">
-        <v>4.3099999999999996</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="I24">
-        <v>73.55</v>
+        <v>329.99</v>
       </c>
       <c r="J24">
-        <v>6.64</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>5.4210000000000003</v>
+        <v>14.939</v>
       </c>
       <c r="L24">
-        <v>4.5540000000000003</v>
+        <v>8.1980000000000004</v>
       </c>
       <c r="M24">
-        <v>0.86699999999999999</v>
+        <v>6.7409999999999997</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.45">
@@ -17246,37 +17246,37 @@
         <v>2019</v>
       </c>
       <c r="C25">
-        <v>51.77</v>
+        <v>153.6</v>
       </c>
       <c r="D25">
-        <v>40.71</v>
+        <v>199.31</v>
       </c>
       <c r="E25">
-        <v>1.63</v>
+        <v>5.29</v>
       </c>
       <c r="F25">
-        <v>0.12</v>
+        <v>0.85</v>
       </c>
       <c r="G25">
-        <v>12.73</v>
+        <v>24.56</v>
       </c>
       <c r="H25">
-        <v>14.59</v>
+        <v>3.39</v>
       </c>
       <c r="I25">
-        <v>92.34</v>
+        <v>321.63</v>
       </c>
       <c r="J25">
-        <v>5.6790000000000003</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>5.7110000000000003</v>
+        <v>14.43</v>
       </c>
       <c r="L25">
-        <v>4.8239999999999998</v>
+        <v>8.0190000000000001</v>
       </c>
       <c r="M25">
-        <v>0.88700000000000001</v>
+        <v>6.4109999999999996</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.45">
@@ -17287,37 +17287,37 @@
         <v>2020</v>
       </c>
       <c r="C26">
-        <v>51.17</v>
+        <v>161.07</v>
       </c>
       <c r="D26">
-        <v>40</v>
+        <v>187.85</v>
       </c>
       <c r="E26">
-        <v>1.44</v>
+        <v>4.8499999999999996</v>
       </c>
       <c r="F26">
-        <v>0.14000000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="G26">
-        <v>13.72</v>
+        <v>22.39</v>
       </c>
       <c r="H26">
-        <v>14.05</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="I26">
-        <v>87.92</v>
+        <v>308.98</v>
       </c>
       <c r="J26">
-        <v>5.5380000000000003</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>5.641</v>
+        <v>14.536</v>
       </c>
       <c r="L26">
-        <v>4.6859999999999999</v>
+        <v>7.601</v>
       </c>
       <c r="M26">
-        <v>0.95499999999999996</v>
+        <v>6.9349999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.45">
@@ -17328,37 +17328,37 @@
         <v>2021</v>
       </c>
       <c r="C27">
-        <v>52.96</v>
+        <v>159.69999999999999</v>
       </c>
       <c r="D27">
-        <v>40.22</v>
+        <v>190.09</v>
       </c>
       <c r="E27">
-        <v>1.52</v>
+        <v>4.74</v>
       </c>
       <c r="F27">
-        <v>0.33</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G27">
-        <v>15.19</v>
+        <v>28.82</v>
       </c>
       <c r="H27">
-        <v>23.07</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="I27">
-        <v>99.05</v>
+        <v>306.74</v>
       </c>
       <c r="J27">
-        <v>5.6970000000000001</v>
+        <v>0</v>
       </c>
       <c r="K27">
-        <v>5.8</v>
+        <v>14.542999999999999</v>
       </c>
       <c r="L27">
-        <v>4.7629999999999999</v>
+        <v>7.4980000000000002</v>
       </c>
       <c r="M27">
-        <v>1.0369999999999999</v>
+        <v>7.0449999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.45">
@@ -17369,37 +17369,37 @@
         <v>2022</v>
       </c>
       <c r="C28">
-        <v>51.47</v>
+        <v>155.49</v>
       </c>
       <c r="D28">
-        <v>38.15</v>
+        <v>177.18</v>
       </c>
       <c r="E28">
-        <v>1.66</v>
+        <v>4.82</v>
       </c>
       <c r="F28">
-        <v>0.61</v>
+        <v>4.08</v>
       </c>
       <c r="G28">
-        <v>16.350000000000001</v>
+        <v>15.51</v>
       </c>
       <c r="H28">
-        <v>23.88</v>
+        <v>20.82</v>
       </c>
       <c r="I28">
-        <v>94.18</v>
+        <v>322.94</v>
       </c>
       <c r="J28">
-        <v>4.9379999999999997</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>5.0049999999999999</v>
+        <v>14.167999999999999</v>
       </c>
       <c r="L28">
-        <v>4.0209999999999999</v>
+        <v>6.9870000000000001</v>
       </c>
       <c r="M28">
-        <v>0.98399999999999999</v>
+        <v>7.181</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.45">
@@ -17410,37 +17410,37 @@
         <v>2023</v>
       </c>
       <c r="C29">
-        <v>50.45</v>
+        <v>154.54</v>
       </c>
       <c r="D29">
-        <v>37.700000000000003</v>
+        <v>174.34</v>
       </c>
       <c r="E29">
-        <v>1.58</v>
+        <v>4.91</v>
       </c>
       <c r="F29">
-        <v>1.1000000000000001</v>
+        <v>6.35</v>
       </c>
       <c r="G29">
-        <v>20.22</v>
+        <v>33.32</v>
       </c>
       <c r="H29">
-        <v>18.59</v>
+        <v>9.49</v>
       </c>
       <c r="I29">
-        <v>82.1</v>
+        <v>292.45999999999998</v>
       </c>
       <c r="J29">
-        <v>4.2699999999999996</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>4.32</v>
+        <v>13.894</v>
       </c>
       <c r="L29">
-        <v>3.1909999999999998</v>
+        <v>6.6689999999999996</v>
       </c>
       <c r="M29">
-        <v>1.129</v>
+        <v>7.2249999999999996</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.45">
@@ -17451,37 +17451,37 @@
         <v>2024</v>
       </c>
       <c r="C30">
-        <v>52.92</v>
+        <v>151.51</v>
       </c>
       <c r="D30">
-        <v>38.72</v>
+        <v>176.15</v>
       </c>
       <c r="E30">
-        <v>1.5</v>
+        <v>5.03</v>
       </c>
       <c r="F30">
-        <v>1.74</v>
+        <v>8.93</v>
       </c>
       <c r="G30">
-        <v>27.75</v>
+        <v>43.73</v>
       </c>
       <c r="H30">
-        <v>17.41</v>
+        <v>10.33</v>
       </c>
       <c r="I30">
-        <v>75.709999999999994</v>
+        <v>283.27</v>
       </c>
       <c r="J30">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="K30">
-        <v>4.0739999999999998</v>
+        <v>14.222</v>
       </c>
       <c r="L30">
-        <v>2.9460000000000002</v>
+        <v>7.1429999999999998</v>
       </c>
       <c r="M30">
-        <v>1.1279999999999999</v>
+        <v>7.0789999999999997</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.45">
@@ -17492,37 +17492,37 @@
         <v>2015</v>
       </c>
       <c r="C31">
-        <v>138.44</v>
+        <v>47.7</v>
       </c>
       <c r="D31">
-        <v>206.03</v>
+        <v>41.35</v>
       </c>
       <c r="E31">
-        <v>4.5199999999999996</v>
+        <v>1.56</v>
       </c>
       <c r="F31">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="G31">
-        <v>22.96</v>
+        <v>23.71</v>
       </c>
       <c r="H31">
-        <v>1.86</v>
+        <v>2.72</v>
       </c>
       <c r="I31">
-        <v>335.3</v>
+        <v>68.150000000000006</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>7.2930000000000001</v>
       </c>
       <c r="K31">
-        <v>14.38</v>
+        <v>6.1239999999999997</v>
       </c>
       <c r="L31">
-        <v>7.89</v>
+        <v>5.1959999999999997</v>
       </c>
       <c r="M31">
-        <v>6.49</v>
+        <v>0.92800000000000005</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
@@ -17533,37 +17533,37 @@
         <v>2016</v>
       </c>
       <c r="C32">
-        <v>141.4</v>
+        <v>48.36</v>
       </c>
       <c r="D32">
-        <v>206.03</v>
+        <v>41.37</v>
       </c>
       <c r="E32">
-        <v>4.6900000000000004</v>
+        <v>1.6</v>
       </c>
       <c r="F32">
-        <v>0.13</v>
+        <v>0.03</v>
       </c>
       <c r="G32">
-        <v>20.02</v>
+        <v>14.65</v>
       </c>
       <c r="H32">
-        <v>2.27</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="I32">
-        <v>334.29</v>
+        <v>83.97</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>6.976</v>
       </c>
       <c r="K32">
-        <v>14.414</v>
+        <v>5.9649999999999999</v>
       </c>
       <c r="L32">
-        <v>7.7569999999999997</v>
+        <v>5.0940000000000003</v>
       </c>
       <c r="M32">
-        <v>6.657</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
@@ -17574,37 +17574,37 @@
         <v>2017</v>
       </c>
       <c r="C33">
-        <v>145.15</v>
+        <v>49.62</v>
       </c>
       <c r="D33">
-        <v>202.51</v>
+        <v>40.98</v>
       </c>
       <c r="E33">
-        <v>4.83</v>
+        <v>1.66</v>
       </c>
       <c r="F33">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="G33">
-        <v>18.170000000000002</v>
+        <v>14.19</v>
       </c>
       <c r="H33">
-        <v>3.41</v>
+        <v>8.17</v>
       </c>
       <c r="I33">
-        <v>334.56</v>
+        <v>84.95</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>6.069</v>
       </c>
       <c r="K33">
-        <v>14.78</v>
+        <v>5.0659999999999998</v>
       </c>
       <c r="L33">
-        <v>8.2469999999999999</v>
+        <v>4.2640000000000002</v>
       </c>
       <c r="M33">
-        <v>6.5330000000000004</v>
+        <v>0.80200000000000005</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
@@ -17615,37 +17615,37 @@
         <v>2018</v>
       </c>
       <c r="C34">
-        <v>149.49</v>
+        <v>50.77</v>
       </c>
       <c r="D34">
-        <v>203.07</v>
+        <v>40.99</v>
       </c>
       <c r="E34">
-        <v>5.05</v>
+        <v>1.68</v>
       </c>
       <c r="F34">
-        <v>0.61</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G34">
-        <v>21.33</v>
+        <v>21.64</v>
       </c>
       <c r="H34">
-        <v>2.2200000000000002</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="I34">
-        <v>329.99</v>
+        <v>73.55</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="K34">
-        <v>14.939</v>
+        <v>5.4210000000000003</v>
       </c>
       <c r="L34">
-        <v>8.1980000000000004</v>
+        <v>4.5540000000000003</v>
       </c>
       <c r="M34">
-        <v>6.7409999999999997</v>
+        <v>0.86699999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
@@ -17656,37 +17656,37 @@
         <v>2019</v>
       </c>
       <c r="C35">
-        <v>153.6</v>
+        <v>51.77</v>
       </c>
       <c r="D35">
-        <v>199.31</v>
+        <v>40.71</v>
       </c>
       <c r="E35">
-        <v>5.29</v>
+        <v>1.63</v>
       </c>
       <c r="F35">
-        <v>0.85</v>
+        <v>0.12</v>
       </c>
       <c r="G35">
-        <v>24.56</v>
+        <v>12.73</v>
       </c>
       <c r="H35">
-        <v>3.39</v>
+        <v>14.59</v>
       </c>
       <c r="I35">
-        <v>321.63</v>
+        <v>92.34</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>5.6790000000000003</v>
       </c>
       <c r="K35">
-        <v>14.43</v>
+        <v>5.7110000000000003</v>
       </c>
       <c r="L35">
-        <v>8.0190000000000001</v>
+        <v>4.8239999999999998</v>
       </c>
       <c r="M35">
-        <v>6.4109999999999996</v>
+        <v>0.88700000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
@@ -17697,37 +17697,37 @@
         <v>2020</v>
       </c>
       <c r="C36">
-        <v>161.07</v>
+        <v>51.17</v>
       </c>
       <c r="D36">
-        <v>187.85</v>
+        <v>40</v>
       </c>
       <c r="E36">
-        <v>4.8499999999999996</v>
+        <v>1.44</v>
       </c>
       <c r="F36">
-        <v>0.88</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G36">
-        <v>22.39</v>
+        <v>13.72</v>
       </c>
       <c r="H36">
-        <v>4.4800000000000004</v>
+        <v>14.05</v>
       </c>
       <c r="I36">
-        <v>308.98</v>
+        <v>87.92</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>5.5380000000000003</v>
       </c>
       <c r="K36">
-        <v>14.536</v>
+        <v>5.641</v>
       </c>
       <c r="L36">
-        <v>7.601</v>
+        <v>4.6859999999999999</v>
       </c>
       <c r="M36">
-        <v>6.9349999999999996</v>
+        <v>0.95499999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.45">
@@ -17738,37 +17738,37 @@
         <v>2021</v>
       </c>
       <c r="C37">
-        <v>159.69999999999999</v>
+        <v>52.96</v>
       </c>
       <c r="D37">
-        <v>190.09</v>
+        <v>40.22</v>
       </c>
       <c r="E37">
-        <v>4.74</v>
+        <v>1.52</v>
       </c>
       <c r="F37">
-        <v>2.2599999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="G37">
-        <v>28.82</v>
+        <v>15.19</v>
       </c>
       <c r="H37">
-        <v>4.1900000000000004</v>
+        <v>23.07</v>
       </c>
       <c r="I37">
-        <v>306.74</v>
+        <v>99.05</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>5.6970000000000001</v>
       </c>
       <c r="K37">
-        <v>14.542999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="L37">
-        <v>7.4980000000000002</v>
+        <v>4.7629999999999999</v>
       </c>
       <c r="M37">
-        <v>7.0449999999999999</v>
+        <v>1.0369999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.45">
@@ -17779,37 +17779,37 @@
         <v>2022</v>
       </c>
       <c r="C38">
-        <v>155.49</v>
+        <v>51.47</v>
       </c>
       <c r="D38">
-        <v>177.18</v>
+        <v>38.15</v>
       </c>
       <c r="E38">
-        <v>4.82</v>
+        <v>1.66</v>
       </c>
       <c r="F38">
-        <v>4.08</v>
+        <v>0.61</v>
       </c>
       <c r="G38">
-        <v>15.51</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="H38">
-        <v>20.82</v>
+        <v>23.88</v>
       </c>
       <c r="I38">
-        <v>322.94</v>
+        <v>94.18</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>4.9379999999999997</v>
       </c>
       <c r="K38">
-        <v>14.167999999999999</v>
+        <v>5.0049999999999999</v>
       </c>
       <c r="L38">
-        <v>6.9870000000000001</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="M38">
-        <v>7.181</v>
+        <v>0.98399999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.45">
@@ -17820,37 +17820,37 @@
         <v>2023</v>
       </c>
       <c r="C39">
-        <v>154.54</v>
+        <v>50.45</v>
       </c>
       <c r="D39">
-        <v>174.34</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="E39">
-        <v>4.91</v>
+        <v>1.58</v>
       </c>
       <c r="F39">
-        <v>6.35</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G39">
-        <v>33.32</v>
+        <v>20.22</v>
       </c>
       <c r="H39">
-        <v>9.49</v>
+        <v>18.59</v>
       </c>
       <c r="I39">
-        <v>292.45999999999998</v>
+        <v>82.1</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="K39">
-        <v>13.894</v>
+        <v>4.32</v>
       </c>
       <c r="L39">
-        <v>6.6689999999999996</v>
+        <v>3.1909999999999998</v>
       </c>
       <c r="M39">
-        <v>7.2249999999999996</v>
+        <v>1.129</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.45">
@@ -17861,37 +17861,37 @@
         <v>2024</v>
       </c>
       <c r="C40">
-        <v>151.51</v>
+        <v>52.92</v>
       </c>
       <c r="D40">
-        <v>176.15</v>
+        <v>38.72</v>
       </c>
       <c r="E40">
-        <v>5.03</v>
+        <v>1.5</v>
       </c>
       <c r="F40">
-        <v>8.93</v>
+        <v>1.74</v>
       </c>
       <c r="G40">
-        <v>43.73</v>
+        <v>27.75</v>
       </c>
       <c r="H40">
-        <v>10.33</v>
+        <v>17.41</v>
       </c>
       <c r="I40">
-        <v>283.27</v>
+        <v>75.709999999999994</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="K40">
-        <v>14.222</v>
+        <v>4.0739999999999998</v>
       </c>
       <c r="L40">
-        <v>7.1429999999999998</v>
+        <v>2.9460000000000002</v>
       </c>
       <c r="M40">
-        <v>7.0789999999999997</v>
+        <v>1.1279999999999999</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.45">
@@ -17902,37 +17902,37 @@
         <v>2015</v>
       </c>
       <c r="C41">
-        <v>57.21</v>
+        <v>279.04000000000002</v>
       </c>
       <c r="D41">
-        <v>67.48</v>
+        <v>274.98</v>
       </c>
       <c r="E41">
-        <v>1.64</v>
+        <v>11.07</v>
       </c>
       <c r="F41">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="G41">
-        <v>30.76</v>
+        <v>37.01</v>
       </c>
       <c r="H41">
-        <v>22.01</v>
+        <v>85.29</v>
       </c>
       <c r="I41">
-        <v>110.21</v>
+        <v>642.39</v>
       </c>
       <c r="J41">
-        <v>29.603000000000002</v>
+        <v>91.739000000000004</v>
       </c>
       <c r="K41">
-        <v>21.741</v>
+        <v>111.577</v>
       </c>
       <c r="L41">
-        <v>20.081</v>
+        <v>48.174999999999997</v>
       </c>
       <c r="M41">
-        <v>1.66</v>
+        <v>63.402000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.45">
@@ -17943,37 +17943,37 @@
         <v>2016</v>
       </c>
       <c r="C42">
-        <v>58.53</v>
+        <v>285.44</v>
       </c>
       <c r="D42">
-        <v>67.13</v>
+        <v>275.24</v>
       </c>
       <c r="E42">
-        <v>1.71</v>
+        <v>11.63</v>
       </c>
       <c r="F42">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="G42">
-        <v>24.26</v>
+        <v>28.34</v>
       </c>
       <c r="H42">
-        <v>19.34</v>
+        <v>78.86</v>
       </c>
       <c r="I42">
-        <v>115.16</v>
+        <v>644.86</v>
       </c>
       <c r="J42">
-        <v>28.346</v>
+        <v>95.225999999999999</v>
       </c>
       <c r="K42">
-        <v>21.286999999999999</v>
+        <v>113.752</v>
       </c>
       <c r="L42">
-        <v>19.175000000000001</v>
+        <v>49.697000000000003</v>
       </c>
       <c r="M42">
-        <v>2.1120000000000001</v>
+        <v>64.055000000000007</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.45">
@@ -17984,37 +17984,37 @@
         <v>2017</v>
       </c>
       <c r="C43">
-        <v>60.87</v>
+        <v>289</v>
       </c>
       <c r="D43">
-        <v>68</v>
+        <v>274.77</v>
       </c>
       <c r="E43">
-        <v>1.72</v>
+        <v>11.8</v>
       </c>
       <c r="F43">
-        <v>0.28000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="G43">
-        <v>22.46</v>
+        <v>27.84</v>
       </c>
       <c r="H43">
-        <v>18.95</v>
+        <v>80.3</v>
       </c>
       <c r="I43">
-        <v>117.17</v>
+        <v>647.72</v>
       </c>
       <c r="J43">
-        <v>27.327999999999999</v>
+        <v>95.143000000000001</v>
       </c>
       <c r="K43">
-        <v>19.71</v>
+        <v>114.04600000000001</v>
       </c>
       <c r="L43">
-        <v>17.439</v>
+        <v>47.804000000000002</v>
       </c>
       <c r="M43">
-        <v>2.2709999999999999</v>
+        <v>66.242000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.45">
@@ -18025,37 +18025,37 @@
         <v>2018</v>
       </c>
       <c r="C44">
-        <v>63.16</v>
+        <v>285.68</v>
       </c>
       <c r="D44">
-        <v>69.34</v>
+        <v>266.58</v>
       </c>
       <c r="E44">
-        <v>1.78</v>
+        <v>11.86</v>
       </c>
       <c r="F44">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="G44">
-        <v>26.75</v>
+        <v>31.73</v>
       </c>
       <c r="H44">
-        <v>18.78</v>
+        <v>80.459999999999994</v>
       </c>
       <c r="I44">
-        <v>114.38</v>
+        <v>634.29999999999995</v>
       </c>
       <c r="J44">
-        <v>24.956</v>
+        <v>98.507999999999996</v>
       </c>
       <c r="K44">
-        <v>21.138999999999999</v>
+        <v>110.97799999999999</v>
       </c>
       <c r="L44">
-        <v>16.437999999999999</v>
+        <v>52.889000000000003</v>
       </c>
       <c r="M44">
-        <v>4.7009999999999996</v>
+        <v>58.088999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.45">
@@ -18066,37 +18066,37 @@
         <v>2019</v>
       </c>
       <c r="C45">
-        <v>64.650000000000006</v>
+        <v>276.60000000000002</v>
       </c>
       <c r="D45">
-        <v>69.540000000000006</v>
+        <v>261.64</v>
       </c>
       <c r="E45">
-        <v>1.81</v>
+        <v>11.27</v>
       </c>
       <c r="F45">
-        <v>0.53</v>
+        <v>0.34</v>
       </c>
       <c r="G45">
-        <v>20.399999999999999</v>
+        <v>40.130000000000003</v>
       </c>
       <c r="H45">
-        <v>19.55</v>
+        <v>72.790000000000006</v>
       </c>
       <c r="I45">
-        <v>121.41</v>
+        <v>600.98</v>
       </c>
       <c r="J45">
-        <v>24.497</v>
+        <v>97.305999999999997</v>
       </c>
       <c r="K45">
-        <v>22.204000000000001</v>
+        <v>111.782</v>
       </c>
       <c r="L45">
-        <v>17.024999999999999</v>
+        <v>49.478999999999999</v>
       </c>
       <c r="M45">
-        <v>5.1790000000000003</v>
+        <v>62.302999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.45">
@@ -18107,37 +18107,37 @@
         <v>2020</v>
       </c>
       <c r="C46">
-        <v>70.2</v>
+        <v>264.64</v>
       </c>
       <c r="D46">
-        <v>68.33</v>
+        <v>259.06</v>
       </c>
       <c r="E46">
-        <v>1.63</v>
+        <v>10.87</v>
       </c>
       <c r="F46">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G46">
-        <v>19.77</v>
+        <v>47.85</v>
       </c>
       <c r="H46">
-        <v>22.43</v>
+        <v>66.88</v>
       </c>
       <c r="I46">
-        <v>123.28</v>
+        <v>568.91</v>
       </c>
       <c r="J46">
-        <v>21.129000000000001</v>
+        <v>89.994</v>
       </c>
       <c r="K46">
-        <v>20.227</v>
+        <v>103.56699999999999</v>
       </c>
       <c r="L46">
-        <v>15.135999999999999</v>
+        <v>46.262</v>
       </c>
       <c r="M46">
-        <v>5.0910000000000002</v>
+        <v>57.305</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.45">
@@ -18148,37 +18148,37 @@
         <v>2021</v>
       </c>
       <c r="C47">
-        <v>72.55</v>
+        <v>273.68</v>
       </c>
       <c r="D47">
-        <v>69.25</v>
+        <v>267.54000000000002</v>
       </c>
       <c r="E47">
-        <v>1.63</v>
+        <v>11.48</v>
       </c>
       <c r="F47">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="G47">
-        <v>20.89</v>
+        <v>51.73</v>
       </c>
       <c r="H47">
-        <v>20.63</v>
+        <v>70.31</v>
       </c>
       <c r="I47">
-        <v>122.17</v>
+        <v>587.46</v>
       </c>
       <c r="J47">
-        <v>21.524999999999999</v>
+        <v>97.787000000000006</v>
       </c>
       <c r="K47">
-        <v>21.481000000000002</v>
+        <v>113.82899999999999</v>
       </c>
       <c r="L47">
-        <v>16.103000000000002</v>
+        <v>48.845999999999997</v>
       </c>
       <c r="M47">
-        <v>5.3780000000000001</v>
+        <v>64.983000000000004</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.45">
@@ -18189,37 +18189,37 @@
         <v>2022</v>
       </c>
       <c r="C48">
-        <v>71.5</v>
+        <v>254.86</v>
       </c>
       <c r="D48">
-        <v>65.88</v>
+        <v>255.66</v>
       </c>
       <c r="E48">
-        <v>1.69</v>
+        <v>12.95</v>
       </c>
       <c r="F48">
-        <v>1.65</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G48">
-        <v>18.54</v>
+        <v>49.33</v>
       </c>
       <c r="H48">
-        <v>22.81</v>
+        <v>76.59</v>
       </c>
       <c r="I48">
-        <v>121.57</v>
+        <v>573</v>
       </c>
       <c r="J48">
-        <v>20.457000000000001</v>
+        <v>88.561999999999998</v>
       </c>
       <c r="K48">
-        <v>19.547000000000001</v>
+        <v>103.169</v>
       </c>
       <c r="L48">
-        <v>14.882</v>
+        <v>45.581000000000003</v>
       </c>
       <c r="M48">
-        <v>4.665</v>
+        <v>57.588000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.45">
@@ -18230,37 +18230,37 @@
         <v>2023</v>
       </c>
       <c r="C49">
-        <v>72.709999999999994</v>
+        <v>279.62</v>
       </c>
       <c r="D49">
-        <v>65.349999999999994</v>
+        <v>256.26</v>
       </c>
       <c r="E49">
-        <v>1.66</v>
+        <v>12.74</v>
       </c>
       <c r="F49">
-        <v>2.21</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="G49">
-        <v>19.55</v>
+        <v>69.31</v>
       </c>
       <c r="H49">
-        <v>25.21</v>
+        <v>60.08</v>
       </c>
       <c r="I49">
-        <v>121.64</v>
+        <v>517.42999999999995</v>
       </c>
       <c r="J49">
-        <v>18.094000000000001</v>
+        <v>83.772000000000006</v>
       </c>
       <c r="K49">
-        <v>17.292000000000002</v>
+        <v>99.41</v>
       </c>
       <c r="L49">
-        <v>13.074999999999999</v>
+        <v>42.277999999999999</v>
       </c>
       <c r="M49">
-        <v>4.2169999999999996</v>
+        <v>57.131999999999998</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.45">
@@ -18271,37 +18271,37 @@
         <v>2024</v>
       </c>
       <c r="C50">
-        <v>74.430000000000007</v>
+        <v>293</v>
       </c>
       <c r="D50">
-        <v>68.8</v>
+        <v>257.72000000000003</v>
       </c>
       <c r="E50">
-        <v>1.7</v>
+        <v>11.58</v>
       </c>
       <c r="F50">
-        <v>2.75</v>
+        <v>5.91</v>
       </c>
       <c r="G50">
-        <v>20.03</v>
+        <v>81.66</v>
       </c>
       <c r="H50">
-        <v>24.25</v>
+        <v>55.39</v>
       </c>
       <c r="I50">
-        <v>123.84</v>
+        <v>507.66</v>
       </c>
       <c r="J50">
-        <v>16.524000000000001</v>
+        <v>81.938000000000002</v>
       </c>
       <c r="K50">
-        <v>17.977</v>
+        <v>100.52500000000001</v>
       </c>
       <c r="L50">
-        <v>13.765000000000001</v>
+        <v>43.360999999999997</v>
       </c>
       <c r="M50">
-        <v>4.2119999999999997</v>
+        <v>57.164000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.45">
@@ -18312,37 +18312,37 @@
         <v>2015</v>
       </c>
       <c r="C51">
-        <v>279.04000000000002</v>
+        <v>25</v>
       </c>
       <c r="D51">
-        <v>274.98</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="E51">
-        <v>11.07</v>
+        <v>3.14</v>
       </c>
       <c r="F51">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="G51">
-        <v>37.01</v>
+        <v>34.03</v>
       </c>
       <c r="H51">
-        <v>85.29</v>
+        <v>35.07</v>
       </c>
       <c r="I51">
-        <v>642.39</v>
+        <v>66.08</v>
       </c>
       <c r="J51">
-        <v>91.739000000000004</v>
+        <v>4.3970000000000002</v>
       </c>
       <c r="K51">
-        <v>111.577</v>
+        <v>5.5270000000000001</v>
       </c>
       <c r="L51">
-        <v>48.174999999999997</v>
+        <v>2.0230000000000001</v>
       </c>
       <c r="M51">
-        <v>63.402000000000001</v>
+        <v>3.504</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.45">
@@ -18353,37 +18353,37 @@
         <v>2016</v>
       </c>
       <c r="C52">
-        <v>285.44</v>
+        <v>24.9</v>
       </c>
       <c r="D52">
-        <v>275.24</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="E52">
-        <v>11.63</v>
+        <v>3.2</v>
       </c>
       <c r="F52">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="G52">
-        <v>28.34</v>
+        <v>34.1</v>
       </c>
       <c r="H52">
-        <v>78.86</v>
+        <v>30.17</v>
       </c>
       <c r="I52">
-        <v>644.86</v>
+        <v>61.12</v>
       </c>
       <c r="J52">
-        <v>95.225999999999999</v>
+        <v>4.766</v>
       </c>
       <c r="K52">
-        <v>113.752</v>
+        <v>5.9560000000000004</v>
       </c>
       <c r="L52">
-        <v>49.697000000000003</v>
+        <v>2.0840000000000001</v>
       </c>
       <c r="M52">
-        <v>64.055000000000007</v>
+        <v>3.8719999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.45">
@@ -18394,37 +18394,37 @@
         <v>2017</v>
       </c>
       <c r="C53">
-        <v>289</v>
+        <v>25.33</v>
       </c>
       <c r="D53">
-        <v>274.77</v>
+        <v>37.18</v>
       </c>
       <c r="E53">
-        <v>11.8</v>
+        <v>3.15</v>
       </c>
       <c r="F53">
-        <v>0.16</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G53">
-        <v>27.84</v>
+        <v>36.5</v>
       </c>
       <c r="H53">
-        <v>80.3</v>
+        <v>30.95</v>
       </c>
       <c r="I53">
-        <v>647.72</v>
+        <v>60.18</v>
       </c>
       <c r="J53">
-        <v>95.143000000000001</v>
+        <v>5.0410000000000004</v>
       </c>
       <c r="K53">
-        <v>114.04600000000001</v>
+        <v>6.2809999999999997</v>
       </c>
       <c r="L53">
-        <v>47.804000000000002</v>
+        <v>2.1709999999999998</v>
       </c>
       <c r="M53">
-        <v>66.242000000000004</v>
+        <v>4.1100000000000003</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
@@ -18435,37 +18435,37 @@
         <v>2018</v>
       </c>
       <c r="C54">
-        <v>285.68</v>
+        <v>25.21</v>
       </c>
       <c r="D54">
-        <v>266.58</v>
+        <v>36.979999999999997</v>
       </c>
       <c r="E54">
-        <v>11.86</v>
+        <v>3.09</v>
       </c>
       <c r="F54">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="G54">
-        <v>31.73</v>
+        <v>31.02</v>
       </c>
       <c r="H54">
-        <v>80.459999999999994</v>
+        <v>32.61</v>
       </c>
       <c r="I54">
-        <v>634.29999999999995</v>
+        <v>66.319999999999993</v>
       </c>
       <c r="J54">
-        <v>98.507999999999996</v>
+        <v>5.07</v>
       </c>
       <c r="K54">
-        <v>110.97799999999999</v>
+        <v>6.2350000000000003</v>
       </c>
       <c r="L54">
-        <v>52.889000000000003</v>
+        <v>2.2189999999999999</v>
       </c>
       <c r="M54">
-        <v>58.088999999999999</v>
+        <v>4.016</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.45">
@@ -18476,37 +18476,37 @@
         <v>2019</v>
       </c>
       <c r="C55">
-        <v>276.60000000000002</v>
+        <v>25.42</v>
       </c>
       <c r="D55">
-        <v>261.64</v>
+        <v>36.590000000000003</v>
       </c>
       <c r="E55">
-        <v>11.27</v>
+        <v>3.04</v>
       </c>
       <c r="F55">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="G55">
-        <v>40.130000000000003</v>
+        <v>29.5</v>
       </c>
       <c r="H55">
-        <v>72.790000000000006</v>
+        <v>35.770000000000003</v>
       </c>
       <c r="I55">
-        <v>600.98</v>
+        <v>70.59</v>
       </c>
       <c r="J55">
-        <v>97.305999999999997</v>
+        <v>5.6820000000000004</v>
       </c>
       <c r="K55">
-        <v>111.782</v>
+        <v>7.0979999999999999</v>
       </c>
       <c r="L55">
-        <v>49.478999999999999</v>
+        <v>2.4329999999999998</v>
       </c>
       <c r="M55">
-        <v>62.302999999999997</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.45">
@@ -18517,37 +18517,37 @@
         <v>2020</v>
       </c>
       <c r="C56">
-        <v>264.64</v>
+        <v>25.45</v>
       </c>
       <c r="D56">
-        <v>259.06</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="E56">
-        <v>10.87</v>
+        <v>2.82</v>
       </c>
       <c r="F56">
-        <v>0.66</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G56">
-        <v>47.85</v>
+        <v>26.99</v>
       </c>
       <c r="H56">
-        <v>66.88</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="I56">
-        <v>568.91</v>
+        <v>68.650000000000006</v>
       </c>
       <c r="J56">
-        <v>89.994</v>
+        <v>5.5659999999999998</v>
       </c>
       <c r="K56">
-        <v>103.56699999999999</v>
+        <v>6.9420000000000002</v>
       </c>
       <c r="L56">
-        <v>46.262</v>
+        <v>2.4140000000000001</v>
       </c>
       <c r="M56">
-        <v>57.305</v>
+        <v>4.5279999999999996</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
@@ -18558,37 +18558,37 @@
         <v>2021</v>
       </c>
       <c r="C57">
-        <v>273.68</v>
+        <v>26.7</v>
       </c>
       <c r="D57">
-        <v>267.54000000000002</v>
+        <v>37.6</v>
       </c>
       <c r="E57">
-        <v>11.48</v>
+        <v>2.97</v>
       </c>
       <c r="F57">
-        <v>1.39</v>
+        <v>0.26</v>
       </c>
       <c r="G57">
-        <v>51.73</v>
+        <v>31.53</v>
       </c>
       <c r="H57">
-        <v>70.31</v>
+        <v>29.12</v>
       </c>
       <c r="I57">
-        <v>587.46</v>
+        <v>63.29</v>
       </c>
       <c r="J57">
-        <v>97.787000000000006</v>
+        <v>5.9770000000000003</v>
       </c>
       <c r="K57">
-        <v>113.82899999999999</v>
+        <v>7.524</v>
       </c>
       <c r="L57">
-        <v>48.845999999999997</v>
+        <v>2.5609999999999999</v>
       </c>
       <c r="M57">
-        <v>64.983000000000004</v>
+        <v>4.9630000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.45">
@@ -18599,37 +18599,37 @@
         <v>2022</v>
       </c>
       <c r="C58">
-        <v>254.86</v>
+        <v>27.22</v>
       </c>
       <c r="D58">
-        <v>255.66</v>
+        <v>36.68</v>
       </c>
       <c r="E58">
-        <v>12.95</v>
+        <v>3.03</v>
       </c>
       <c r="F58">
-        <v>2.4500000000000002</v>
+        <v>0.44</v>
       </c>
       <c r="G58">
-        <v>49.33</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="H58">
-        <v>76.59</v>
+        <v>29.73</v>
       </c>
       <c r="I58">
-        <v>573</v>
+        <v>62</v>
       </c>
       <c r="J58">
-        <v>88.561999999999998</v>
+        <v>5.6429999999999998</v>
       </c>
       <c r="K58">
-        <v>103.169</v>
+        <v>6.9960000000000004</v>
       </c>
       <c r="L58">
-        <v>45.581000000000003</v>
+        <v>2.5449999999999999</v>
       </c>
       <c r="M58">
-        <v>57.588000000000001</v>
+        <v>4.4509999999999996</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.45">
@@ -18640,37 +18640,37 @@
         <v>2023</v>
       </c>
       <c r="C59">
-        <v>279.62</v>
+        <v>27.14</v>
       </c>
       <c r="D59">
-        <v>256.26</v>
+        <v>36.4</v>
       </c>
       <c r="E59">
-        <v>12.74</v>
+        <v>3.02</v>
       </c>
       <c r="F59">
-        <v>4.5199999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="G59">
-        <v>69.31</v>
+        <v>27.46</v>
       </c>
       <c r="H59">
-        <v>60.08</v>
+        <v>33.86</v>
       </c>
       <c r="I59">
-        <v>517.42999999999995</v>
+        <v>70.459999999999994</v>
       </c>
       <c r="J59">
-        <v>83.772000000000006</v>
+        <v>5.9429999999999996</v>
       </c>
       <c r="K59">
-        <v>99.41</v>
+        <v>7.1909999999999998</v>
       </c>
       <c r="L59">
-        <v>42.277999999999999</v>
+        <v>2.6869999999999998</v>
       </c>
       <c r="M59">
-        <v>57.131999999999998</v>
+        <v>4.5039999999999996</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
@@ -18681,37 +18681,37 @@
         <v>2024</v>
       </c>
       <c r="C60">
-        <v>293</v>
+        <v>28.79</v>
       </c>
       <c r="D60">
-        <v>257.72000000000003</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="E60">
-        <v>11.58</v>
+        <v>3.08</v>
       </c>
       <c r="F60">
-        <v>5.91</v>
+        <v>0.88</v>
       </c>
       <c r="G60">
-        <v>81.66</v>
+        <v>25.96</v>
       </c>
       <c r="H60">
-        <v>55.39</v>
+        <v>40.35</v>
       </c>
       <c r="I60">
-        <v>507.66</v>
+        <v>79.23</v>
       </c>
       <c r="J60">
-        <v>81.938000000000002</v>
+        <v>6.3490000000000002</v>
       </c>
       <c r="K60">
-        <v>100.52500000000001</v>
+        <v>7.4550000000000001</v>
       </c>
       <c r="L60">
-        <v>43.360999999999997</v>
+        <v>2.827</v>
       </c>
       <c r="M60">
-        <v>57.164000000000001</v>
+        <v>4.6280000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.45">
@@ -18722,37 +18722,37 @@
         <v>2015</v>
       </c>
       <c r="C61">
-        <v>25</v>
+        <v>131.75</v>
       </c>
       <c r="D61">
-        <v>36.909999999999997</v>
+        <v>163.96</v>
       </c>
       <c r="E61">
-        <v>3.14</v>
+        <v>5.51</v>
       </c>
       <c r="F61">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G61">
-        <v>34.03</v>
+        <v>50.85</v>
       </c>
       <c r="H61">
-        <v>35.07</v>
+        <v>4.47</v>
       </c>
       <c r="I61">
-        <v>66.08</v>
+        <v>281.56</v>
       </c>
       <c r="J61">
-        <v>4.3970000000000002</v>
+        <v>59.222999999999999</v>
       </c>
       <c r="K61">
-        <v>5.5270000000000001</v>
+        <v>44.710999999999999</v>
       </c>
       <c r="L61">
-        <v>2.0230000000000001</v>
+        <v>31.463999999999999</v>
       </c>
       <c r="M61">
-        <v>3.504</v>
+        <v>13.247</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.45">
@@ -18763,37 +18763,37 @@
         <v>2016</v>
       </c>
       <c r="C62">
-        <v>24.9</v>
+        <v>131.72</v>
       </c>
       <c r="D62">
-        <v>37.049999999999997</v>
+        <v>161.61000000000001</v>
       </c>
       <c r="E62">
-        <v>3.2</v>
+        <v>5.84</v>
       </c>
       <c r="F62">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G62">
-        <v>34.1</v>
+        <v>43.18</v>
       </c>
       <c r="H62">
-        <v>30.17</v>
+        <v>6.15</v>
       </c>
       <c r="I62">
-        <v>61.12</v>
+        <v>287.94</v>
       </c>
       <c r="J62">
-        <v>4.766</v>
+        <v>61.045999999999999</v>
       </c>
       <c r="K62">
-        <v>5.9560000000000004</v>
+        <v>45.857999999999997</v>
       </c>
       <c r="L62">
-        <v>2.0840000000000001</v>
+        <v>31.867999999999999</v>
       </c>
       <c r="M62">
-        <v>3.8719999999999999</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.45">
@@ -18804,37 +18804,37 @@
         <v>2017</v>
       </c>
       <c r="C63">
-        <v>25.33</v>
+        <v>135.38999999999999</v>
       </c>
       <c r="D63">
-        <v>37.18</v>
+        <v>164.97</v>
       </c>
       <c r="E63">
-        <v>3.15</v>
+        <v>5.89</v>
       </c>
       <c r="F63">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G63">
-        <v>36.5</v>
+        <v>42.89</v>
       </c>
       <c r="H63">
-        <v>30.95</v>
+        <v>5.13</v>
       </c>
       <c r="I63">
-        <v>60.18</v>
+        <v>294</v>
       </c>
       <c r="J63">
-        <v>5.0410000000000004</v>
+        <v>61.08</v>
       </c>
       <c r="K63">
-        <v>6.2809999999999997</v>
+        <v>47.750999999999998</v>
       </c>
       <c r="L63">
-        <v>2.1709999999999998</v>
+        <v>33.521000000000001</v>
       </c>
       <c r="M63">
-        <v>4.1100000000000003</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.45">
@@ -18845,37 +18845,37 @@
         <v>2018</v>
       </c>
       <c r="C64">
-        <v>25.21</v>
+        <v>138.85</v>
       </c>
       <c r="D64">
-        <v>36.979999999999997</v>
+        <v>165.47</v>
       </c>
       <c r="E64">
-        <v>3.09</v>
+        <v>6.07</v>
       </c>
       <c r="F64">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G64">
-        <v>31.02</v>
+        <v>47.17</v>
       </c>
       <c r="H64">
-        <v>32.61</v>
+        <v>3.27</v>
       </c>
       <c r="I64">
-        <v>66.319999999999993</v>
+        <v>287.99</v>
       </c>
       <c r="J64">
-        <v>5.07</v>
+        <v>59.622</v>
       </c>
       <c r="K64">
-        <v>6.2350000000000003</v>
+        <v>47.627000000000002</v>
       </c>
       <c r="L64">
-        <v>2.2189999999999999</v>
+        <v>30.41</v>
       </c>
       <c r="M64">
-        <v>4.016</v>
+        <v>17.216999999999999</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.45">
@@ -18886,37 +18886,37 @@
         <v>2019</v>
       </c>
       <c r="C65">
-        <v>25.42</v>
+        <v>141.87</v>
       </c>
       <c r="D65">
-        <v>36.590000000000003</v>
+        <v>160.86000000000001</v>
       </c>
       <c r="E65">
-        <v>3.04</v>
+        <v>5.84</v>
       </c>
       <c r="F65">
-        <v>0.12</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G65">
-        <v>29.5</v>
+        <v>43.97</v>
       </c>
       <c r="H65">
-        <v>35.770000000000003</v>
+        <v>5.83</v>
       </c>
       <c r="I65">
-        <v>70.59</v>
+        <v>292.02</v>
       </c>
       <c r="J65">
-        <v>5.6820000000000004</v>
+        <v>60.246000000000002</v>
       </c>
       <c r="K65">
-        <v>7.0979999999999999</v>
+        <v>48.22</v>
       </c>
       <c r="L65">
-        <v>2.4329999999999998</v>
+        <v>34.286000000000001</v>
       </c>
       <c r="M65">
-        <v>4.665</v>
+        <v>13.933999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.45">
@@ -18927,37 +18927,37 @@
         <v>2020</v>
       </c>
       <c r="C66">
-        <v>25.45</v>
+        <v>137.63999999999999</v>
       </c>
       <c r="D66">
-        <v>36.159999999999997</v>
+        <v>147.78</v>
       </c>
       <c r="E66">
-        <v>2.82</v>
+        <v>4.93</v>
       </c>
       <c r="F66">
-        <v>0.14000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="G66">
-        <v>26.99</v>
+        <v>39.79</v>
       </c>
       <c r="H66">
-        <v>32.549999999999997</v>
+        <v>7.59</v>
       </c>
       <c r="I66">
-        <v>68.650000000000006</v>
+        <v>278.58999999999997</v>
       </c>
       <c r="J66">
-        <v>5.5659999999999998</v>
+        <v>59.3</v>
       </c>
       <c r="K66">
-        <v>6.9420000000000002</v>
+        <v>45.024000000000001</v>
       </c>
       <c r="L66">
-        <v>2.4140000000000001</v>
+        <v>31.337</v>
       </c>
       <c r="M66">
-        <v>4.5279999999999996</v>
+        <v>13.686999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.45">
@@ -18968,37 +18968,37 @@
         <v>2021</v>
       </c>
       <c r="C67">
-        <v>26.7</v>
+        <v>167.82</v>
       </c>
       <c r="D67">
-        <v>37.6</v>
+        <v>165.99</v>
       </c>
       <c r="E67">
-        <v>2.97</v>
+        <v>5.46</v>
       </c>
       <c r="F67">
-        <v>0.26</v>
+        <v>0.44</v>
       </c>
       <c r="G67">
-        <v>31.53</v>
+        <v>46.57</v>
       </c>
       <c r="H67">
-        <v>29.12</v>
+        <v>3.78</v>
       </c>
       <c r="I67">
-        <v>63.29</v>
+        <v>286.98</v>
       </c>
       <c r="J67">
-        <v>5.9770000000000003</v>
+        <v>21.324000000000002</v>
       </c>
       <c r="K67">
-        <v>7.524</v>
+        <v>17.997</v>
       </c>
       <c r="L67">
-        <v>2.5609999999999999</v>
+        <v>6.89</v>
       </c>
       <c r="M67">
-        <v>4.9630000000000001</v>
+        <v>11.106999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.45">
@@ -19009,37 +19009,37 @@
         <v>2022</v>
       </c>
       <c r="C68">
-        <v>27.22</v>
+        <v>165.68</v>
       </c>
       <c r="D68">
-        <v>36.68</v>
+        <v>166.22</v>
       </c>
       <c r="E68">
-        <v>3.03</v>
+        <v>5.9</v>
       </c>
       <c r="F68">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="G68">
-        <v>33.119999999999997</v>
+        <v>47.39</v>
       </c>
       <c r="H68">
-        <v>29.73</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I68">
-        <v>62</v>
+        <v>282.07</v>
       </c>
       <c r="J68">
-        <v>5.6429999999999998</v>
+        <v>19.646999999999998</v>
       </c>
       <c r="K68">
-        <v>6.9960000000000004</v>
+        <v>17.373000000000001</v>
       </c>
       <c r="L68">
-        <v>2.5449999999999999</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="M68">
-        <v>4.4509999999999996</v>
+        <v>10.842000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.45">
@@ -19050,37 +19050,37 @@
         <v>2023</v>
       </c>
       <c r="C69">
-        <v>27.14</v>
+        <v>160.19</v>
       </c>
       <c r="D69">
-        <v>36.4</v>
+        <v>163.18</v>
       </c>
       <c r="E69">
-        <v>3.02</v>
+        <v>6.49</v>
       </c>
       <c r="F69">
-        <v>0.62</v>
+        <v>0.82</v>
       </c>
       <c r="G69">
-        <v>27.46</v>
+        <v>54.57</v>
       </c>
       <c r="H69">
-        <v>33.86</v>
+        <v>3.32</v>
       </c>
       <c r="I69">
-        <v>70.459999999999994</v>
+        <v>263.17</v>
       </c>
       <c r="J69">
-        <v>5.9429999999999996</v>
+        <v>19.937000000000001</v>
       </c>
       <c r="K69">
-        <v>7.1909999999999998</v>
+        <v>16.628</v>
       </c>
       <c r="L69">
-        <v>2.6869999999999998</v>
+        <v>6.5359999999999996</v>
       </c>
       <c r="M69">
-        <v>4.5039999999999996</v>
+        <v>10.092000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.45">
@@ -19091,37 +19091,37 @@
         <v>2024</v>
       </c>
       <c r="C70">
-        <v>28.79</v>
+        <v>163.46</v>
       </c>
       <c r="D70">
-        <v>36.909999999999997</v>
+        <v>168.27</v>
       </c>
       <c r="E70">
-        <v>3.08</v>
+        <v>6.63</v>
       </c>
       <c r="F70">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="G70">
-        <v>25.96</v>
+        <v>55.91</v>
       </c>
       <c r="H70">
-        <v>40.35</v>
+        <v>4.91</v>
       </c>
       <c r="I70">
-        <v>79.23</v>
+        <v>269.38</v>
       </c>
       <c r="J70">
-        <v>6.3490000000000002</v>
+        <v>20.145</v>
       </c>
       <c r="K70">
-        <v>7.4550000000000001</v>
+        <v>17.812999999999999</v>
       </c>
       <c r="L70">
-        <v>2.827</v>
+        <v>6.508</v>
       </c>
       <c r="M70">
-        <v>4.6280000000000001</v>
+        <v>11.305</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.45">
@@ -19132,37 +19132,37 @@
         <v>2015</v>
       </c>
       <c r="C71">
-        <v>131.75</v>
+        <v>111.6</v>
       </c>
       <c r="D71">
-        <v>163.96</v>
+        <v>150</v>
       </c>
       <c r="E71">
-        <v>5.51</v>
+        <v>3.93</v>
       </c>
       <c r="F71">
-        <v>7.0000000000000007E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G71">
-        <v>50.85</v>
+        <v>14.96</v>
       </c>
       <c r="H71">
-        <v>4.47</v>
+        <v>15.09</v>
       </c>
       <c r="I71">
-        <v>281.56</v>
+        <v>277.68</v>
       </c>
       <c r="J71">
-        <v>59.222999999999999</v>
+        <v>0</v>
       </c>
       <c r="K71">
-        <v>44.710999999999999</v>
+        <v>0</v>
       </c>
       <c r="L71">
-        <v>31.463999999999999</v>
+        <v>0</v>
       </c>
       <c r="M71">
-        <v>13.247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.45">
@@ -19173,37 +19173,37 @@
         <v>2016</v>
       </c>
       <c r="C72">
-        <v>131.72</v>
+        <v>113.7</v>
       </c>
       <c r="D72">
-        <v>161.61000000000001</v>
+        <v>149.02000000000001</v>
       </c>
       <c r="E72">
-        <v>5.84</v>
+        <v>3.84</v>
       </c>
       <c r="F72">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G72">
-        <v>43.18</v>
+        <v>21.84</v>
       </c>
       <c r="H72">
-        <v>6.15</v>
+        <v>14.18</v>
       </c>
       <c r="I72">
-        <v>287.94</v>
+        <v>271.3</v>
       </c>
       <c r="J72">
-        <v>61.045999999999999</v>
+        <v>0</v>
       </c>
       <c r="K72">
-        <v>45.857999999999997</v>
+        <v>0</v>
       </c>
       <c r="L72">
-        <v>31.867999999999999</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>13.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.45">
@@ -19214,37 +19214,37 @@
         <v>2017</v>
       </c>
       <c r="C73">
-        <v>135.38999999999999</v>
+        <v>118.66</v>
       </c>
       <c r="D73">
-        <v>164.97</v>
+        <v>152.59</v>
       </c>
       <c r="E73">
-        <v>5.89</v>
+        <v>3.9</v>
       </c>
       <c r="F73">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G73">
-        <v>42.89</v>
+        <v>23.76</v>
       </c>
       <c r="H73">
-        <v>5.13</v>
+        <v>14.59</v>
       </c>
       <c r="I73">
-        <v>294</v>
+        <v>272.98</v>
       </c>
       <c r="J73">
-        <v>61.08</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>47.750999999999998</v>
+        <v>0</v>
       </c>
       <c r="L73">
-        <v>33.521000000000001</v>
+        <v>0</v>
       </c>
       <c r="M73">
-        <v>14.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.45">
@@ -19255,37 +19255,37 @@
         <v>2018</v>
       </c>
       <c r="C74">
-        <v>138.85</v>
+        <v>117.47</v>
       </c>
       <c r="D74">
-        <v>165.47</v>
+        <v>154.53</v>
       </c>
       <c r="E74">
-        <v>6.07</v>
+        <v>3.91</v>
       </c>
       <c r="F74">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G74">
-        <v>47.17</v>
+        <v>24.02</v>
       </c>
       <c r="H74">
-        <v>3.27</v>
+        <v>12.92</v>
       </c>
       <c r="I74">
-        <v>287.99</v>
+        <v>271.98</v>
       </c>
       <c r="J74">
-        <v>59.622</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>47.627000000000002</v>
+        <v>0</v>
       </c>
       <c r="L74">
-        <v>30.41</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>17.216999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.45">
@@ -19296,37 +19296,37 @@
         <v>2019</v>
       </c>
       <c r="C75">
-        <v>141.87</v>
+        <v>115.82</v>
       </c>
       <c r="D75">
-        <v>160.86000000000001</v>
+        <v>153.09</v>
       </c>
       <c r="E75">
-        <v>5.84</v>
+        <v>3.76</v>
       </c>
       <c r="F75">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="G75">
-        <v>43.97</v>
+        <v>18.72</v>
       </c>
       <c r="H75">
-        <v>5.83</v>
+        <v>11.86</v>
       </c>
       <c r="I75">
-        <v>292.02</v>
+        <v>271.02999999999997</v>
       </c>
       <c r="J75">
-        <v>60.246000000000002</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>48.22</v>
+        <v>0</v>
       </c>
       <c r="L75">
-        <v>34.286000000000001</v>
+        <v>0</v>
       </c>
       <c r="M75">
-        <v>13.933999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.45">
@@ -19337,37 +19337,37 @@
         <v>2020</v>
       </c>
       <c r="C76">
-        <v>137.63999999999999</v>
+        <v>106.27</v>
       </c>
       <c r="D76">
-        <v>147.78</v>
+        <v>145.71</v>
       </c>
       <c r="E76">
-        <v>4.93</v>
+        <v>3.11</v>
       </c>
       <c r="F76">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G76">
-        <v>39.79</v>
+        <v>17.93</v>
       </c>
       <c r="H76">
-        <v>7.59</v>
+        <v>14.65</v>
       </c>
       <c r="I76">
-        <v>278.58999999999997</v>
+        <v>259.88</v>
       </c>
       <c r="J76">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="K76">
-        <v>45.024000000000001</v>
+        <v>0</v>
       </c>
       <c r="L76">
-        <v>31.337</v>
+        <v>0</v>
       </c>
       <c r="M76">
-        <v>13.686999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.45">
@@ -19378,37 +19378,37 @@
         <v>2021</v>
       </c>
       <c r="C77">
-        <v>167.82</v>
+        <v>114</v>
       </c>
       <c r="D77">
-        <v>165.99</v>
+        <v>148.05000000000001</v>
       </c>
       <c r="E77">
-        <v>5.46</v>
+        <v>3.29</v>
       </c>
       <c r="F77">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="G77">
-        <v>46.57</v>
+        <v>17.41</v>
       </c>
       <c r="H77">
-        <v>3.78</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="I77">
-        <v>286.98</v>
+        <v>271.08999999999997</v>
       </c>
       <c r="J77">
-        <v>21.324000000000002</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>17.997</v>
+        <v>0</v>
       </c>
       <c r="L77">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>11.106999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.45">
@@ -19419,37 +19419,37 @@
         <v>2022</v>
       </c>
       <c r="C78">
-        <v>165.68</v>
+        <v>102.28</v>
       </c>
       <c r="D78">
-        <v>166.22</v>
+        <v>148.93</v>
       </c>
       <c r="E78">
-        <v>5.9</v>
+        <v>3.43</v>
       </c>
       <c r="F78">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G78">
-        <v>47.39</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="H78">
-        <v>4.4000000000000004</v>
+        <v>27.83</v>
       </c>
       <c r="I78">
-        <v>282.07</v>
+        <v>287.94</v>
       </c>
       <c r="J78">
-        <v>19.646999999999998</v>
+        <v>0</v>
       </c>
       <c r="K78">
-        <v>17.373000000000001</v>
+        <v>0</v>
       </c>
       <c r="L78">
-        <v>6.5309999999999997</v>
+        <v>0</v>
       </c>
       <c r="M78">
-        <v>10.842000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.45">
@@ -19460,37 +19460,37 @@
         <v>2023</v>
       </c>
       <c r="C79">
-        <v>160.19</v>
+        <v>100.97</v>
       </c>
       <c r="D79">
-        <v>163.18</v>
+        <v>151.04</v>
       </c>
       <c r="E79">
-        <v>6.49</v>
+        <v>3.52</v>
       </c>
       <c r="F79">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="G79">
-        <v>54.57</v>
+        <v>11.32</v>
       </c>
       <c r="H79">
-        <v>3.32</v>
+        <v>25.27</v>
       </c>
       <c r="I79">
-        <v>263.17</v>
+        <v>279.77</v>
       </c>
       <c r="J79">
-        <v>19.937000000000001</v>
+        <v>0</v>
       </c>
       <c r="K79">
-        <v>16.628</v>
+        <v>0</v>
       </c>
       <c r="L79">
-        <v>6.5359999999999996</v>
+        <v>0</v>
       </c>
       <c r="M79">
-        <v>10.092000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.45">
@@ -19501,37 +19501,37 @@
         <v>2024</v>
       </c>
       <c r="C80">
-        <v>163.46</v>
+        <v>104.1</v>
       </c>
       <c r="D80">
-        <v>168.27</v>
+        <v>156.66999999999999</v>
       </c>
       <c r="E80">
-        <v>6.63</v>
+        <v>3.76</v>
       </c>
       <c r="F80">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="G80">
-        <v>55.91</v>
+        <v>14.35</v>
       </c>
       <c r="H80">
-        <v>4.91</v>
+        <v>24.58</v>
       </c>
       <c r="I80">
-        <v>269.38</v>
+        <v>281.51</v>
       </c>
       <c r="J80">
-        <v>20.145</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="K80">
-        <v>17.812999999999999</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="L80">
-        <v>6.508</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="M80">
-        <v>11.305</v>
+        <v>0.48799999999999999</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.45">
@@ -19542,37 +19542,37 @@
         <v>2015</v>
       </c>
       <c r="C81">
-        <v>111.6</v>
+        <v>57.21</v>
       </c>
       <c r="D81">
-        <v>150</v>
+        <v>67.48</v>
       </c>
       <c r="E81">
-        <v>3.93</v>
+        <v>1.64</v>
       </c>
       <c r="F81">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="G81">
-        <v>14.96</v>
+        <v>30.76</v>
       </c>
       <c r="H81">
-        <v>15.09</v>
+        <v>22.01</v>
       </c>
       <c r="I81">
-        <v>277.68</v>
+        <v>110.21</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>29.603000000000002</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>21.741</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>20.081</v>
       </c>
       <c r="M81">
-        <v>0</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.45">
@@ -19583,37 +19583,37 @@
         <v>2016</v>
       </c>
       <c r="C82">
-        <v>113.7</v>
+        <v>58.53</v>
       </c>
       <c r="D82">
-        <v>149.02000000000001</v>
+        <v>67.13</v>
       </c>
       <c r="E82">
-        <v>3.84</v>
+        <v>1.71</v>
       </c>
       <c r="F82">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="G82">
-        <v>21.84</v>
+        <v>24.26</v>
       </c>
       <c r="H82">
-        <v>14.18</v>
+        <v>19.34</v>
       </c>
       <c r="I82">
-        <v>271.3</v>
+        <v>115.16</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>28.346</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>21.286999999999999</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>19.175000000000001</v>
       </c>
       <c r="M82">
-        <v>0</v>
+        <v>2.1120000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.45">
@@ -19624,37 +19624,37 @@
         <v>2017</v>
       </c>
       <c r="C83">
-        <v>118.66</v>
+        <v>60.87</v>
       </c>
       <c r="D83">
-        <v>152.59</v>
+        <v>68</v>
       </c>
       <c r="E83">
-        <v>3.9</v>
+        <v>1.72</v>
       </c>
       <c r="F83">
-        <v>0.06</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G83">
-        <v>23.76</v>
+        <v>22.46</v>
       </c>
       <c r="H83">
-        <v>14.59</v>
+        <v>18.95</v>
       </c>
       <c r="I83">
-        <v>272.98</v>
+        <v>117.17</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>27.327999999999999</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>19.71</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>17.439</v>
       </c>
       <c r="M83">
-        <v>0</v>
+        <v>2.2709999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.45">
@@ -19665,37 +19665,37 @@
         <v>2018</v>
       </c>
       <c r="C84">
-        <v>117.47</v>
+        <v>63.16</v>
       </c>
       <c r="D84">
-        <v>154.53</v>
+        <v>69.34</v>
       </c>
       <c r="E84">
-        <v>3.91</v>
+        <v>1.78</v>
       </c>
       <c r="F84">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="G84">
-        <v>24.02</v>
+        <v>26.75</v>
       </c>
       <c r="H84">
-        <v>12.92</v>
+        <v>18.78</v>
       </c>
       <c r="I84">
-        <v>271.98</v>
+        <v>114.38</v>
       </c>
       <c r="J84">
-        <v>0</v>
+        <v>24.956</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>21.138999999999999</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>16.437999999999999</v>
       </c>
       <c r="M84">
-        <v>0</v>
+        <v>4.7009999999999996</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.45">
@@ -19706,37 +19706,37 @@
         <v>2019</v>
       </c>
       <c r="C85">
-        <v>115.82</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="D85">
-        <v>153.09</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="E85">
-        <v>3.76</v>
+        <v>1.81</v>
       </c>
       <c r="F85">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="G85">
-        <v>18.72</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H85">
-        <v>11.86</v>
+        <v>19.55</v>
       </c>
       <c r="I85">
-        <v>271.02999999999997</v>
+        <v>121.41</v>
       </c>
       <c r="J85">
-        <v>0</v>
+        <v>24.497</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>22.204000000000001</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>17.024999999999999</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>5.1790000000000003</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.45">
@@ -19747,37 +19747,37 @@
         <v>2020</v>
       </c>
       <c r="C86">
-        <v>106.27</v>
+        <v>70.2</v>
       </c>
       <c r="D86">
-        <v>145.71</v>
+        <v>68.33</v>
       </c>
       <c r="E86">
-        <v>3.11</v>
+        <v>1.63</v>
       </c>
       <c r="F86">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="G86">
-        <v>17.93</v>
+        <v>19.77</v>
       </c>
       <c r="H86">
-        <v>14.65</v>
+        <v>22.43</v>
       </c>
       <c r="I86">
-        <v>259.88</v>
+        <v>123.28</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>21.129000000000001</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>20.227</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>15.135999999999999</v>
       </c>
       <c r="M86">
-        <v>0</v>
+        <v>5.0910000000000002</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.45">
@@ -19788,37 +19788,37 @@
         <v>2021</v>
       </c>
       <c r="C87">
-        <v>114</v>
+        <v>72.55</v>
       </c>
       <c r="D87">
-        <v>148.05000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E87">
-        <v>3.29</v>
+        <v>1.63</v>
       </c>
       <c r="F87">
-        <v>0.35</v>
+        <v>1.07</v>
       </c>
       <c r="G87">
-        <v>17.41</v>
+        <v>20.89</v>
       </c>
       <c r="H87">
-        <v>16.559999999999999</v>
+        <v>20.63</v>
       </c>
       <c r="I87">
-        <v>271.08999999999997</v>
+        <v>122.17</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>21.524999999999999</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>21.481000000000002</v>
       </c>
       <c r="L87">
-        <v>0</v>
+        <v>16.103000000000002</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>5.3780000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.45">
@@ -19829,37 +19829,37 @@
         <v>2022</v>
       </c>
       <c r="C88">
-        <v>102.28</v>
+        <v>71.5</v>
       </c>
       <c r="D88">
-        <v>148.93</v>
+        <v>65.88</v>
       </c>
       <c r="E88">
-        <v>3.43</v>
+        <v>1.69</v>
       </c>
       <c r="F88">
-        <v>0.53</v>
+        <v>1.65</v>
       </c>
       <c r="G88">
-        <v>8.0299999999999994</v>
+        <v>18.54</v>
       </c>
       <c r="H88">
-        <v>27.83</v>
+        <v>22.81</v>
       </c>
       <c r="I88">
-        <v>287.94</v>
+        <v>121.57</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>20.457000000000001</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>19.547000000000001</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>14.882</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.45">
@@ -19870,37 +19870,37 @@
         <v>2023</v>
       </c>
       <c r="C89">
-        <v>100.97</v>
+        <v>72.709999999999994</v>
       </c>
       <c r="D89">
-        <v>151.04</v>
+        <v>65.349999999999994</v>
       </c>
       <c r="E89">
-        <v>3.52</v>
+        <v>1.66</v>
       </c>
       <c r="F89">
-        <v>0.77</v>
+        <v>2.21</v>
       </c>
       <c r="G89">
-        <v>11.32</v>
+        <v>19.55</v>
       </c>
       <c r="H89">
-        <v>25.27</v>
+        <v>25.21</v>
       </c>
       <c r="I89">
-        <v>279.77</v>
+        <v>121.64</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>18.094000000000001</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>17.292000000000002</v>
       </c>
       <c r="L89">
-        <v>0</v>
+        <v>13.074999999999999</v>
       </c>
       <c r="M89">
-        <v>0</v>
+        <v>4.2169999999999996</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.45">
@@ -19911,37 +19911,37 @@
         <v>2024</v>
       </c>
       <c r="C90">
-        <v>104.1</v>
+        <v>74.430000000000007</v>
       </c>
       <c r="D90">
-        <v>156.66999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="E90">
-        <v>3.76</v>
+        <v>1.7</v>
       </c>
       <c r="F90">
-        <v>0.91</v>
+        <v>2.75</v>
       </c>
       <c r="G90">
-        <v>14.35</v>
+        <v>20.03</v>
       </c>
       <c r="H90">
-        <v>24.58</v>
+        <v>24.25</v>
       </c>
       <c r="I90">
-        <v>281.51</v>
+        <v>123.84</v>
       </c>
       <c r="J90">
-        <v>3.7999999999999999E-2</v>
+        <v>16.524000000000001</v>
       </c>
       <c r="K90">
-        <v>0.56200000000000006</v>
+        <v>17.977</v>
       </c>
       <c r="L90">
-        <v>7.3999999999999996E-2</v>
+        <v>13.765000000000001</v>
       </c>
       <c r="M90">
-        <v>0.48799999999999999</v>
+        <v>4.2119999999999997</v>
       </c>
     </row>
   </sheetData>
@@ -35694,7 +35694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{919666AF-7698-471E-8633-8BE2CEAC314E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C333B76-6CB4-4348-A9F4-2A452963EE96}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -35813,7 +35813,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>86.65</v>
+        <v>317.63</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -35831,7 +35831,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.0209999999999999</v>
+        <v>6.9870000000000001</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -35846,7 +35846,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0.98399999999999999</v>
+        <v>7.181</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -35897,31 +35897,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>86.65</v>
+        <v>317.63</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>90.982500000000016</v>
+        <v>333.51150000000001</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>101.3805</v>
+        <v>371.62709999999998</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>111.77850000000001</v>
+        <v>409.74270000000001</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>123.04300000000001</v>
+        <v>451.03459999999995</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>137.77350000000001</v>
+        <v>505.0317</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>149.90450000000001</v>
+        <v>549.49990000000003</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -35960,7 +35960,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=BEL</v>
+        <v>~TFM_INS-TS: region=GBR</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -36124,31 +36124,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>32.060500000000005</v>
+        <v>117.5231</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>31.843875000000004</v>
+        <v>116.72902499999999</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>34.469370000000005</v>
+        <v>126.35321400000001</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>36.886905000000006</v>
+        <v>135.215091</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>36.9129</v>
+        <v>135.31037999999998</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>39.954315000000001</v>
+        <v>146.459193</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>44.971350000000001</v>
+        <v>164.84997000000001</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -36191,31 +36191,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>51.1235</v>
+        <v>187.40169999999998</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>53.679675000000003</v>
+        <v>196.77178499999999</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>59.814494999999994</v>
+        <v>219.25998899999999</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>64.831530000000001</v>
+        <v>237.650766</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>71.364940000000004</v>
+        <v>261.60006799999996</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>77.153160000000014</v>
+        <v>282.81775200000004</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>80.948430000000016</v>
+        <v>296.72994600000004</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -36258,31 +36258,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>2.5994999999999999</v>
+        <v>9.5289000000000001</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -36297,31 +36297,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>0.86650000000000205</v>
+        <v>3.1762999999999693</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>2.8594500000000096</v>
+        <v>10.48178999999999</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>4.4971350000000001</v>
+        <v>16.484996999999964</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>7.4605650000000026</v>
+        <v>27.347942999999987</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>12.165660000000003</v>
+        <v>44.595251999999959</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>18.066524999999984</v>
+        <v>66.22585499999991</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>21.385220000000004</v>
+        <v>78.391083999999978</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -36333,31 +36333,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>4.0209999999999999</v>
+        <v>6.9870000000000001</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>3.9405799999999997</v>
+        <v>6.8472600000000003</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>3.8601599999999996</v>
+        <v>6.7075199999999997</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>3.6993200000000002</v>
+        <v>6.4280400000000002</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>3.37764</v>
+        <v>5.8690800000000003</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>3.3374299999999999</v>
+        <v>5.7992099999999995</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>3.2168000000000001</v>
+        <v>5.5896000000000008</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -36369,31 +36369,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>0.98399999999999999</v>
+        <v>7.181</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>0.96431999999999995</v>
+        <v>7.0373799999999997</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>0.94463999999999992</v>
+        <v>6.8937599999999994</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>0.90527999999999997</v>
+        <v>6.6065200000000006</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>0.82655999999999996</v>
+        <v>6.0320399999999994</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>0.81672</v>
+        <v>5.9602300000000001</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>0.78720000000000001</v>
+        <v>5.7448000000000006</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -36468,7 +36468,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=BEL</v>
+        <v>~TFM_INS-TS: region=GBR</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -36513,14 +36513,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>16.350000000000001</v>
+        <v>15.51</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>16.350000000000001</v>
+        <v>15.51</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -36537,14 +36537,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>23.88</v>
+        <v>20.82</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>23.88</v>
+        <v>20.82</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -36699,7 +36699,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=BEL; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=GBR; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -36753,39 +36753,39 @@
       </c>
       <c r="D47">
         <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
-        <v>35.1</v>
+        <v>33.4</v>
       </c>
       <c r="E47">
         <f t="shared" si="9"/>
-        <v>37.557000000000002</v>
+        <v>35.738</v>
       </c>
       <c r="F47">
         <f t="shared" si="9"/>
-        <v>43.524000000000001</v>
+        <v>41.415999999999997</v>
       </c>
       <c r="G47">
         <f t="shared" si="9"/>
-        <v>40.365000000000002</v>
+        <v>38.409999999999997</v>
       </c>
       <c r="H47">
         <f t="shared" si="9"/>
-        <v>43.875</v>
+        <v>41.75</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>41.067</v>
+        <v>39.077999999999996</v>
       </c>
       <c r="J47">
         <f t="shared" si="9"/>
-        <v>47.034000000000006</v>
+        <v>44.756</v>
       </c>
       <c r="M47">
         <f>HLOOKUP($B47&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>29.1</v>
+        <v>27.4</v>
       </c>
       <c r="N47">
         <f>HLOOKUP($B47&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>41.1</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.45">
@@ -36936,13 +36936,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -36956,13 +36956,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
@@ -36977,7 +36977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE723EB7-B1EA-4CBD-938C-6E35FF5F4979}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F80FC7-3021-478E-95CD-6D59871A7C97}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37096,7 +37096,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>317.63</v>
+        <v>86.65</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -37114,7 +37114,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>6.9870000000000001</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -37129,7 +37129,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>7.181</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -37180,31 +37180,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>317.63</v>
+        <v>86.65</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>333.51150000000001</v>
+        <v>90.982500000000016</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>371.62709999999998</v>
+        <v>101.3805</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>409.74270000000001</v>
+        <v>111.77850000000001</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>451.03459999999995</v>
+        <v>123.04300000000001</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>505.0317</v>
+        <v>137.77350000000001</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>549.49990000000003</v>
+        <v>149.90450000000001</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -37243,7 +37243,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=GBR</v>
+        <v>~TFM_INS-TS: region=BEL</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -37407,31 +37407,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>117.5231</v>
+        <v>32.060500000000005</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>116.72902499999999</v>
+        <v>31.843875000000004</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>126.35321400000001</v>
+        <v>34.469370000000005</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>135.215091</v>
+        <v>36.886905000000006</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>135.31037999999998</v>
+        <v>36.9129</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>146.459193</v>
+        <v>39.954315000000001</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>164.84997000000001</v>
+        <v>44.971350000000001</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -37474,31 +37474,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>187.40169999999998</v>
+        <v>51.1235</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>196.77178499999999</v>
+        <v>53.679675000000003</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>219.25998899999999</v>
+        <v>59.814494999999994</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>237.650766</v>
+        <v>64.831530000000001</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>261.60006799999996</v>
+        <v>71.364940000000004</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>282.81775200000004</v>
+        <v>77.153160000000014</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>296.72994600000004</v>
+        <v>80.948430000000016</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -37541,31 +37541,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>9.5289000000000001</v>
+        <v>2.5994999999999999</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -37580,31 +37580,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>3.1762999999999693</v>
+        <v>0.86650000000000205</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>10.48178999999999</v>
+        <v>2.8594500000000096</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>16.484996999999964</v>
+        <v>4.4971350000000001</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>27.347942999999987</v>
+        <v>7.4605650000000026</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>44.595251999999959</v>
+        <v>12.165660000000003</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>66.22585499999991</v>
+        <v>18.066524999999984</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>78.391083999999978</v>
+        <v>21.385220000000004</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -37616,31 +37616,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>6.9870000000000001</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>6.8472600000000003</v>
+        <v>3.9405799999999997</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>6.7075199999999997</v>
+        <v>3.8601599999999996</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>6.4280400000000002</v>
+        <v>3.6993200000000002</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>5.8690800000000003</v>
+        <v>3.37764</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>5.7992099999999995</v>
+        <v>3.3374299999999999</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>5.5896000000000008</v>
+        <v>3.2168000000000001</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -37652,31 +37652,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>7.181</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>7.0373799999999997</v>
+        <v>0.96431999999999995</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>6.8937599999999994</v>
+        <v>0.94463999999999992</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>6.6065200000000006</v>
+        <v>0.90527999999999997</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>6.0320399999999994</v>
+        <v>0.82655999999999996</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>5.9602300000000001</v>
+        <v>0.81672</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>5.7448000000000006</v>
+        <v>0.78720000000000001</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -37751,7 +37751,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=GBR</v>
+        <v>~TFM_INS-TS: region=BEL</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -37796,14 +37796,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>15.51</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>15.51</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -37820,14 +37820,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>20.82</v>
+        <v>23.88</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>20.82</v>
+        <v>23.88</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -37982,7 +37982,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=GBR; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=BEL; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -38036,39 +38036,39 @@
       </c>
       <c r="D47">
         <f t="shared" ref="D47:J50" si="9">AVERAGE($M47:$N47)*D39</f>
-        <v>33.4</v>
+        <v>35.1</v>
       </c>
       <c r="E47">
         <f t="shared" si="9"/>
-        <v>35.738</v>
+        <v>37.557000000000002</v>
       </c>
       <c r="F47">
         <f t="shared" si="9"/>
-        <v>41.415999999999997</v>
+        <v>43.524000000000001</v>
       </c>
       <c r="G47">
         <f t="shared" si="9"/>
-        <v>38.409999999999997</v>
+        <v>40.365000000000002</v>
       </c>
       <c r="H47">
         <f t="shared" si="9"/>
-        <v>41.75</v>
+        <v>43.875</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>39.077999999999996</v>
+        <v>41.067</v>
       </c>
       <c r="J47">
         <f t="shared" si="9"/>
-        <v>44.756</v>
+        <v>47.034000000000006</v>
       </c>
       <c r="M47">
         <f>HLOOKUP($B47&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>27.4</v>
+        <v>29.1</v>
       </c>
       <c r="N47">
         <f>HLOOKUP($B47&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>39.4</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.45">
@@ -38219,13 +38219,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -38239,13 +38239,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
@@ -38260,7 +38260,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7344597D-4AE9-4376-8101-2564302C7890}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFDE922C-FFE7-4B17-866D-CC127767DB8D}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -38379,7 +38379,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>117.29999999999998</v>
+        <v>545.74</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -38397,7 +38397,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>14.882</v>
+        <v>45.581000000000003</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -38412,7 +38412,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.665</v>
+        <v>57.588000000000001</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -38463,31 +38463,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>117.29999999999998</v>
+        <v>545.74</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>123.16499999999999</v>
+        <v>573.02700000000004</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>137.24099999999999</v>
+        <v>638.51580000000001</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>151.31699999999998</v>
+        <v>704.00459999999998</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>166.56599999999997</v>
+        <v>774.95079999999996</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>186.50699999999998</v>
+        <v>867.72660000000008</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>202.92899999999997</v>
+        <v>944.13020000000006</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -38526,7 +38526,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=NLD</v>
+        <v>~TFM_INS-TS: region=DEU</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -38690,31 +38690,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>43.400999999999996</v>
+        <v>201.9238</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>43.107749999999996</v>
+        <v>200.55945</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>46.661940000000001</v>
+        <v>217.09537200000003</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>49.934609999999992</v>
+        <v>232.321518</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>49.969799999999992</v>
+        <v>232.48523999999998</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>54.087029999999992</v>
+        <v>251.640714</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>60.878699999999988</v>
+        <v>283.23905999999999</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -38757,31 +38757,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>69.206999999999979</v>
+        <v>321.98660000000001</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>72.667349999999985</v>
+        <v>338.08593000000002</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>80.972189999999983</v>
+        <v>376.72432199999997</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>87.76385999999998</v>
+        <v>408.32266799999996</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>96.608279999999979</v>
+        <v>449.47146399999997</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>104.44391999999999</v>
+        <v>485.92689600000011</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>109.58166</v>
+        <v>509.83030800000006</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -38824,31 +38824,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>3.5189999999999992</v>
+        <v>16.372199999999999</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -38863,31 +38863,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>1.1730000000000018</v>
+        <v>5.4574000000000069</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>3.870900000000006</v>
+        <v>18.009419999999977</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>6.0878700000000094</v>
+        <v>28.323905999999965</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>10.099529999999987</v>
+        <v>46.988213999999971</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>16.468919999999997</v>
+        <v>76.621895999999992</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>24.457049999999981</v>
+        <v>113.78679</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>28.949639999999988</v>
+        <v>134.68863199999998</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -38899,31 +38899,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>14.882</v>
+        <v>45.581000000000003</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>14.58436</v>
+        <v>44.669380000000004</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>14.286719999999999</v>
+        <v>43.757760000000005</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>13.69144</v>
+        <v>41.934520000000006</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>12.500879999999999</v>
+        <v>38.288040000000002</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>12.35206</v>
+        <v>37.832230000000003</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>11.9056</v>
+        <v>36.464800000000004</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -38935,31 +38935,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>4.665</v>
+        <v>57.588000000000001</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>4.5716999999999999</v>
+        <v>56.436239999999998</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>4.4783999999999997</v>
+        <v>55.284480000000002</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>4.2918000000000003</v>
+        <v>52.980960000000003</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>3.9186000000000001</v>
+        <v>48.373919999999998</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>3.87195</v>
+        <v>47.79804</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>3.7320000000000002</v>
+        <v>46.070400000000006</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -39034,7 +39034,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=NLD</v>
+        <v>~TFM_INS-TS: region=DEU</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -39079,14 +39079,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>18.54</v>
+        <v>49.33</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>18.54</v>
+        <v>49.33</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -39103,14 +39103,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>22.81</v>
+        <v>76.59</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>22.81</v>
+        <v>76.59</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -39265,7 +39265,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=NLD; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=DEU; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -39454,19 +39454,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -39502,13 +39502,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>0.64</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="D56">
-        <v>0.7</v>
+        <v>14.914999999999999</v>
       </c>
       <c r="E56">
-        <v>0.7</v>
+        <v>15.615</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -39522,13 +39522,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="D57">
-        <v>0.7</v>
+        <v>10.1</v>
       </c>
       <c r="E57">
-        <v>0.7</v>
+        <v>10.1</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>
@@ -39543,7 +39543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A86505-FFD5-4EF0-B1F7-8BFB16D4EAE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF4C40E-FB55-4D60-B3BC-A6C18806AEAE}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -39662,7 +39662,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>545.74</v>
+        <v>65.39</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -39680,7 +39680,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>45.581000000000003</v>
+        <v>2.5449999999999999</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -39695,7 +39695,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>57.588000000000001</v>
+        <v>4.4509999999999996</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -39746,31 +39746,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>545.74</v>
+        <v>65.39</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>573.02700000000004</v>
+        <v>68.659500000000008</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>638.51580000000001</v>
+        <v>76.506299999999996</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>704.00459999999998</v>
+        <v>84.353099999999998</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>774.95079999999996</v>
+        <v>92.853799999999993</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>867.72660000000008</v>
+        <v>103.9701</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>944.13020000000006</v>
+        <v>113.1247</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -39809,7 +39809,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=DEU</v>
+        <v>~TFM_INS-TS: region=CHE</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -39973,31 +39973,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>201.9238</v>
+        <v>24.194299999999998</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>200.55945</v>
+        <v>24.030825</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>217.09537200000003</v>
+        <v>26.012142000000001</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>232.321518</v>
+        <v>27.836523</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>232.48523999999998</v>
+        <v>27.856139999999996</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>251.640714</v>
+        <v>30.151328999999997</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>283.23905999999999</v>
+        <v>33.93741</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -40040,31 +40040,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>321.98660000000001</v>
+        <v>38.580100000000002</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>338.08593000000002</v>
+        <v>40.509105000000005</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>376.72432199999997</v>
+        <v>45.138716999999993</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>408.32266799999996</v>
+        <v>48.924797999999996</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>449.47146399999997</v>
+        <v>53.855203999999993</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>485.92689600000011</v>
+        <v>58.223256000000006</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>509.83030800000006</v>
+        <v>61.08733800000001</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -40107,31 +40107,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>16.372199999999999</v>
+        <v>1.9617</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -40146,31 +40146,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>5.4574000000000069</v>
+        <v>0.65390000000000725</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>18.009419999999977</v>
+        <v>2.1578700000000168</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>28.323905999999965</v>
+        <v>3.3937410000000057</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>46.988213999999971</v>
+        <v>5.6300790000000092</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>76.621895999999992</v>
+        <v>9.1807560000000024</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>113.78679</v>
+        <v>13.633815000000013</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>134.68863199999998</v>
+        <v>16.138251999999994</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -40182,31 +40182,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>45.581000000000003</v>
+        <v>2.5449999999999999</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>44.669380000000004</v>
+        <v>2.4941</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>43.757760000000005</v>
+        <v>2.4432</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>41.934520000000006</v>
+        <v>2.3414000000000001</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>38.288040000000002</v>
+        <v>2.1377999999999999</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>37.832230000000003</v>
+        <v>2.1123499999999997</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>36.464800000000004</v>
+        <v>2.036</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -40218,31 +40218,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>57.588000000000001</v>
+        <v>4.4509999999999996</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>56.436239999999998</v>
+        <v>4.36198</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>55.284480000000002</v>
+        <v>4.2729599999999994</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>52.980960000000003</v>
+        <v>4.0949200000000001</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>48.373919999999998</v>
+        <v>3.7388399999999997</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>47.79804</v>
+        <v>3.6943299999999994</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>46.070400000000006</v>
+        <v>3.5608</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -40317,7 +40317,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=DEU</v>
+        <v>~TFM_INS-TS: region=CHE</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -40362,14 +40362,14 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>49.33</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
       </c>
       <c r="O30" s="3">
         <f>L30</f>
-        <v>49.33</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -40386,14 +40386,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>76.59</v>
+        <v>29.73</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>ABS(L31)</f>
-        <v>76.59</v>
+        <v>29.73</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -40548,7 +40548,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=DEU; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=CHE; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -40647,39 +40647,39 @@
       </c>
       <c r="D48">
         <f t="shared" si="9"/>
-        <v>15.2</v>
+        <v>16.75</v>
       </c>
       <c r="E48">
         <f t="shared" si="9"/>
-        <v>15.504</v>
+        <v>17.085000000000001</v>
       </c>
       <c r="F48">
         <f t="shared" si="9"/>
-        <v>16.111999999999998</v>
+        <v>17.755000000000003</v>
       </c>
       <c r="G48">
         <f t="shared" si="9"/>
-        <v>16.263999999999999</v>
+        <v>17.922499999999999</v>
       </c>
       <c r="H48">
         <f t="shared" si="9"/>
-        <v>16.416</v>
+        <v>18.09</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>16.72</v>
+        <v>18.425000000000001</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>17.024000000000001</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="M48">
         <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
       <c r="N48">
         <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
@@ -40692,39 +40692,39 @@
       </c>
       <c r="D49">
         <f t="shared" si="9"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <f t="shared" si="9"/>
-        <v>53.53</v>
+        <v>55.55</v>
       </c>
       <c r="F49">
         <f t="shared" si="9"/>
-        <v>58.830000000000005</v>
+        <v>61.050000000000004</v>
       </c>
       <c r="G49">
         <f t="shared" si="9"/>
-        <v>53.53</v>
+        <v>55.55</v>
       </c>
       <c r="H49">
         <f t="shared" si="9"/>
-        <v>53.53</v>
+        <v>55.55</v>
       </c>
       <c r="I49">
         <f t="shared" si="9"/>
-        <v>55.120000000000005</v>
+        <v>57.2</v>
       </c>
       <c r="J49">
         <f t="shared" si="9"/>
-        <v>60.419999999999995</v>
+        <v>62.699999999999996</v>
       </c>
       <c r="M49">
         <f>HLOOKUP($B49&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N49">
         <f>HLOOKUP($B49&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
@@ -40737,19 +40737,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -40785,13 +40785,13 @@
         <v>107</v>
       </c>
       <c r="C56">
-        <v>8.3149999999999995</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>14.914999999999999</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>15.615</v>
+        <v>0</v>
       </c>
       <c r="F56" t="s">
         <v>108</v>
@@ -40805,13 +40805,13 @@
         <v>107</v>
       </c>
       <c r="C57">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="D57">
-        <v>10.1</v>
+        <v>1.2</v>
       </c>
       <c r="E57">
-        <v>10.1</v>
+        <v>1.2</v>
       </c>
       <c r="F57" t="s">
         <v>108</v>

--- a/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_CEA_8C\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A9E3BC-2076-43FD-85DB-BE72D8108AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DDDE0B6-A05E-4CC7-A1A0-F759BB689853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17596" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="12773" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -19,24 +19,24 @@
     <sheet name="iea_data" sheetId="2" r:id="rId4"/>
     <sheet name="ar6_r10" sheetId="3" r:id="rId5"/>
     <sheet name="Veda_GBR" sheetId="6" r:id="rId6"/>
-    <sheet name="Veda_BEL" sheetId="7" r:id="rId7"/>
-    <sheet name="Veda_DEU" sheetId="8" r:id="rId8"/>
-    <sheet name="Veda_CHE" sheetId="9" r:id="rId9"/>
-    <sheet name="Veda_ITA" sheetId="10" r:id="rId10"/>
-    <sheet name="Veda_ESP" sheetId="11" r:id="rId11"/>
-    <sheet name="Veda_NLD" sheetId="12" r:id="rId12"/>
+    <sheet name="Veda_NLD" sheetId="7" r:id="rId7"/>
+    <sheet name="Veda_BEL" sheetId="8" r:id="rId8"/>
+    <sheet name="Veda_DEU" sheetId="9" r:id="rId9"/>
+    <sheet name="Veda_CHE" sheetId="10" r:id="rId10"/>
+    <sheet name="Veda_ITA" sheetId="11" r:id="rId11"/>
+    <sheet name="Veda_ESP" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ar6_r10!$A$10:$M$395</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">controller!$B$17:$E$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Veda_BEL!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Veda_CHE!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Veda_DEU!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Veda_ESP!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Veda_BEL!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Veda_CHE!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Veda_DEU!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Veda_ESP!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Veda_FRA!#REF!</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Veda_GBR!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Veda_ITA!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Veda_NLD!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Veda_ITA!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Veda_NLD!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +97,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{31D0649A-C783-4615-B84E-5BB93967A279}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{5A9C7618-E1A6-4757-86D2-45C20155C224}">
       <text>
         <r>
           <rPr>
@@ -133,7 +133,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{AF5E831E-E654-4648-A8CD-3AA35C4A1EAC}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{88664B10-27D9-448B-8E53-5663524AA164}">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{C1778D0A-2F14-4FCD-B77C-12349E7F4D3B}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{8EAE00FE-4D99-49FC-B37A-AE04F080DA17}">
       <text>
         <r>
           <rPr>
@@ -205,7 +205,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{82198A64-7B01-4F36-A4E6-89DA0D1FD15E}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{05BE2A54-CEBF-48A5-924C-27365F85976E}">
       <text>
         <r>
           <rPr>
@@ -241,7 +241,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{1ECEF842-4662-40DE-A390-0F051E7818FE}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{C34CDB5E-682A-4892-93F6-E065865B9BBB}">
       <text>
         <r>
           <rPr>
@@ -277,7 +277,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{A66864E9-BF18-4AB7-9E10-EB2F66238E32}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{38F21F7C-32CF-40FE-BFEE-774980D6AE80}">
       <text>
         <r>
           <rPr>
@@ -313,7 +313,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{9BF66D26-4647-42A9-A9A0-FF75FE1C5E50}">
+    <comment ref="AH8" authorId="0" shapeId="0" xr:uid="{3B604C3E-1260-4A54-9203-E454BF2E651B}">
       <text>
         <r>
           <rPr>
@@ -673,6 +673,9 @@
     <t>GBR</t>
   </si>
   <si>
+    <t>NLD</t>
+  </si>
+  <si>
     <t>BEL</t>
   </si>
   <si>
@@ -688,13 +691,13 @@
     <t>ESP</t>
   </si>
   <si>
-    <t>NLD</t>
-  </si>
-  <si>
     <t>UP</t>
   </si>
   <si>
     <t>~tfm_ins-ts: region=GBR</t>
+  </si>
+  <si>
+    <t>~tfm_ins-ts: region=NLD</t>
   </si>
   <si>
     <t>~tfm_ins-ts: region=BEL</t>
@@ -712,10 +715,10 @@
     <t>~tfm_ins-ts: region=ESP</t>
   </si>
   <si>
-    <t>~tfm_ins-ts: region=NLD</t>
+    <t>NBP gas hub, Drax biomass plants</t>
   </si>
   <si>
-    <t>NBP gas hub, Drax biomass plants</t>
+    <t>TTF hub, major pellet importer</t>
   </si>
   <si>
     <t>Zeebrugge LNG, pellet imports</t>
@@ -731,9 +734,6 @@
   </si>
   <si>
     <t>Iberian market, olive &amp; agricultural waste</t>
-  </si>
-  <si>
-    <t>TTF hub, major pellet importer</t>
   </si>
 </sst>
 </file>
@@ -1195,25 +1195,25 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>469.59</c:v>
+                  <c:v>522.03</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>493.06950000000001</c:v>
+                  <c:v>548.13149999999996</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>549.42029999999988</c:v>
+                  <c:v>610.77509999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>605.77109999999993</c:v>
+                  <c:v>673.41869999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>666.81779999999992</c:v>
+                  <c:v>741.28259999999989</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>746.6481</c:v>
+                  <c:v>830.02769999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>812.39069999999992</c:v>
+                  <c:v>903.11189999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1455,7 +1455,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_CHE!$D$18:$J$18</c:f>
+              <c:f>Veda_DEU!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1485,7 +1485,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_CHE!$D$26:$J$26</c:f>
+              <c:f>Veda_DEU!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1516,7 +1516,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3F35-4A48-B990-8608609C2C23}"/>
+              <c16:uniqueId val="{00000000-1678-4E64-B5A7-0927D948C7BF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1750,7 +1750,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ITA!$O$18:$U$18</c:f>
+              <c:f>Veda_CHE!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1780,30 +1780,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ITA!$O$15:$U$15</c:f>
+              <c:f>Veda_CHE!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>282.07</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>296.17349999999999</c:v>
+                  <c:v>65.100000000000009</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>330.02189999999996</c:v>
+                  <c:v>72.539999999999992</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>363.87029999999999</c:v>
+                  <c:v>79.98</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>400.53939999999994</c:v>
+                  <c:v>88.039999999999992</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>448.49130000000002</c:v>
+                  <c:v>98.58</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>487.98109999999997</c:v>
+                  <c:v>107.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1811,7 +1811,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EF99-4D59-9B84-38702C5E24C4}"/>
+              <c16:uniqueId val="{00000000-4DBE-4BCD-9EBE-A57F2E76EFD6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2045,7 +2045,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ITA!$D$18:$J$18</c:f>
+              <c:f>Veda_CHE!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2075,7 +2075,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ITA!$D$26:$J$26</c:f>
+              <c:f>Veda_CHE!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2106,7 +2106,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DA9A-498F-A9D4-744554727416}"/>
+              <c16:uniqueId val="{00000000-D0CF-4266-9F7A-45337AA01506}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2340,7 +2340,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ESP!$O$18:$U$18</c:f>
+              <c:f>Veda_ITA!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2370,30 +2370,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ESP!$O$15:$U$15</c:f>
+              <c:f>Veda_ITA!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>287.94</c:v>
+                  <c:v>282.07</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>302.33699999999999</c:v>
+                  <c:v>296.17349999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>336.88979999999998</c:v>
+                  <c:v>330.02189999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>371.44260000000003</c:v>
+                  <c:v>363.87029999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>408.87479999999999</c:v>
+                  <c:v>400.53939999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>457.82460000000003</c:v>
+                  <c:v>448.49130000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>498.13619999999997</c:v>
+                  <c:v>487.98109999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2401,7 +2401,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CBFF-4EEC-B152-C956601E2D4A}"/>
+              <c16:uniqueId val="{00000000-D505-46CF-B337-A8DE2D860EF2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2635,7 +2635,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_ESP!$D$18:$J$18</c:f>
+              <c:f>Veda_ITA!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2665,7 +2665,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_ESP!$D$26:$J$26</c:f>
+              <c:f>Veda_ITA!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2696,7 +2696,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FE2A-47C5-8636-D02EE96C69BB}"/>
+              <c16:uniqueId val="{00000000-0FB7-434C-9248-0AD262E60248}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2930,7 +2930,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_NLD!$O$18:$U$18</c:f>
+              <c:f>Veda_ESP!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2960,30 +2960,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_NLD!$O$15:$U$15</c:f>
+              <c:f>Veda_ESP!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>121.57</c:v>
+                  <c:v>287.94</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>127.6485</c:v>
+                  <c:v>302.33699999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>142.23689999999999</c:v>
+                  <c:v>336.88979999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>156.8253</c:v>
+                  <c:v>371.44260000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>172.62939999999998</c:v>
+                  <c:v>408.87479999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>193.2963</c:v>
+                  <c:v>457.82460000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>210.31609999999998</c:v>
+                  <c:v>498.13619999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2991,7 +2991,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C417-485B-8825-98059D7F9EF9}"/>
+              <c16:uniqueId val="{00000000-D2C3-4338-86BC-9FDE8DCF4E9A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3225,7 +3225,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_NLD!$D$18:$J$18</c:f>
+              <c:f>Veda_ESP!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3255,7 +3255,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_NLD!$D$26:$J$26</c:f>
+              <c:f>Veda_ESP!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -3286,7 +3286,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5BFB-41DC-9704-1494F935398B}"/>
+              <c16:uniqueId val="{00000000-CBB9-4E3B-9674-08851765AC6E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3869,7 +3869,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-47B0-4FF2-950C-4133F79810BF}"/>
+              <c16:uniqueId val="{00000000-CF62-45DB-9B89-76785A03A8CE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4164,7 +4164,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1FFA-4FDC-BBAD-1BDE318F6199}"/>
+              <c16:uniqueId val="{00000000-C798-4D4F-A361-00DC26D1F80D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4398,7 +4398,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_BEL!$O$18:$U$18</c:f>
+              <c:f>Veda_NLD!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4428,30 +4428,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_BEL!$O$15:$U$15</c:f>
+              <c:f>Veda_NLD!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>94.18</c:v>
+                  <c:v>121.57</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>98.88900000000001</c:v>
+                  <c:v>127.6485</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>110.1906</c:v>
+                  <c:v>142.23689999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>121.49220000000001</c:v>
+                  <c:v>156.8253</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>133.73560000000001</c:v>
+                  <c:v>172.62939999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>149.74620000000002</c:v>
+                  <c:v>193.2963</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>162.9314</c:v>
+                  <c:v>210.31609999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4459,7 +4459,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7DFF-4DCF-8A3F-1307FFA64517}"/>
+              <c16:uniqueId val="{00000000-3B87-4F62-8887-DD5C3BD68D1C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4693,7 +4693,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_BEL!$D$18:$J$18</c:f>
+              <c:f>Veda_NLD!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4723,7 +4723,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_BEL!$D$26:$J$26</c:f>
+              <c:f>Veda_NLD!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -4754,7 +4754,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B72A-40FF-8516-F1B921827BF3}"/>
+              <c16:uniqueId val="{00000000-3F48-4886-850E-CB16378132BC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4988,7 +4988,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_DEU!$O$18:$U$18</c:f>
+              <c:f>Veda_BEL!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5018,30 +5018,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_DEU!$O$15:$U$15</c:f>
+              <c:f>Veda_BEL!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>573</c:v>
+                  <c:v>94.18</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>601.65</c:v>
+                  <c:v>98.88900000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>670.41</c:v>
+                  <c:v>110.1906</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>739.17000000000007</c:v>
+                  <c:v>121.49220000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>813.66</c:v>
+                  <c:v>133.73560000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>911.07</c:v>
+                  <c:v>149.74620000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>991.29</c:v>
+                  <c:v>162.9314</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5049,7 +5049,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4EF6-4201-98C6-D25A43BE4E87}"/>
+              <c16:uniqueId val="{00000000-06BB-4A80-AEBC-77F86800CD45}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5283,7 +5283,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_DEU!$D$18:$J$18</c:f>
+              <c:f>Veda_BEL!$D$18:$J$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5313,7 +5313,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_DEU!$D$26:$J$26</c:f>
+              <c:f>Veda_BEL!$D$26:$J$26</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5344,7 +5344,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EAFA-4435-8678-618E209B22A4}"/>
+              <c16:uniqueId val="{00000000-4BCC-4D9F-8A43-7F5D6DB304F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5578,7 +5578,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>Veda_CHE!$O$18:$U$18</c:f>
+              <c:f>Veda_DEU!$O$18:$U$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5608,30 +5608,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Veda_CHE!$O$15:$U$15</c:f>
+              <c:f>Veda_DEU!$O$15:$U$15</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>62</c:v>
+                  <c:v>573</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65.100000000000009</c:v>
+                  <c:v>601.65</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72.539999999999992</c:v>
+                  <c:v>670.41</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>79.98</c:v>
+                  <c:v>739.17000000000007</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>88.039999999999992</c:v>
+                  <c:v>813.66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>98.58</c:v>
+                  <c:v>911.07</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>107.26</c:v>
+                  <c:v>991.29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5639,7 +5639,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FDE8-495A-9C7E-0C4C5731C49D}"/>
+              <c16:uniqueId val="{00000000-981E-4556-9C07-17AD59D9D09D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5858,7 +5858,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9357EAFD-E7C1-4981-82DE-4DB5FB51FD0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CAFF327-ECA5-47CD-AE72-06F9F78B06CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5896,7 +5896,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B7A35E4-11E5-4CF0-A015-C4CECE7F504A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B4D7BF4-1EE6-4F10-86BD-3A16AAEE1F9D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5939,7 +5939,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6177C510-60A1-438E-BB20-6A70981E82FF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7899CC7C-8860-449C-9DF6-3D7AC2C71E74}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5977,7 +5977,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09E566A0-EB7E-4C4B-8565-A2FC01372470}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFFF5A90-1CDB-4232-8F4A-D7EB348063A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10235,7 +10235,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D876028-5711-4126-A2AF-69F9C94A5A21}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{373A2169-3DA7-42F6-80B2-A1979C6D494C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10273,7 +10273,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60AAA62E-C429-44E2-965C-31A961398BF6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E876458D-29F1-4610-96F1-38F25FA6A30A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10316,7 +10316,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C05FA99-2C9E-4D9A-AACB-E660E87ECAC1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C41F1810-3F9A-435F-A847-430C86E61801}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10354,7 +10354,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A183F16-6DBE-45BA-B96B-7ACC7DFD4AFA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E53932F5-7262-4BAE-984A-8B2FD0DABE37}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10397,7 +10397,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28F71015-1AA8-4A45-934F-D5F6BCCF3A43}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02DECBD8-133A-46BF-B3ED-DABB5C3723FE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10435,7 +10435,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EB2117E-0C80-4752-BD20-DC1FA1B8D037}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC267C06-B8D3-490B-B967-5A56F0D16DD6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10478,7 +10478,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F4DD31A-D798-49F9-BB37-8A40BAAD5695}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{560B0C26-A178-4C1C-8E15-282E1464D9C4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10516,7 +10516,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8309ADD7-2EE5-4232-8976-88F9C24D0D48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97BE9E63-1CBD-426F-B4DF-E4BB3CED4BC9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10559,7 +10559,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA780505-5654-4FA8-B1CD-06E334618846}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F434969F-B569-4825-B448-2307DE2CF57B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10597,7 +10597,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5E1FF64-EE8C-40A6-ABAB-57DC51877EB5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22FB363D-941F-419C-9905-BD852A6E3265}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -11159,7 +11159,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF5039BE-8525-4D3E-8400-04D3F254B6F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64808D6C-D496-43B0-87D6-869E9894BDB4}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -11278,7 +11278,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>282.07</v>
+        <v>62</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -11296,7 +11296,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>6.5309999999999997</v>
+        <v>2.5449999999999999</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -11311,7 +11311,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>10.842000000000001</v>
+        <v>4.4509999999999996</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -11362,31 +11362,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>282.07</v>
+        <v>62</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>296.17349999999999</v>
+        <v>65.100000000000009</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>330.02189999999996</v>
+        <v>72.539999999999992</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>363.87029999999999</v>
+        <v>79.98</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>400.53939999999994</v>
+        <v>88.039999999999992</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>448.49130000000002</v>
+        <v>98.58</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>487.98109999999997</v>
+        <v>107.26</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -11425,7 +11425,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ITA</v>
+        <v>~TFM_INS-TS: region=CHE</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11589,31 +11589,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>104.3659</v>
+        <v>22.94</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>103.66072499999999</v>
+        <v>22.785</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>112.20744599999999</v>
+        <v>24.663599999999999</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>120.07719900000001</v>
+        <v>26.393400000000003</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>120.16181999999998</v>
+        <v>26.411999999999995</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>130.062477</v>
+        <v>28.588199999999997</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>146.39433</v>
+        <v>32.177999999999997</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -11656,31 +11656,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>166.42129999999997</v>
+        <v>36.58</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>174.74236499999998</v>
+        <v>38.409000000000006</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>194.71292099999997</v>
+        <v>42.798599999999993</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>211.04477399999999</v>
+        <v>46.388399999999997</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>232.31285199999996</v>
+        <v>51.063199999999995</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>251.15512800000005</v>
+        <v>55.204800000000006</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>263.509794</v>
+        <v>57.920400000000008</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -11723,31 +11723,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>8.4620999999999995</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -11762,31 +11762,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>2.820699999999988</v>
+        <v>0.62000000000000455</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>9.3083100000000059</v>
+        <v>2.0460000000000065</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>14.639432999999997</v>
+        <v>3.2177999999999969</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>24.28622699999994</v>
+        <v>5.3382000000000005</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>39.602627999999982</v>
+        <v>8.7048000000000059</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>58.811594999999954</v>
+        <v>12.926999999999992</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>69.614875999999924</v>
+        <v>15.301600000000008</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -11798,31 +11798,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>6.5309999999999997</v>
+        <v>2.5449999999999999</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>6.4003799999999993</v>
+        <v>2.4941</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>6.2697599999999998</v>
+        <v>2.4432</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>6.0085199999999999</v>
+        <v>2.3414000000000001</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>5.4860399999999991</v>
+        <v>2.1377999999999999</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>5.4207299999999998</v>
+        <v>2.1123499999999997</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>5.2248000000000001</v>
+        <v>2.036</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -11834,31 +11834,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>10.842000000000001</v>
+        <v>4.4509999999999996</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>10.625160000000001</v>
+        <v>4.36198</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>10.40832</v>
+        <v>4.2729599999999994</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>9.9746400000000008</v>
+        <v>4.0949200000000001</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>9.1072799999999994</v>
+        <v>3.7388399999999997</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>8.9988600000000005</v>
+        <v>3.6943299999999994</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>8.6736000000000004</v>
+        <v>3.5608</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -11933,7 +11933,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ITA</v>
+        <v>~TFM_INS-TS: region=CHE</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -11978,7 +11978,7 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>47.39</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -12001,7 +12001,7 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.4000000000000004</v>
+        <v>29.73</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -12162,7 +12162,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=ITA; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=CHE; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -12351,19 +12351,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -12399,13 +12399,13 @@
         <v>106</v>
       </c>
       <c r="C56">
-        <v>1.5049999999999999</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>2.5049999999999999</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="F56" t="s">
         <v>107</v>
@@ -12419,13 +12419,13 @@
         <v>106</v>
       </c>
       <c r="C57">
-        <v>1.125</v>
+        <v>1.2</v>
       </c>
       <c r="D57">
-        <v>1.375</v>
+        <v>1.2</v>
       </c>
       <c r="E57">
-        <v>2.875</v>
+        <v>1.2</v>
       </c>
       <c r="F57" t="s">
         <v>107</v>
@@ -12440,7 +12440,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B3B0EB0-EB70-4DA4-A54A-25900B71E6DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2048130B-5051-469D-A815-BB2809E7E5DE}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -12559,7 +12559,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>287.94</v>
+        <v>282.07</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -12577,7 +12577,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -12592,7 +12592,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0</v>
+        <v>10.842000000000001</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -12643,31 +12643,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>287.94</v>
+        <v>282.07</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>302.33699999999999</v>
+        <v>296.17349999999999</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>336.88979999999998</v>
+        <v>330.02189999999996</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>371.44260000000003</v>
+        <v>363.87029999999999</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>408.87479999999999</v>
+        <v>400.53939999999994</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>457.82460000000003</v>
+        <v>448.49130000000002</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>498.13619999999997</v>
+        <v>487.98109999999997</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -12706,7 +12706,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ESP</v>
+        <v>~TFM_INS-TS: region=ITA</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -12870,31 +12870,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>106.5378</v>
+        <v>104.3659</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>105.81795</v>
+        <v>103.66072499999999</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>114.54253199999999</v>
+        <v>112.20744599999999</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>122.57605800000002</v>
+        <v>120.07719900000001</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>122.66243999999999</v>
+        <v>120.16181999999998</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>132.76913400000001</v>
+        <v>130.062477</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>149.44085999999999</v>
+        <v>146.39433</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -12937,31 +12937,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>169.88459999999998</v>
+        <v>166.42129999999997</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>178.37882999999999</v>
+        <v>174.74236499999998</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>198.76498199999997</v>
+        <v>194.71292099999997</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>215.43670800000001</v>
+        <v>211.04477399999999</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>237.14738399999999</v>
+        <v>232.31285199999996</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>256.38177600000006</v>
+        <v>251.15512800000005</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>268.99354799999998</v>
+        <v>263.509794</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -13004,31 +13004,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>8.6381999999999994</v>
+        <v>8.4620999999999995</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -13043,31 +13043,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>2.8794000000000324</v>
+        <v>2.820699999999988</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>9.5020200000000159</v>
+        <v>9.3083100000000059</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>14.944086000000027</v>
+        <v>14.639432999999997</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>24.791633999999988</v>
+        <v>24.28622699999994</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>40.426776000000018</v>
+        <v>39.602627999999982</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>60.035489999999982</v>
+        <v>58.811594999999954</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>71.063592000000028</v>
+        <v>69.614875999999924</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -13079,31 +13079,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>0</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>0</v>
+        <v>6.4003799999999993</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>0</v>
+        <v>6.2697599999999998</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>0</v>
+        <v>6.0085199999999999</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.4860399999999991</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.4207299999999998</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5.2248000000000001</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -13115,31 +13115,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>0</v>
+        <v>10.842000000000001</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>0</v>
+        <v>10.625160000000001</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>0</v>
+        <v>10.40832</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9.9746400000000008</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>9.1072799999999994</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8.9988600000000005</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8.6736000000000004</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -13214,7 +13214,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=ESP</v>
+        <v>~TFM_INS-TS: region=ITA</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -13259,7 +13259,7 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>8.0299999999999994</v>
+        <v>47.39</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -13282,7 +13282,7 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>27.83</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -13443,7 +13443,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=ESP; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=ITA; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -13542,39 +13542,39 @@
       </c>
       <c r="D48">
         <f t="shared" si="9"/>
-        <v>15.2</v>
+        <v>16.75</v>
       </c>
       <c r="E48">
         <f t="shared" si="9"/>
-        <v>15.504</v>
+        <v>17.085000000000001</v>
       </c>
       <c r="F48">
         <f t="shared" si="9"/>
-        <v>16.111999999999998</v>
+        <v>17.755000000000003</v>
       </c>
       <c r="G48">
         <f t="shared" si="9"/>
-        <v>16.263999999999999</v>
+        <v>17.922499999999999</v>
       </c>
       <c r="H48">
         <f t="shared" si="9"/>
-        <v>16.416</v>
+        <v>18.09</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>16.72</v>
+        <v>18.425000000000001</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>17.024000000000001</v>
+        <v>18.760000000000002</v>
       </c>
       <c r="M48">
         <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
       <c r="N48">
         <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
@@ -13632,19 +13632,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -13680,13 +13680,13 @@
         <v>106</v>
       </c>
       <c r="C56">
-        <v>4.38</v>
+        <v>1.5049999999999999</v>
       </c>
       <c r="D56">
-        <v>5.0999999999999996</v>
+        <v>2.5049999999999999</v>
       </c>
       <c r="E56">
-        <v>5.75</v>
+        <v>3.93</v>
       </c>
       <c r="F56" t="s">
         <v>107</v>
@@ -13700,13 +13700,13 @@
         <v>106</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>2.875</v>
       </c>
       <c r="F57" t="s">
         <v>107</v>
@@ -13721,7 +13721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D31AC3-47CC-4DEE-919D-B61414D1ACCD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D9F19E-FCF7-4168-8DFE-81FD4146D3F8}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -13840,7 +13840,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>121.57</v>
+        <v>287.94</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -13858,7 +13858,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>14.882</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -13873,7 +13873,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.665</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -13924,31 +13924,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>121.57</v>
+        <v>287.94</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>127.6485</v>
+        <v>302.33699999999999</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>142.23689999999999</v>
+        <v>336.88979999999998</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>156.8253</v>
+        <v>371.44260000000003</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>172.62939999999998</v>
+        <v>408.87479999999999</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>193.2963</v>
+        <v>457.82460000000003</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>210.31609999999998</v>
+        <v>498.13619999999997</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -13987,7 +13987,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=NLD</v>
+        <v>~TFM_INS-TS: region=ESP</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -14151,31 +14151,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>44.980899999999998</v>
+        <v>106.5378</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>44.676974999999999</v>
+        <v>105.81795</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>48.360545999999999</v>
+        <v>114.54253199999999</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>51.752349000000002</v>
+        <v>122.57605800000002</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>51.788819999999994</v>
+        <v>122.66243999999999</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>56.055926999999997</v>
+        <v>132.76913400000001</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>63.094829999999988</v>
+        <v>149.44085999999999</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -14218,31 +14218,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>71.726299999999995</v>
+        <v>169.88459999999998</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>75.312614999999994</v>
+        <v>178.37882999999999</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>83.919770999999997</v>
+        <v>198.76498199999997</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>90.958673999999988</v>
+        <v>215.43670800000001</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>100.12505199999998</v>
+        <v>237.14738399999999</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>108.24592800000001</v>
+        <v>256.38177600000006</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>113.57069399999999</v>
+        <v>268.99354799999998</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -14285,31 +14285,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>3.6470999999999996</v>
+        <v>8.6381999999999994</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -14324,31 +14324,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>1.2156999999999982</v>
+        <v>2.8794000000000324</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>4.0118100000000112</v>
+        <v>9.5020200000000159</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>6.3094830000000002</v>
+        <v>14.944086000000027</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>10.467177000000021</v>
+        <v>24.791633999999988</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>17.068428000000011</v>
+        <v>40.426776000000018</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>25.347345000000018</v>
+        <v>60.035489999999982</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>30.003476000000006</v>
+        <v>71.063592000000028</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -14360,31 +14360,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>14.882</v>
+        <v>0</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>14.58436</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>14.286719999999999</v>
+        <v>0</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>13.69144</v>
+        <v>0</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>12.500879999999999</v>
+        <v>0</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>12.35206</v>
+        <v>0</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>11.9056</v>
+        <v>0</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -14396,31 +14396,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>4.665</v>
+        <v>0</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>4.5716999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>4.4783999999999997</v>
+        <v>0</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>4.2918000000000003</v>
+        <v>0</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>3.9186000000000001</v>
+        <v>0</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>3.87195</v>
+        <v>0</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>3.7320000000000002</v>
+        <v>0</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -14495,7 +14495,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=NLD</v>
+        <v>~TFM_INS-TS: region=ESP</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -14540,7 +14540,7 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>18.54</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -14563,7 +14563,7 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>22.81</v>
+        <v>27.83</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -14724,7 +14724,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=NLD; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=ESP; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -14868,39 +14868,39 @@
       </c>
       <c r="D49">
         <f t="shared" si="9"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E49">
         <f t="shared" si="9"/>
-        <v>53.53</v>
+        <v>55.55</v>
       </c>
       <c r="F49">
         <f t="shared" si="9"/>
-        <v>58.830000000000005</v>
+        <v>61.050000000000004</v>
       </c>
       <c r="G49">
         <f t="shared" si="9"/>
-        <v>53.53</v>
+        <v>55.55</v>
       </c>
       <c r="H49">
         <f t="shared" si="9"/>
-        <v>53.53</v>
+        <v>55.55</v>
       </c>
       <c r="I49">
         <f t="shared" si="9"/>
-        <v>55.120000000000005</v>
+        <v>57.2</v>
       </c>
       <c r="J49">
         <f t="shared" si="9"/>
-        <v>60.419999999999995</v>
+        <v>62.699999999999996</v>
       </c>
       <c r="M49">
         <f>HLOOKUP($B49&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N49">
         <f>HLOOKUP($B49&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
@@ -14913,19 +14913,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -14961,13 +14961,13 @@
         <v>106</v>
       </c>
       <c r="C56">
-        <v>0.64</v>
+        <v>4.38</v>
       </c>
       <c r="D56">
-        <v>0.7</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="E56">
-        <v>0.7</v>
+        <v>5.75</v>
       </c>
       <c r="F56" t="s">
         <v>107</v>
@@ -14981,13 +14981,13 @@
         <v>106</v>
       </c>
       <c r="C57">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F57" t="s">
         <v>107</v>
@@ -15121,7 +15121,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>469.59</v>
+        <v>522.03</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -15205,31 +15205,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>469.59</v>
+        <v>522.03</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>493.06950000000001</v>
+        <v>548.13149999999996</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>549.42029999999988</v>
+        <v>610.77509999999995</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>605.77109999999993</v>
+        <v>673.41869999999994</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>666.81779999999992</v>
+        <v>741.28259999999989</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>746.6481</v>
+        <v>830.02769999999998</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>812.39069999999992</v>
+        <v>903.11189999999999</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -15432,31 +15432,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>173.7483</v>
+        <v>193.15109999999999</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>172.57432499999999</v>
+        <v>191.84602499999997</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>186.80290199999996</v>
+        <v>207.663534</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>199.90446299999999</v>
+        <v>222.228171</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>200.04533999999998</v>
+        <v>222.38477999999995</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>216.52794899999998</v>
+        <v>240.70803299999997</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>243.71720999999997</v>
+        <v>270.93356999999997</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -15499,31 +15499,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>277.05809999999997</v>
+        <v>307.99769999999995</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>290.91100499999999</v>
+        <v>323.39758499999994</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>324.1579769999999</v>
+        <v>360.35730899999993</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>351.34723799999995</v>
+        <v>390.58284599999996</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>386.75432399999994</v>
+        <v>429.94390799999991</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>418.12293600000004</v>
+        <v>464.81551200000001</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>438.69097799999997</v>
+        <v>487.68042600000001</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -15566,31 +15566,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>14.087699999999998</v>
+        <v>15.660899999999998</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -15605,31 +15605,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>4.6959000000000515</v>
+        <v>5.2203000000000657</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>15.496470000000045</v>
+        <v>17.226990000000114</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>24.37172099999998</v>
+        <v>27.093357000000083</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>40.431698999999981</v>
+        <v>44.946782999999982</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>65.930435999999986</v>
+        <v>73.29301200000009</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>97.909514999999942</v>
+        <v>108.843255</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>115.894812</v>
+        <v>128.83700399999998</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -15827,7 +15827,7 @@
         <v>30</v>
       </c>
       <c r="O30" s="3">
-        <v>0</v>
+        <v>52.44</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -16450,10 +16450,10 @@
         <v>58</v>
       </c>
       <c r="H14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J14" t="s">
         <v>125</v>
@@ -16470,22 +16470,22 @@
         <v>41.1</v>
       </c>
       <c r="D15">
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="E15">
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
       <c r="F15">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G15">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H15">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I15">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
         <v>126</v>
@@ -16514,10 +16514,10 @@
         <v>60</v>
       </c>
       <c r="H16">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I16">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J16" t="s">
         <v>127</v>
@@ -16534,10 +16534,10 @@
         <v>41.1</v>
       </c>
       <c r="D17">
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
       <c r="E17">
-        <v>16.7</v>
+        <v>18.3</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -16546,10 +16546,10 @@
         <v>60</v>
       </c>
       <c r="H17">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J17" t="s">
         <v>128</v>
@@ -16572,16 +16572,16 @@
         <v>16.7</v>
       </c>
       <c r="F18">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G18">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H18">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I18">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
         <v>129</v>
@@ -17484,37 +17484,37 @@
         <v>2015</v>
       </c>
       <c r="C31">
-        <v>47.7</v>
+        <v>57.21</v>
       </c>
       <c r="D31">
-        <v>41.35</v>
+        <v>67.48</v>
       </c>
       <c r="E31">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="F31">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="G31">
-        <v>23.71</v>
+        <v>30.76</v>
       </c>
       <c r="H31">
-        <v>2.72</v>
+        <v>22.01</v>
       </c>
       <c r="I31">
-        <v>68.150000000000006</v>
+        <v>110.21</v>
       </c>
       <c r="J31">
-        <v>7.2930000000000001</v>
+        <v>29.603000000000002</v>
       </c>
       <c r="K31">
-        <v>6.1239999999999997</v>
+        <v>21.741</v>
       </c>
       <c r="L31">
-        <v>5.1959999999999997</v>
+        <v>20.081</v>
       </c>
       <c r="M31">
-        <v>0.92800000000000005</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.45">
@@ -17525,37 +17525,37 @@
         <v>2016</v>
       </c>
       <c r="C32">
-        <v>48.36</v>
+        <v>58.53</v>
       </c>
       <c r="D32">
-        <v>41.37</v>
+        <v>67.13</v>
       </c>
       <c r="E32">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="F32">
-        <v>0.03</v>
+        <v>0.21</v>
       </c>
       <c r="G32">
-        <v>14.65</v>
+        <v>24.26</v>
       </c>
       <c r="H32">
-        <v>8.4700000000000006</v>
+        <v>19.34</v>
       </c>
       <c r="I32">
-        <v>83.97</v>
+        <v>115.16</v>
       </c>
       <c r="J32">
-        <v>6.976</v>
+        <v>28.346</v>
       </c>
       <c r="K32">
-        <v>5.9649999999999999</v>
+        <v>21.286999999999999</v>
       </c>
       <c r="L32">
-        <v>5.0940000000000003</v>
+        <v>19.175000000000001</v>
       </c>
       <c r="M32">
-        <v>0.871</v>
+        <v>2.1120000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
@@ -17566,37 +17566,37 @@
         <v>2017</v>
       </c>
       <c r="C33">
-        <v>49.62</v>
+        <v>60.87</v>
       </c>
       <c r="D33">
-        <v>40.98</v>
+        <v>68</v>
       </c>
       <c r="E33">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="F33">
-        <v>0.05</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G33">
-        <v>14.19</v>
+        <v>22.46</v>
       </c>
       <c r="H33">
-        <v>8.17</v>
+        <v>18.95</v>
       </c>
       <c r="I33">
-        <v>84.95</v>
+        <v>117.17</v>
       </c>
       <c r="J33">
-        <v>6.069</v>
+        <v>27.327999999999999</v>
       </c>
       <c r="K33">
-        <v>5.0659999999999998</v>
+        <v>19.71</v>
       </c>
       <c r="L33">
-        <v>4.2640000000000002</v>
+        <v>17.439</v>
       </c>
       <c r="M33">
-        <v>0.80200000000000005</v>
+        <v>2.2709999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
@@ -17607,37 +17607,37 @@
         <v>2018</v>
       </c>
       <c r="C34">
-        <v>50.77</v>
+        <v>63.16</v>
       </c>
       <c r="D34">
-        <v>40.99</v>
+        <v>69.34</v>
       </c>
       <c r="E34">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="F34">
-        <v>7.0000000000000007E-2</v>
+        <v>0.39</v>
       </c>
       <c r="G34">
-        <v>21.64</v>
+        <v>26.75</v>
       </c>
       <c r="H34">
-        <v>4.3099999999999996</v>
+        <v>18.78</v>
       </c>
       <c r="I34">
-        <v>73.55</v>
+        <v>114.38</v>
       </c>
       <c r="J34">
-        <v>6.64</v>
+        <v>24.956</v>
       </c>
       <c r="K34">
-        <v>5.4210000000000003</v>
+        <v>21.138999999999999</v>
       </c>
       <c r="L34">
-        <v>4.5540000000000003</v>
+        <v>16.437999999999999</v>
       </c>
       <c r="M34">
-        <v>0.86699999999999999</v>
+        <v>4.7009999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
@@ -17648,37 +17648,37 @@
         <v>2019</v>
       </c>
       <c r="C35">
-        <v>51.77</v>
+        <v>64.650000000000006</v>
       </c>
       <c r="D35">
-        <v>40.71</v>
+        <v>69.540000000000006</v>
       </c>
       <c r="E35">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="F35">
-        <v>0.12</v>
+        <v>0.53</v>
       </c>
       <c r="G35">
-        <v>12.73</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="H35">
-        <v>14.59</v>
+        <v>19.55</v>
       </c>
       <c r="I35">
-        <v>92.34</v>
+        <v>121.41</v>
       </c>
       <c r="J35">
-        <v>5.6790000000000003</v>
+        <v>24.497</v>
       </c>
       <c r="K35">
-        <v>5.7110000000000003</v>
+        <v>22.204000000000001</v>
       </c>
       <c r="L35">
-        <v>4.8239999999999998</v>
+        <v>17.024999999999999</v>
       </c>
       <c r="M35">
-        <v>0.88700000000000001</v>
+        <v>5.1790000000000003</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
@@ -17689,37 +17689,37 @@
         <v>2020</v>
       </c>
       <c r="C36">
-        <v>51.17</v>
+        <v>70.2</v>
       </c>
       <c r="D36">
-        <v>40</v>
+        <v>68.33</v>
       </c>
       <c r="E36">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="F36">
-        <v>0.14000000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="G36">
-        <v>13.72</v>
+        <v>19.77</v>
       </c>
       <c r="H36">
-        <v>14.05</v>
+        <v>22.43</v>
       </c>
       <c r="I36">
-        <v>87.92</v>
+        <v>123.28</v>
       </c>
       <c r="J36">
-        <v>5.5380000000000003</v>
+        <v>21.129000000000001</v>
       </c>
       <c r="K36">
-        <v>5.641</v>
+        <v>20.227</v>
       </c>
       <c r="L36">
-        <v>4.6859999999999999</v>
+        <v>15.135999999999999</v>
       </c>
       <c r="M36">
-        <v>0.95499999999999996</v>
+        <v>5.0910000000000002</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.45">
@@ -17730,37 +17730,37 @@
         <v>2021</v>
       </c>
       <c r="C37">
-        <v>52.96</v>
+        <v>72.55</v>
       </c>
       <c r="D37">
-        <v>40.22</v>
+        <v>69.25</v>
       </c>
       <c r="E37">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="F37">
-        <v>0.33</v>
+        <v>1.07</v>
       </c>
       <c r="G37">
-        <v>15.19</v>
+        <v>20.89</v>
       </c>
       <c r="H37">
-        <v>23.07</v>
+        <v>20.63</v>
       </c>
       <c r="I37">
-        <v>99.05</v>
+        <v>122.17</v>
       </c>
       <c r="J37">
-        <v>5.6970000000000001</v>
+        <v>21.524999999999999</v>
       </c>
       <c r="K37">
-        <v>5.8</v>
+        <v>21.481000000000002</v>
       </c>
       <c r="L37">
-        <v>4.7629999999999999</v>
+        <v>16.103000000000002</v>
       </c>
       <c r="M37">
-        <v>1.0369999999999999</v>
+        <v>5.3780000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.45">
@@ -17771,37 +17771,37 @@
         <v>2022</v>
       </c>
       <c r="C38">
-        <v>51.47</v>
+        <v>71.5</v>
       </c>
       <c r="D38">
-        <v>38.15</v>
+        <v>65.88</v>
       </c>
       <c r="E38">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="F38">
-        <v>0.61</v>
+        <v>1.65</v>
       </c>
       <c r="G38">
-        <v>16.350000000000001</v>
+        <v>18.54</v>
       </c>
       <c r="H38">
-        <v>23.88</v>
+        <v>22.81</v>
       </c>
       <c r="I38">
-        <v>94.18</v>
+        <v>121.57</v>
       </c>
       <c r="J38">
-        <v>4.9379999999999997</v>
+        <v>20.457000000000001</v>
       </c>
       <c r="K38">
-        <v>5.0049999999999999</v>
+        <v>19.547000000000001</v>
       </c>
       <c r="L38">
-        <v>4.0209999999999999</v>
+        <v>14.882</v>
       </c>
       <c r="M38">
-        <v>0.98399999999999999</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.45">
@@ -17812,37 +17812,37 @@
         <v>2023</v>
       </c>
       <c r="C39">
-        <v>50.45</v>
+        <v>72.709999999999994</v>
       </c>
       <c r="D39">
-        <v>37.700000000000003</v>
+        <v>65.349999999999994</v>
       </c>
       <c r="E39">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="F39">
-        <v>1.1000000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="G39">
-        <v>20.22</v>
+        <v>19.55</v>
       </c>
       <c r="H39">
-        <v>18.59</v>
+        <v>25.21</v>
       </c>
       <c r="I39">
-        <v>82.1</v>
+        <v>121.64</v>
       </c>
       <c r="J39">
-        <v>4.2699999999999996</v>
+        <v>18.094000000000001</v>
       </c>
       <c r="K39">
-        <v>4.32</v>
+        <v>17.292000000000002</v>
       </c>
       <c r="L39">
-        <v>3.1909999999999998</v>
+        <v>13.074999999999999</v>
       </c>
       <c r="M39">
-        <v>1.129</v>
+        <v>4.2169999999999996</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.45">
@@ -17853,37 +17853,37 @@
         <v>2024</v>
       </c>
       <c r="C40">
-        <v>52.92</v>
+        <v>74.430000000000007</v>
       </c>
       <c r="D40">
-        <v>38.72</v>
+        <v>68.8</v>
       </c>
       <c r="E40">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="F40">
-        <v>1.74</v>
+        <v>2.75</v>
       </c>
       <c r="G40">
-        <v>27.75</v>
+        <v>20.03</v>
       </c>
       <c r="H40">
-        <v>17.41</v>
+        <v>24.25</v>
       </c>
       <c r="I40">
-        <v>75.709999999999994</v>
+        <v>123.84</v>
       </c>
       <c r="J40">
-        <v>3.92</v>
+        <v>16.524000000000001</v>
       </c>
       <c r="K40">
-        <v>4.0739999999999998</v>
+        <v>17.977</v>
       </c>
       <c r="L40">
-        <v>2.9460000000000002</v>
+        <v>13.765000000000001</v>
       </c>
       <c r="M40">
-        <v>1.1279999999999999</v>
+        <v>4.2119999999999997</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.45">
@@ -17894,37 +17894,37 @@
         <v>2015</v>
       </c>
       <c r="C41">
-        <v>279.04000000000002</v>
+        <v>47.7</v>
       </c>
       <c r="D41">
-        <v>274.98</v>
+        <v>41.35</v>
       </c>
       <c r="E41">
-        <v>11.07</v>
+        <v>1.56</v>
       </c>
       <c r="F41">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="G41">
-        <v>37.01</v>
+        <v>23.71</v>
       </c>
       <c r="H41">
-        <v>85.29</v>
+        <v>2.72</v>
       </c>
       <c r="I41">
-        <v>642.39</v>
+        <v>68.150000000000006</v>
       </c>
       <c r="J41">
-        <v>91.739000000000004</v>
+        <v>7.2930000000000001</v>
       </c>
       <c r="K41">
-        <v>111.577</v>
+        <v>6.1239999999999997</v>
       </c>
       <c r="L41">
-        <v>48.174999999999997</v>
+        <v>5.1959999999999997</v>
       </c>
       <c r="M41">
-        <v>63.402000000000001</v>
+        <v>0.92800000000000005</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.45">
@@ -17935,37 +17935,37 @@
         <v>2016</v>
       </c>
       <c r="C42">
-        <v>285.44</v>
+        <v>48.36</v>
       </c>
       <c r="D42">
-        <v>275.24</v>
+        <v>41.37</v>
       </c>
       <c r="E42">
-        <v>11.63</v>
+        <v>1.6</v>
       </c>
       <c r="F42">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="G42">
-        <v>28.34</v>
+        <v>14.65</v>
       </c>
       <c r="H42">
-        <v>78.86</v>
+        <v>8.4700000000000006</v>
       </c>
       <c r="I42">
-        <v>644.86</v>
+        <v>83.97</v>
       </c>
       <c r="J42">
-        <v>95.225999999999999</v>
+        <v>6.976</v>
       </c>
       <c r="K42">
-        <v>113.752</v>
+        <v>5.9649999999999999</v>
       </c>
       <c r="L42">
-        <v>49.697000000000003</v>
+        <v>5.0940000000000003</v>
       </c>
       <c r="M42">
-        <v>64.055000000000007</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.45">
@@ -17976,37 +17976,37 @@
         <v>2017</v>
       </c>
       <c r="C43">
-        <v>289</v>
+        <v>49.62</v>
       </c>
       <c r="D43">
-        <v>274.77</v>
+        <v>40.98</v>
       </c>
       <c r="E43">
-        <v>11.8</v>
+        <v>1.66</v>
       </c>
       <c r="F43">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="G43">
-        <v>27.84</v>
+        <v>14.19</v>
       </c>
       <c r="H43">
-        <v>80.3</v>
+        <v>8.17</v>
       </c>
       <c r="I43">
-        <v>647.72</v>
+        <v>84.95</v>
       </c>
       <c r="J43">
-        <v>95.143000000000001</v>
+        <v>6.069</v>
       </c>
       <c r="K43">
-        <v>114.04600000000001</v>
+        <v>5.0659999999999998</v>
       </c>
       <c r="L43">
-        <v>47.804000000000002</v>
+        <v>4.2640000000000002</v>
       </c>
       <c r="M43">
-        <v>66.242000000000004</v>
+        <v>0.80200000000000005</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.45">
@@ -18017,37 +18017,37 @@
         <v>2018</v>
       </c>
       <c r="C44">
-        <v>285.68</v>
+        <v>50.77</v>
       </c>
       <c r="D44">
-        <v>266.58</v>
+        <v>40.99</v>
       </c>
       <c r="E44">
-        <v>11.86</v>
+        <v>1.68</v>
       </c>
       <c r="F44">
-        <v>0.23</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G44">
-        <v>31.73</v>
+        <v>21.64</v>
       </c>
       <c r="H44">
-        <v>80.459999999999994</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="I44">
-        <v>634.29999999999995</v>
+        <v>73.55</v>
       </c>
       <c r="J44">
-        <v>98.507999999999996</v>
+        <v>6.64</v>
       </c>
       <c r="K44">
-        <v>110.97799999999999</v>
+        <v>5.4210000000000003</v>
       </c>
       <c r="L44">
-        <v>52.889000000000003</v>
+        <v>4.5540000000000003</v>
       </c>
       <c r="M44">
-        <v>58.088999999999999</v>
+        <v>0.86699999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.45">
@@ -18058,37 +18058,37 @@
         <v>2019</v>
       </c>
       <c r="C45">
-        <v>276.60000000000002</v>
+        <v>51.77</v>
       </c>
       <c r="D45">
-        <v>261.64</v>
+        <v>40.71</v>
       </c>
       <c r="E45">
-        <v>11.27</v>
+        <v>1.63</v>
       </c>
       <c r="F45">
-        <v>0.34</v>
+        <v>0.12</v>
       </c>
       <c r="G45">
-        <v>40.130000000000003</v>
+        <v>12.73</v>
       </c>
       <c r="H45">
-        <v>72.790000000000006</v>
+        <v>14.59</v>
       </c>
       <c r="I45">
-        <v>600.98</v>
+        <v>92.34</v>
       </c>
       <c r="J45">
-        <v>97.305999999999997</v>
+        <v>5.6790000000000003</v>
       </c>
       <c r="K45">
-        <v>111.782</v>
+        <v>5.7110000000000003</v>
       </c>
       <c r="L45">
-        <v>49.478999999999999</v>
+        <v>4.8239999999999998</v>
       </c>
       <c r="M45">
-        <v>62.302999999999997</v>
+        <v>0.88700000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.45">
@@ -18099,37 +18099,37 @@
         <v>2020</v>
       </c>
       <c r="C46">
-        <v>264.64</v>
+        <v>51.17</v>
       </c>
       <c r="D46">
-        <v>259.06</v>
+        <v>40</v>
       </c>
       <c r="E46">
-        <v>10.87</v>
+        <v>1.44</v>
       </c>
       <c r="F46">
-        <v>0.66</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G46">
-        <v>47.85</v>
+        <v>13.72</v>
       </c>
       <c r="H46">
-        <v>66.88</v>
+        <v>14.05</v>
       </c>
       <c r="I46">
-        <v>568.91</v>
+        <v>87.92</v>
       </c>
       <c r="J46">
-        <v>89.994</v>
+        <v>5.5380000000000003</v>
       </c>
       <c r="K46">
-        <v>103.56699999999999</v>
+        <v>5.641</v>
       </c>
       <c r="L46">
-        <v>46.262</v>
+        <v>4.6859999999999999</v>
       </c>
       <c r="M46">
-        <v>57.305</v>
+        <v>0.95499999999999996</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.45">
@@ -18140,37 +18140,37 @@
         <v>2021</v>
       </c>
       <c r="C47">
-        <v>273.68</v>
+        <v>52.96</v>
       </c>
       <c r="D47">
-        <v>267.54000000000002</v>
+        <v>40.22</v>
       </c>
       <c r="E47">
-        <v>11.48</v>
+        <v>1.52</v>
       </c>
       <c r="F47">
-        <v>1.39</v>
+        <v>0.33</v>
       </c>
       <c r="G47">
-        <v>51.73</v>
+        <v>15.19</v>
       </c>
       <c r="H47">
-        <v>70.31</v>
+        <v>23.07</v>
       </c>
       <c r="I47">
-        <v>587.46</v>
+        <v>99.05</v>
       </c>
       <c r="J47">
-        <v>97.787000000000006</v>
+        <v>5.6970000000000001</v>
       </c>
       <c r="K47">
-        <v>113.82899999999999</v>
+        <v>5.8</v>
       </c>
       <c r="L47">
-        <v>48.845999999999997</v>
+        <v>4.7629999999999999</v>
       </c>
       <c r="M47">
-        <v>64.983000000000004</v>
+        <v>1.0369999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.45">
@@ -18181,37 +18181,37 @@
         <v>2022</v>
       </c>
       <c r="C48">
-        <v>254.86</v>
+        <v>51.47</v>
       </c>
       <c r="D48">
-        <v>255.66</v>
+        <v>38.15</v>
       </c>
       <c r="E48">
-        <v>12.95</v>
+        <v>1.66</v>
       </c>
       <c r="F48">
-        <v>2.4500000000000002</v>
+        <v>0.61</v>
       </c>
       <c r="G48">
-        <v>49.33</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="H48">
-        <v>76.59</v>
+        <v>23.88</v>
       </c>
       <c r="I48">
-        <v>573</v>
+        <v>94.18</v>
       </c>
       <c r="J48">
-        <v>88.561999999999998</v>
+        <v>4.9379999999999997</v>
       </c>
       <c r="K48">
-        <v>103.169</v>
+        <v>5.0049999999999999</v>
       </c>
       <c r="L48">
-        <v>45.581000000000003</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="M48">
-        <v>57.588000000000001</v>
+        <v>0.98399999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.45">
@@ -18222,37 +18222,37 @@
         <v>2023</v>
       </c>
       <c r="C49">
-        <v>279.62</v>
+        <v>50.45</v>
       </c>
       <c r="D49">
-        <v>256.26</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="E49">
-        <v>12.74</v>
+        <v>1.58</v>
       </c>
       <c r="F49">
-        <v>4.5199999999999996</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G49">
-        <v>69.31</v>
+        <v>20.22</v>
       </c>
       <c r="H49">
-        <v>60.08</v>
+        <v>18.59</v>
       </c>
       <c r="I49">
-        <v>517.42999999999995</v>
+        <v>82.1</v>
       </c>
       <c r="J49">
-        <v>83.772000000000006</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="K49">
-        <v>99.41</v>
+        <v>4.32</v>
       </c>
       <c r="L49">
-        <v>42.277999999999999</v>
+        <v>3.1909999999999998</v>
       </c>
       <c r="M49">
-        <v>57.131999999999998</v>
+        <v>1.129</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.45">
@@ -18263,37 +18263,37 @@
         <v>2024</v>
       </c>
       <c r="C50">
-        <v>293</v>
+        <v>52.92</v>
       </c>
       <c r="D50">
-        <v>257.72000000000003</v>
+        <v>38.72</v>
       </c>
       <c r="E50">
-        <v>11.58</v>
+        <v>1.5</v>
       </c>
       <c r="F50">
-        <v>5.91</v>
+        <v>1.74</v>
       </c>
       <c r="G50">
-        <v>81.66</v>
+        <v>27.75</v>
       </c>
       <c r="H50">
-        <v>55.39</v>
+        <v>17.41</v>
       </c>
       <c r="I50">
-        <v>507.66</v>
+        <v>75.709999999999994</v>
       </c>
       <c r="J50">
-        <v>81.938000000000002</v>
+        <v>3.92</v>
       </c>
       <c r="K50">
-        <v>100.52500000000001</v>
+        <v>4.0739999999999998</v>
       </c>
       <c r="L50">
-        <v>43.360999999999997</v>
+        <v>2.9460000000000002</v>
       </c>
       <c r="M50">
-        <v>57.164000000000001</v>
+        <v>1.1279999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.45">
@@ -18304,37 +18304,37 @@
         <v>2015</v>
       </c>
       <c r="C51">
-        <v>25</v>
+        <v>279.04000000000002</v>
       </c>
       <c r="D51">
-        <v>36.909999999999997</v>
+        <v>274.98</v>
       </c>
       <c r="E51">
-        <v>3.14</v>
+        <v>11.07</v>
       </c>
       <c r="F51">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="G51">
-        <v>34.03</v>
+        <v>37.01</v>
       </c>
       <c r="H51">
-        <v>35.07</v>
+        <v>85.29</v>
       </c>
       <c r="I51">
-        <v>66.08</v>
+        <v>642.39</v>
       </c>
       <c r="J51">
-        <v>4.3970000000000002</v>
+        <v>91.739000000000004</v>
       </c>
       <c r="K51">
-        <v>5.5270000000000001</v>
+        <v>111.577</v>
       </c>
       <c r="L51">
-        <v>2.0230000000000001</v>
+        <v>48.174999999999997</v>
       </c>
       <c r="M51">
-        <v>3.504</v>
+        <v>63.402000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.45">
@@ -18345,37 +18345,37 @@
         <v>2016</v>
       </c>
       <c r="C52">
-        <v>24.9</v>
+        <v>285.44</v>
       </c>
       <c r="D52">
-        <v>37.049999999999997</v>
+        <v>275.24</v>
       </c>
       <c r="E52">
-        <v>3.2</v>
+        <v>11.63</v>
       </c>
       <c r="F52">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="G52">
-        <v>34.1</v>
+        <v>28.34</v>
       </c>
       <c r="H52">
-        <v>30.17</v>
+        <v>78.86</v>
       </c>
       <c r="I52">
-        <v>61.12</v>
+        <v>644.86</v>
       </c>
       <c r="J52">
-        <v>4.766</v>
+        <v>95.225999999999999</v>
       </c>
       <c r="K52">
-        <v>5.9560000000000004</v>
+        <v>113.752</v>
       </c>
       <c r="L52">
-        <v>2.0840000000000001</v>
+        <v>49.697000000000003</v>
       </c>
       <c r="M52">
-        <v>3.8719999999999999</v>
+        <v>64.055000000000007</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.45">
@@ -18386,37 +18386,37 @@
         <v>2017</v>
       </c>
       <c r="C53">
-        <v>25.33</v>
+        <v>289</v>
       </c>
       <c r="D53">
-        <v>37.18</v>
+        <v>274.77</v>
       </c>
       <c r="E53">
-        <v>3.15</v>
+        <v>11.8</v>
       </c>
       <c r="F53">
-        <v>7.0000000000000007E-2</v>
+        <v>0.16</v>
       </c>
       <c r="G53">
-        <v>36.5</v>
+        <v>27.84</v>
       </c>
       <c r="H53">
-        <v>30.95</v>
+        <v>80.3</v>
       </c>
       <c r="I53">
-        <v>60.18</v>
+        <v>647.72</v>
       </c>
       <c r="J53">
-        <v>5.0410000000000004</v>
+        <v>95.143000000000001</v>
       </c>
       <c r="K53">
-        <v>6.2809999999999997</v>
+        <v>114.04600000000001</v>
       </c>
       <c r="L53">
-        <v>2.1709999999999998</v>
+        <v>47.804000000000002</v>
       </c>
       <c r="M53">
-        <v>4.1100000000000003</v>
+        <v>66.242000000000004</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
@@ -18427,37 +18427,37 @@
         <v>2018</v>
       </c>
       <c r="C54">
-        <v>25.21</v>
+        <v>285.68</v>
       </c>
       <c r="D54">
-        <v>36.979999999999997</v>
+        <v>266.58</v>
       </c>
       <c r="E54">
-        <v>3.09</v>
+        <v>11.86</v>
       </c>
       <c r="F54">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="G54">
-        <v>31.02</v>
+        <v>31.73</v>
       </c>
       <c r="H54">
-        <v>32.61</v>
+        <v>80.459999999999994</v>
       </c>
       <c r="I54">
-        <v>66.319999999999993</v>
+        <v>634.29999999999995</v>
       </c>
       <c r="J54">
-        <v>5.07</v>
+        <v>98.507999999999996</v>
       </c>
       <c r="K54">
-        <v>6.2350000000000003</v>
+        <v>110.97799999999999</v>
       </c>
       <c r="L54">
-        <v>2.2189999999999999</v>
+        <v>52.889000000000003</v>
       </c>
       <c r="M54">
-        <v>4.016</v>
+        <v>58.088999999999999</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.45">
@@ -18468,37 +18468,37 @@
         <v>2019</v>
       </c>
       <c r="C55">
-        <v>25.42</v>
+        <v>276.60000000000002</v>
       </c>
       <c r="D55">
-        <v>36.590000000000003</v>
+        <v>261.64</v>
       </c>
       <c r="E55">
-        <v>3.04</v>
+        <v>11.27</v>
       </c>
       <c r="F55">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="G55">
-        <v>29.5</v>
+        <v>40.130000000000003</v>
       </c>
       <c r="H55">
-        <v>35.770000000000003</v>
+        <v>72.790000000000006</v>
       </c>
       <c r="I55">
-        <v>70.59</v>
+        <v>600.98</v>
       </c>
       <c r="J55">
-        <v>5.6820000000000004</v>
+        <v>97.305999999999997</v>
       </c>
       <c r="K55">
-        <v>7.0979999999999999</v>
+        <v>111.782</v>
       </c>
       <c r="L55">
-        <v>2.4329999999999998</v>
+        <v>49.478999999999999</v>
       </c>
       <c r="M55">
-        <v>4.665</v>
+        <v>62.302999999999997</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.45">
@@ -18509,37 +18509,37 @@
         <v>2020</v>
       </c>
       <c r="C56">
-        <v>25.45</v>
+        <v>264.64</v>
       </c>
       <c r="D56">
-        <v>36.159999999999997</v>
+        <v>259.06</v>
       </c>
       <c r="E56">
-        <v>2.82</v>
+        <v>10.87</v>
       </c>
       <c r="F56">
-        <v>0.14000000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="G56">
-        <v>26.99</v>
+        <v>47.85</v>
       </c>
       <c r="H56">
-        <v>32.549999999999997</v>
+        <v>66.88</v>
       </c>
       <c r="I56">
-        <v>68.650000000000006</v>
+        <v>568.91</v>
       </c>
       <c r="J56">
-        <v>5.5659999999999998</v>
+        <v>89.994</v>
       </c>
       <c r="K56">
-        <v>6.9420000000000002</v>
+        <v>103.56699999999999</v>
       </c>
       <c r="L56">
-        <v>2.4140000000000001</v>
+        <v>46.262</v>
       </c>
       <c r="M56">
-        <v>4.5279999999999996</v>
+        <v>57.305</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
@@ -18550,37 +18550,37 @@
         <v>2021</v>
       </c>
       <c r="C57">
-        <v>26.7</v>
+        <v>273.68</v>
       </c>
       <c r="D57">
-        <v>37.6</v>
+        <v>267.54000000000002</v>
       </c>
       <c r="E57">
-        <v>2.97</v>
+        <v>11.48</v>
       </c>
       <c r="F57">
-        <v>0.26</v>
+        <v>1.39</v>
       </c>
       <c r="G57">
-        <v>31.53</v>
+        <v>51.73</v>
       </c>
       <c r="H57">
-        <v>29.12</v>
+        <v>70.31</v>
       </c>
       <c r="I57">
-        <v>63.29</v>
+        <v>587.46</v>
       </c>
       <c r="J57">
-        <v>5.9770000000000003</v>
+        <v>97.787000000000006</v>
       </c>
       <c r="K57">
-        <v>7.524</v>
+        <v>113.82899999999999</v>
       </c>
       <c r="L57">
-        <v>2.5609999999999999</v>
+        <v>48.845999999999997</v>
       </c>
       <c r="M57">
-        <v>4.9630000000000001</v>
+        <v>64.983000000000004</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.45">
@@ -18591,37 +18591,37 @@
         <v>2022</v>
       </c>
       <c r="C58">
-        <v>27.22</v>
+        <v>254.86</v>
       </c>
       <c r="D58">
-        <v>36.68</v>
+        <v>255.66</v>
       </c>
       <c r="E58">
-        <v>3.03</v>
+        <v>12.95</v>
       </c>
       <c r="F58">
-        <v>0.44</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G58">
-        <v>33.119999999999997</v>
+        <v>49.33</v>
       </c>
       <c r="H58">
-        <v>29.73</v>
+        <v>76.59</v>
       </c>
       <c r="I58">
-        <v>62</v>
+        <v>573</v>
       </c>
       <c r="J58">
-        <v>5.6429999999999998</v>
+        <v>88.561999999999998</v>
       </c>
       <c r="K58">
-        <v>6.9960000000000004</v>
+        <v>103.169</v>
       </c>
       <c r="L58">
-        <v>2.5449999999999999</v>
+        <v>45.581000000000003</v>
       </c>
       <c r="M58">
-        <v>4.4509999999999996</v>
+        <v>57.588000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.45">
@@ -18632,37 +18632,37 @@
         <v>2023</v>
       </c>
       <c r="C59">
-        <v>27.14</v>
+        <v>279.62</v>
       </c>
       <c r="D59">
-        <v>36.4</v>
+        <v>256.26</v>
       </c>
       <c r="E59">
-        <v>3.02</v>
+        <v>12.74</v>
       </c>
       <c r="F59">
-        <v>0.62</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="G59">
-        <v>27.46</v>
+        <v>69.31</v>
       </c>
       <c r="H59">
-        <v>33.86</v>
+        <v>60.08</v>
       </c>
       <c r="I59">
-        <v>70.459999999999994</v>
+        <v>517.42999999999995</v>
       </c>
       <c r="J59">
-        <v>5.9429999999999996</v>
+        <v>83.772000000000006</v>
       </c>
       <c r="K59">
-        <v>7.1909999999999998</v>
+        <v>99.41</v>
       </c>
       <c r="L59">
-        <v>2.6869999999999998</v>
+        <v>42.277999999999999</v>
       </c>
       <c r="M59">
-        <v>4.5039999999999996</v>
+        <v>57.131999999999998</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
@@ -18673,37 +18673,37 @@
         <v>2024</v>
       </c>
       <c r="C60">
-        <v>28.79</v>
+        <v>293</v>
       </c>
       <c r="D60">
-        <v>36.909999999999997</v>
+        <v>257.72000000000003</v>
       </c>
       <c r="E60">
-        <v>3.08</v>
+        <v>11.58</v>
       </c>
       <c r="F60">
-        <v>0.88</v>
+        <v>5.91</v>
       </c>
       <c r="G60">
-        <v>25.96</v>
+        <v>81.66</v>
       </c>
       <c r="H60">
-        <v>40.35</v>
+        <v>55.39</v>
       </c>
       <c r="I60">
-        <v>79.23</v>
+        <v>507.66</v>
       </c>
       <c r="J60">
-        <v>6.3490000000000002</v>
+        <v>81.938000000000002</v>
       </c>
       <c r="K60">
-        <v>7.4550000000000001</v>
+        <v>100.52500000000001</v>
       </c>
       <c r="L60">
-        <v>2.827</v>
+        <v>43.360999999999997</v>
       </c>
       <c r="M60">
-        <v>4.6280000000000001</v>
+        <v>57.164000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.45">
@@ -18714,37 +18714,37 @@
         <v>2015</v>
       </c>
       <c r="C61">
-        <v>131.75</v>
+        <v>25</v>
       </c>
       <c r="D61">
-        <v>163.96</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="E61">
-        <v>5.51</v>
+        <v>3.14</v>
       </c>
       <c r="F61">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G61">
-        <v>50.85</v>
+        <v>34.03</v>
       </c>
       <c r="H61">
-        <v>4.47</v>
+        <v>35.07</v>
       </c>
       <c r="I61">
-        <v>281.56</v>
+        <v>66.08</v>
       </c>
       <c r="J61">
-        <v>59.222999999999999</v>
+        <v>4.3970000000000002</v>
       </c>
       <c r="K61">
-        <v>44.710999999999999</v>
+        <v>5.5270000000000001</v>
       </c>
       <c r="L61">
-        <v>31.463999999999999</v>
+        <v>2.0230000000000001</v>
       </c>
       <c r="M61">
-        <v>13.247</v>
+        <v>3.504</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.45">
@@ -18755,37 +18755,37 @@
         <v>2016</v>
       </c>
       <c r="C62">
-        <v>131.72</v>
+        <v>24.9</v>
       </c>
       <c r="D62">
-        <v>161.61000000000001</v>
+        <v>37.049999999999997</v>
       </c>
       <c r="E62">
-        <v>5.84</v>
+        <v>3.2</v>
       </c>
       <c r="F62">
-        <v>7.0000000000000007E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G62">
-        <v>43.18</v>
+        <v>34.1</v>
       </c>
       <c r="H62">
-        <v>6.15</v>
+        <v>30.17</v>
       </c>
       <c r="I62">
-        <v>287.94</v>
+        <v>61.12</v>
       </c>
       <c r="J62">
-        <v>61.045999999999999</v>
+        <v>4.766</v>
       </c>
       <c r="K62">
-        <v>45.857999999999997</v>
+        <v>5.9560000000000004</v>
       </c>
       <c r="L62">
-        <v>31.867999999999999</v>
+        <v>2.0840000000000001</v>
       </c>
       <c r="M62">
-        <v>13.99</v>
+        <v>3.8719999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.45">
@@ -18796,37 +18796,37 @@
         <v>2017</v>
       </c>
       <c r="C63">
-        <v>135.38999999999999</v>
+        <v>25.33</v>
       </c>
       <c r="D63">
-        <v>164.97</v>
+        <v>37.18</v>
       </c>
       <c r="E63">
-        <v>5.89</v>
+        <v>3.15</v>
       </c>
       <c r="F63">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G63">
-        <v>42.89</v>
+        <v>36.5</v>
       </c>
       <c r="H63">
-        <v>5.13</v>
+        <v>30.95</v>
       </c>
       <c r="I63">
-        <v>294</v>
+        <v>60.18</v>
       </c>
       <c r="J63">
-        <v>61.08</v>
+        <v>5.0410000000000004</v>
       </c>
       <c r="K63">
-        <v>47.750999999999998</v>
+        <v>6.2809999999999997</v>
       </c>
       <c r="L63">
-        <v>33.521000000000001</v>
+        <v>2.1709999999999998</v>
       </c>
       <c r="M63">
-        <v>14.23</v>
+        <v>4.1100000000000003</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.45">
@@ -18837,37 +18837,37 @@
         <v>2018</v>
       </c>
       <c r="C64">
-        <v>138.85</v>
+        <v>25.21</v>
       </c>
       <c r="D64">
-        <v>165.47</v>
+        <v>36.979999999999997</v>
       </c>
       <c r="E64">
-        <v>6.07</v>
+        <v>3.09</v>
       </c>
       <c r="F64">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G64">
-        <v>47.17</v>
+        <v>31.02</v>
       </c>
       <c r="H64">
-        <v>3.27</v>
+        <v>32.61</v>
       </c>
       <c r="I64">
-        <v>287.99</v>
+        <v>66.319999999999993</v>
       </c>
       <c r="J64">
-        <v>59.622</v>
+        <v>5.07</v>
       </c>
       <c r="K64">
-        <v>47.627000000000002</v>
+        <v>6.2350000000000003</v>
       </c>
       <c r="L64">
-        <v>30.41</v>
+        <v>2.2189999999999999</v>
       </c>
       <c r="M64">
-        <v>17.216999999999999</v>
+        <v>4.016</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.45">
@@ -18878,37 +18878,37 @@
         <v>2019</v>
       </c>
       <c r="C65">
-        <v>141.87</v>
+        <v>25.42</v>
       </c>
       <c r="D65">
-        <v>160.86000000000001</v>
+        <v>36.590000000000003</v>
       </c>
       <c r="E65">
-        <v>5.84</v>
+        <v>3.04</v>
       </c>
       <c r="F65">
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G65">
-        <v>43.97</v>
+        <v>29.5</v>
       </c>
       <c r="H65">
-        <v>5.83</v>
+        <v>35.770000000000003</v>
       </c>
       <c r="I65">
-        <v>292.02</v>
+        <v>70.59</v>
       </c>
       <c r="J65">
-        <v>60.246000000000002</v>
+        <v>5.6820000000000004</v>
       </c>
       <c r="K65">
-        <v>48.22</v>
+        <v>7.0979999999999999</v>
       </c>
       <c r="L65">
-        <v>34.286000000000001</v>
+        <v>2.4329999999999998</v>
       </c>
       <c r="M65">
-        <v>13.933999999999999</v>
+        <v>4.665</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.45">
@@ -18919,37 +18919,37 @@
         <v>2020</v>
       </c>
       <c r="C66">
-        <v>137.63999999999999</v>
+        <v>25.45</v>
       </c>
       <c r="D66">
-        <v>147.78</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="E66">
-        <v>4.93</v>
+        <v>2.82</v>
       </c>
       <c r="F66">
-        <v>0.19</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G66">
-        <v>39.79</v>
+        <v>26.99</v>
       </c>
       <c r="H66">
-        <v>7.59</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="I66">
-        <v>278.58999999999997</v>
+        <v>68.650000000000006</v>
       </c>
       <c r="J66">
-        <v>59.3</v>
+        <v>5.5659999999999998</v>
       </c>
       <c r="K66">
-        <v>45.024000000000001</v>
+        <v>6.9420000000000002</v>
       </c>
       <c r="L66">
-        <v>31.337</v>
+        <v>2.4140000000000001</v>
       </c>
       <c r="M66">
-        <v>13.686999999999999</v>
+        <v>4.5279999999999996</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.45">
@@ -18960,37 +18960,37 @@
         <v>2021</v>
       </c>
       <c r="C67">
-        <v>167.82</v>
+        <v>26.7</v>
       </c>
       <c r="D67">
-        <v>165.99</v>
+        <v>37.6</v>
       </c>
       <c r="E67">
-        <v>5.46</v>
+        <v>2.97</v>
       </c>
       <c r="F67">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="G67">
-        <v>46.57</v>
+        <v>31.53</v>
       </c>
       <c r="H67">
-        <v>3.78</v>
+        <v>29.12</v>
       </c>
       <c r="I67">
-        <v>286.98</v>
+        <v>63.29</v>
       </c>
       <c r="J67">
-        <v>21.324000000000002</v>
+        <v>5.9770000000000003</v>
       </c>
       <c r="K67">
-        <v>17.997</v>
+        <v>7.524</v>
       </c>
       <c r="L67">
-        <v>6.89</v>
+        <v>2.5609999999999999</v>
       </c>
       <c r="M67">
-        <v>11.106999999999999</v>
+        <v>4.9630000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.45">
@@ -19001,37 +19001,37 @@
         <v>2022</v>
       </c>
       <c r="C68">
-        <v>165.68</v>
+        <v>27.22</v>
       </c>
       <c r="D68">
-        <v>166.22</v>
+        <v>36.68</v>
       </c>
       <c r="E68">
-        <v>5.9</v>
+        <v>3.03</v>
       </c>
       <c r="F68">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="G68">
-        <v>47.39</v>
+        <v>33.119999999999997</v>
       </c>
       <c r="H68">
-        <v>4.4000000000000004</v>
+        <v>29.73</v>
       </c>
       <c r="I68">
-        <v>282.07</v>
+        <v>62</v>
       </c>
       <c r="J68">
-        <v>19.646999999999998</v>
+        <v>5.6429999999999998</v>
       </c>
       <c r="K68">
-        <v>17.373000000000001</v>
+        <v>6.9960000000000004</v>
       </c>
       <c r="L68">
-        <v>6.5309999999999997</v>
+        <v>2.5449999999999999</v>
       </c>
       <c r="M68">
-        <v>10.842000000000001</v>
+        <v>4.4509999999999996</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.45">
@@ -19042,37 +19042,37 @@
         <v>2023</v>
       </c>
       <c r="C69">
-        <v>160.19</v>
+        <v>27.14</v>
       </c>
       <c r="D69">
-        <v>163.18</v>
+        <v>36.4</v>
       </c>
       <c r="E69">
-        <v>6.49</v>
+        <v>3.02</v>
       </c>
       <c r="F69">
-        <v>0.82</v>
+        <v>0.62</v>
       </c>
       <c r="G69">
-        <v>54.57</v>
+        <v>27.46</v>
       </c>
       <c r="H69">
-        <v>3.32</v>
+        <v>33.86</v>
       </c>
       <c r="I69">
-        <v>263.17</v>
+        <v>70.459999999999994</v>
       </c>
       <c r="J69">
-        <v>19.937000000000001</v>
+        <v>5.9429999999999996</v>
       </c>
       <c r="K69">
-        <v>16.628</v>
+        <v>7.1909999999999998</v>
       </c>
       <c r="L69">
-        <v>6.5359999999999996</v>
+        <v>2.6869999999999998</v>
       </c>
       <c r="M69">
-        <v>10.092000000000001</v>
+        <v>4.5039999999999996</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.45">
@@ -19083,37 +19083,37 @@
         <v>2024</v>
       </c>
       <c r="C70">
-        <v>163.46</v>
+        <v>28.79</v>
       </c>
       <c r="D70">
-        <v>168.27</v>
+        <v>36.909999999999997</v>
       </c>
       <c r="E70">
-        <v>6.63</v>
+        <v>3.08</v>
       </c>
       <c r="F70">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="G70">
-        <v>55.91</v>
+        <v>25.96</v>
       </c>
       <c r="H70">
-        <v>4.91</v>
+        <v>40.35</v>
       </c>
       <c r="I70">
-        <v>269.38</v>
+        <v>79.23</v>
       </c>
       <c r="J70">
-        <v>20.145</v>
+        <v>6.3490000000000002</v>
       </c>
       <c r="K70">
-        <v>17.812999999999999</v>
+        <v>7.4550000000000001</v>
       </c>
       <c r="L70">
-        <v>6.508</v>
+        <v>2.827</v>
       </c>
       <c r="M70">
-        <v>11.305</v>
+        <v>4.6280000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.45">
@@ -19124,37 +19124,37 @@
         <v>2015</v>
       </c>
       <c r="C71">
-        <v>111.6</v>
+        <v>131.75</v>
       </c>
       <c r="D71">
-        <v>150</v>
+        <v>163.96</v>
       </c>
       <c r="E71">
-        <v>3.93</v>
+        <v>5.51</v>
       </c>
       <c r="F71">
-        <v>0.03</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G71">
-        <v>14.96</v>
+        <v>50.85</v>
       </c>
       <c r="H71">
-        <v>15.09</v>
+        <v>4.47</v>
       </c>
       <c r="I71">
-        <v>277.68</v>
+        <v>281.56</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>59.222999999999999</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>44.710999999999999</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>31.463999999999999</v>
       </c>
       <c r="M71">
-        <v>0</v>
+        <v>13.247</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.45">
@@ -19165,37 +19165,37 @@
         <v>2016</v>
       </c>
       <c r="C72">
-        <v>113.7</v>
+        <v>131.72</v>
       </c>
       <c r="D72">
-        <v>149.02000000000001</v>
+        <v>161.61000000000001</v>
       </c>
       <c r="E72">
-        <v>3.84</v>
+        <v>5.84</v>
       </c>
       <c r="F72">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G72">
-        <v>21.84</v>
+        <v>43.18</v>
       </c>
       <c r="H72">
-        <v>14.18</v>
+        <v>6.15</v>
       </c>
       <c r="I72">
-        <v>271.3</v>
+        <v>287.94</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>61.045999999999999</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>45.857999999999997</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>31.867999999999999</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.45">
@@ -19206,37 +19206,37 @@
         <v>2017</v>
       </c>
       <c r="C73">
-        <v>118.66</v>
+        <v>135.38999999999999</v>
       </c>
       <c r="D73">
-        <v>152.59</v>
+        <v>164.97</v>
       </c>
       <c r="E73">
-        <v>3.9</v>
+        <v>5.89</v>
       </c>
       <c r="F73">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="G73">
-        <v>23.76</v>
+        <v>42.89</v>
       </c>
       <c r="H73">
-        <v>14.59</v>
+        <v>5.13</v>
       </c>
       <c r="I73">
-        <v>272.98</v>
+        <v>294</v>
       </c>
       <c r="J73">
-        <v>0</v>
+        <v>61.08</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>47.750999999999998</v>
       </c>
       <c r="L73">
-        <v>0</v>
+        <v>33.521000000000001</v>
       </c>
       <c r="M73">
-        <v>0</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.45">
@@ -19247,37 +19247,37 @@
         <v>2018</v>
       </c>
       <c r="C74">
-        <v>117.47</v>
+        <v>138.85</v>
       </c>
       <c r="D74">
-        <v>154.53</v>
+        <v>165.47</v>
       </c>
       <c r="E74">
-        <v>3.91</v>
+        <v>6.07</v>
       </c>
       <c r="F74">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="G74">
-        <v>24.02</v>
+        <v>47.17</v>
       </c>
       <c r="H74">
-        <v>12.92</v>
+        <v>3.27</v>
       </c>
       <c r="I74">
-        <v>271.98</v>
+        <v>287.99</v>
       </c>
       <c r="J74">
-        <v>0</v>
+        <v>59.622</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>47.627000000000002</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>30.41</v>
       </c>
       <c r="M74">
-        <v>0</v>
+        <v>17.216999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.45">
@@ -19288,37 +19288,37 @@
         <v>2019</v>
       </c>
       <c r="C75">
-        <v>115.82</v>
+        <v>141.87</v>
       </c>
       <c r="D75">
-        <v>153.09</v>
+        <v>160.86000000000001</v>
       </c>
       <c r="E75">
-        <v>3.76</v>
+        <v>5.84</v>
       </c>
       <c r="F75">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G75">
-        <v>18.72</v>
+        <v>43.97</v>
       </c>
       <c r="H75">
-        <v>11.86</v>
+        <v>5.83</v>
       </c>
       <c r="I75">
-        <v>271.02999999999997</v>
+        <v>292.02</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>60.246000000000002</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>48.22</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>34.286000000000001</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>13.933999999999999</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.45">
@@ -19329,37 +19329,37 @@
         <v>2020</v>
       </c>
       <c r="C76">
-        <v>106.27</v>
+        <v>137.63999999999999</v>
       </c>
       <c r="D76">
-        <v>145.71</v>
+        <v>147.78</v>
       </c>
       <c r="E76">
-        <v>3.11</v>
+        <v>4.93</v>
       </c>
       <c r="F76">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G76">
-        <v>17.93</v>
+        <v>39.79</v>
       </c>
       <c r="H76">
-        <v>14.65</v>
+        <v>7.59</v>
       </c>
       <c r="I76">
-        <v>259.88</v>
+        <v>278.58999999999997</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>45.024000000000001</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>31.337</v>
       </c>
       <c r="M76">
-        <v>0</v>
+        <v>13.686999999999999</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.45">
@@ -19370,37 +19370,37 @@
         <v>2021</v>
       </c>
       <c r="C77">
-        <v>114</v>
+        <v>167.82</v>
       </c>
       <c r="D77">
-        <v>148.05000000000001</v>
+        <v>165.99</v>
       </c>
       <c r="E77">
-        <v>3.29</v>
+        <v>5.46</v>
       </c>
       <c r="F77">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="G77">
-        <v>17.41</v>
+        <v>46.57</v>
       </c>
       <c r="H77">
-        <v>16.559999999999999</v>
+        <v>3.78</v>
       </c>
       <c r="I77">
-        <v>271.08999999999997</v>
+        <v>286.98</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>21.324000000000002</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>17.997</v>
       </c>
       <c r="L77">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="M77">
-        <v>0</v>
+        <v>11.106999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.45">
@@ -19411,37 +19411,37 @@
         <v>2022</v>
       </c>
       <c r="C78">
-        <v>102.28</v>
+        <v>165.68</v>
       </c>
       <c r="D78">
-        <v>148.93</v>
+        <v>166.22</v>
       </c>
       <c r="E78">
-        <v>3.43</v>
+        <v>5.9</v>
       </c>
       <c r="F78">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="G78">
-        <v>8.0299999999999994</v>
+        <v>47.39</v>
       </c>
       <c r="H78">
-        <v>27.83</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="I78">
-        <v>287.94</v>
+        <v>282.07</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>19.646999999999998</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>17.373000000000001</v>
       </c>
       <c r="L78">
-        <v>0</v>
+        <v>6.5309999999999997</v>
       </c>
       <c r="M78">
-        <v>0</v>
+        <v>10.842000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.45">
@@ -19452,37 +19452,37 @@
         <v>2023</v>
       </c>
       <c r="C79">
-        <v>100.97</v>
+        <v>160.19</v>
       </c>
       <c r="D79">
-        <v>151.04</v>
+        <v>163.18</v>
       </c>
       <c r="E79">
-        <v>3.52</v>
+        <v>6.49</v>
       </c>
       <c r="F79">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="G79">
-        <v>11.32</v>
+        <v>54.57</v>
       </c>
       <c r="H79">
-        <v>25.27</v>
+        <v>3.32</v>
       </c>
       <c r="I79">
-        <v>279.77</v>
+        <v>263.17</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>19.937000000000001</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>16.628</v>
       </c>
       <c r="L79">
-        <v>0</v>
+        <v>6.5359999999999996</v>
       </c>
       <c r="M79">
-        <v>0</v>
+        <v>10.092000000000001</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.45">
@@ -19493,37 +19493,37 @@
         <v>2024</v>
       </c>
       <c r="C80">
-        <v>104.1</v>
+        <v>163.46</v>
       </c>
       <c r="D80">
-        <v>156.66999999999999</v>
+        <v>168.27</v>
       </c>
       <c r="E80">
-        <v>3.76</v>
+        <v>6.63</v>
       </c>
       <c r="F80">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="G80">
-        <v>14.35</v>
+        <v>55.91</v>
       </c>
       <c r="H80">
-        <v>24.58</v>
+        <v>4.91</v>
       </c>
       <c r="I80">
-        <v>281.51</v>
+        <v>269.38</v>
       </c>
       <c r="J80">
-        <v>3.7999999999999999E-2</v>
+        <v>20.145</v>
       </c>
       <c r="K80">
-        <v>0.56200000000000006</v>
+        <v>17.812999999999999</v>
       </c>
       <c r="L80">
-        <v>7.3999999999999996E-2</v>
+        <v>6.508</v>
       </c>
       <c r="M80">
-        <v>0.48799999999999999</v>
+        <v>11.305</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.45">
@@ -19534,37 +19534,37 @@
         <v>2015</v>
       </c>
       <c r="C81">
-        <v>57.21</v>
+        <v>111.6</v>
       </c>
       <c r="D81">
-        <v>67.48</v>
+        <v>150</v>
       </c>
       <c r="E81">
-        <v>1.64</v>
+        <v>3.93</v>
       </c>
       <c r="F81">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="G81">
-        <v>30.76</v>
+        <v>14.96</v>
       </c>
       <c r="H81">
-        <v>22.01</v>
+        <v>15.09</v>
       </c>
       <c r="I81">
-        <v>110.21</v>
+        <v>277.68</v>
       </c>
       <c r="J81">
-        <v>29.603000000000002</v>
+        <v>0</v>
       </c>
       <c r="K81">
-        <v>21.741</v>
+        <v>0</v>
       </c>
       <c r="L81">
-        <v>20.081</v>
+        <v>0</v>
       </c>
       <c r="M81">
-        <v>1.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.45">
@@ -19575,37 +19575,37 @@
         <v>2016</v>
       </c>
       <c r="C82">
-        <v>58.53</v>
+        <v>113.7</v>
       </c>
       <c r="D82">
-        <v>67.13</v>
+        <v>149.02000000000001</v>
       </c>
       <c r="E82">
-        <v>1.71</v>
+        <v>3.84</v>
       </c>
       <c r="F82">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="G82">
-        <v>24.26</v>
+        <v>21.84</v>
       </c>
       <c r="H82">
-        <v>19.34</v>
+        <v>14.18</v>
       </c>
       <c r="I82">
-        <v>115.16</v>
+        <v>271.3</v>
       </c>
       <c r="J82">
-        <v>28.346</v>
+        <v>0</v>
       </c>
       <c r="K82">
-        <v>21.286999999999999</v>
+        <v>0</v>
       </c>
       <c r="L82">
-        <v>19.175000000000001</v>
+        <v>0</v>
       </c>
       <c r="M82">
-        <v>2.1120000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.45">
@@ -19616,37 +19616,37 @@
         <v>2017</v>
       </c>
       <c r="C83">
-        <v>60.87</v>
+        <v>118.66</v>
       </c>
       <c r="D83">
-        <v>68</v>
+        <v>152.59</v>
       </c>
       <c r="E83">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="F83">
-        <v>0.28000000000000003</v>
+        <v>0.06</v>
       </c>
       <c r="G83">
-        <v>22.46</v>
+        <v>23.76</v>
       </c>
       <c r="H83">
-        <v>18.95</v>
+        <v>14.59</v>
       </c>
       <c r="I83">
-        <v>117.17</v>
+        <v>272.98</v>
       </c>
       <c r="J83">
-        <v>27.327999999999999</v>
+        <v>0</v>
       </c>
       <c r="K83">
-        <v>19.71</v>
+        <v>0</v>
       </c>
       <c r="L83">
-        <v>17.439</v>
+        <v>0</v>
       </c>
       <c r="M83">
-        <v>2.2709999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.45">
@@ -19657,37 +19657,37 @@
         <v>2018</v>
       </c>
       <c r="C84">
-        <v>63.16</v>
+        <v>117.47</v>
       </c>
       <c r="D84">
-        <v>69.34</v>
+        <v>154.53</v>
       </c>
       <c r="E84">
-        <v>1.78</v>
+        <v>3.91</v>
       </c>
       <c r="F84">
-        <v>0.39</v>
+        <v>0.11</v>
       </c>
       <c r="G84">
-        <v>26.75</v>
+        <v>24.02</v>
       </c>
       <c r="H84">
-        <v>18.78</v>
+        <v>12.92</v>
       </c>
       <c r="I84">
-        <v>114.38</v>
+        <v>271.98</v>
       </c>
       <c r="J84">
-        <v>24.956</v>
+        <v>0</v>
       </c>
       <c r="K84">
-        <v>21.138999999999999</v>
+        <v>0</v>
       </c>
       <c r="L84">
-        <v>16.437999999999999</v>
+        <v>0</v>
       </c>
       <c r="M84">
-        <v>4.7009999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.45">
@@ -19698,37 +19698,37 @@
         <v>2019</v>
       </c>
       <c r="C85">
-        <v>64.650000000000006</v>
+        <v>115.82</v>
       </c>
       <c r="D85">
-        <v>69.540000000000006</v>
+        <v>153.09</v>
       </c>
       <c r="E85">
-        <v>1.81</v>
+        <v>3.76</v>
       </c>
       <c r="F85">
-        <v>0.53</v>
+        <v>0.16</v>
       </c>
       <c r="G85">
-        <v>20.399999999999999</v>
+        <v>18.72</v>
       </c>
       <c r="H85">
-        <v>19.55</v>
+        <v>11.86</v>
       </c>
       <c r="I85">
-        <v>121.41</v>
+        <v>271.02999999999997</v>
       </c>
       <c r="J85">
-        <v>24.497</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>22.204000000000001</v>
+        <v>0</v>
       </c>
       <c r="L85">
-        <v>17.024999999999999</v>
+        <v>0</v>
       </c>
       <c r="M85">
-        <v>5.1790000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.45">
@@ -19739,37 +19739,37 @@
         <v>2020</v>
       </c>
       <c r="C86">
-        <v>70.2</v>
+        <v>106.27</v>
       </c>
       <c r="D86">
-        <v>68.33</v>
+        <v>145.71</v>
       </c>
       <c r="E86">
-        <v>1.63</v>
+        <v>3.11</v>
       </c>
       <c r="F86">
-        <v>0.67</v>
+        <v>0.2</v>
       </c>
       <c r="G86">
-        <v>19.77</v>
+        <v>17.93</v>
       </c>
       <c r="H86">
-        <v>22.43</v>
+        <v>14.65</v>
       </c>
       <c r="I86">
-        <v>123.28</v>
+        <v>259.88</v>
       </c>
       <c r="J86">
-        <v>21.129000000000001</v>
+        <v>0</v>
       </c>
       <c r="K86">
-        <v>20.227</v>
+        <v>0</v>
       </c>
       <c r="L86">
-        <v>15.135999999999999</v>
+        <v>0</v>
       </c>
       <c r="M86">
-        <v>5.0910000000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.45">
@@ -19780,37 +19780,37 @@
         <v>2021</v>
       </c>
       <c r="C87">
-        <v>72.55</v>
+        <v>114</v>
       </c>
       <c r="D87">
-        <v>69.25</v>
+        <v>148.05000000000001</v>
       </c>
       <c r="E87">
-        <v>1.63</v>
+        <v>3.29</v>
       </c>
       <c r="F87">
-        <v>1.07</v>
+        <v>0.35</v>
       </c>
       <c r="G87">
-        <v>20.89</v>
+        <v>17.41</v>
       </c>
       <c r="H87">
-        <v>20.63</v>
+        <v>16.559999999999999</v>
       </c>
       <c r="I87">
-        <v>122.17</v>
+        <v>271.08999999999997</v>
       </c>
       <c r="J87">
-        <v>21.524999999999999</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>21.481000000000002</v>
+        <v>0</v>
       </c>
       <c r="L87">
-        <v>16.103000000000002</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>5.3780000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.45">
@@ -19821,37 +19821,37 @@
         <v>2022</v>
       </c>
       <c r="C88">
-        <v>71.5</v>
+        <v>102.28</v>
       </c>
       <c r="D88">
-        <v>65.88</v>
+        <v>148.93</v>
       </c>
       <c r="E88">
-        <v>1.69</v>
+        <v>3.43</v>
       </c>
       <c r="F88">
-        <v>1.65</v>
+        <v>0.53</v>
       </c>
       <c r="G88">
-        <v>18.54</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="H88">
-        <v>22.81</v>
+        <v>27.83</v>
       </c>
       <c r="I88">
-        <v>121.57</v>
+        <v>287.94</v>
       </c>
       <c r="J88">
-        <v>20.457000000000001</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>19.547000000000001</v>
+        <v>0</v>
       </c>
       <c r="L88">
-        <v>14.882</v>
+        <v>0</v>
       </c>
       <c r="M88">
-        <v>4.665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.45">
@@ -19862,37 +19862,37 @@
         <v>2023</v>
       </c>
       <c r="C89">
-        <v>72.709999999999994</v>
+        <v>100.97</v>
       </c>
       <c r="D89">
-        <v>65.349999999999994</v>
+        <v>151.04</v>
       </c>
       <c r="E89">
-        <v>1.66</v>
+        <v>3.52</v>
       </c>
       <c r="F89">
-        <v>2.21</v>
+        <v>0.77</v>
       </c>
       <c r="G89">
-        <v>19.55</v>
+        <v>11.32</v>
       </c>
       <c r="H89">
-        <v>25.21</v>
+        <v>25.27</v>
       </c>
       <c r="I89">
-        <v>121.64</v>
+        <v>279.77</v>
       </c>
       <c r="J89">
-        <v>18.094000000000001</v>
+        <v>0</v>
       </c>
       <c r="K89">
-        <v>17.292000000000002</v>
+        <v>0</v>
       </c>
       <c r="L89">
-        <v>13.074999999999999</v>
+        <v>0</v>
       </c>
       <c r="M89">
-        <v>4.2169999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.45">
@@ -19903,37 +19903,37 @@
         <v>2024</v>
       </c>
       <c r="C90">
-        <v>74.430000000000007</v>
+        <v>104.1</v>
       </c>
       <c r="D90">
-        <v>68.8</v>
+        <v>156.66999999999999</v>
       </c>
       <c r="E90">
-        <v>1.7</v>
+        <v>3.76</v>
       </c>
       <c r="F90">
-        <v>2.75</v>
+        <v>0.91</v>
       </c>
       <c r="G90">
-        <v>20.03</v>
+        <v>14.35</v>
       </c>
       <c r="H90">
-        <v>24.25</v>
+        <v>24.58</v>
       </c>
       <c r="I90">
-        <v>123.84</v>
+        <v>281.51</v>
       </c>
       <c r="J90">
-        <v>16.524000000000001</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="K90">
-        <v>17.977</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="L90">
-        <v>13.765000000000001</v>
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="M90">
-        <v>4.2119999999999997</v>
+        <v>0.48799999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -35686,7 +35686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83445B4-A795-43D8-A6E4-26AB6E000174}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{215F107D-B1E8-4674-B0E5-68B59542255D}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -36967,7 +36967,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65D4ED2E-6EF5-4FC1-966B-B7A9969F11A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE0D0815-1175-47AE-9D9D-6284184F6E2B}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -37086,7 +37086,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>94.18</v>
+        <v>121.57</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -37104,7 +37104,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.0209999999999999</v>
+        <v>14.882</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -37119,7 +37119,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>0.98399999999999999</v>
+        <v>4.665</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -37170,31 +37170,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>94.18</v>
+        <v>121.57</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>98.88900000000001</v>
+        <v>127.6485</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>110.1906</v>
+        <v>142.23689999999999</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>121.49220000000001</v>
+        <v>156.8253</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>133.73560000000001</v>
+        <v>172.62939999999998</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>149.74620000000002</v>
+        <v>193.2963</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>162.9314</v>
+        <v>210.31609999999998</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -37233,7 +37233,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=BEL</v>
+        <v>~TFM_INS-TS: region=NLD</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -37397,31 +37397,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>34.846600000000002</v>
+        <v>44.980899999999998</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>34.611150000000002</v>
+        <v>44.676974999999999</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>37.464804000000001</v>
+        <v>48.360545999999999</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>40.092426000000003</v>
+        <v>51.752349000000002</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>40.12068</v>
+        <v>51.788819999999994</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>43.426397999999999</v>
+        <v>56.055926999999997</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>48.879419999999996</v>
+        <v>63.094829999999988</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -37464,31 +37464,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>55.566200000000002</v>
+        <v>71.726299999999995</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>58.34451</v>
+        <v>75.312614999999994</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>65.012454000000005</v>
+        <v>83.919770999999997</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>70.465475999999995</v>
+        <v>90.958673999999988</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>77.566648000000001</v>
+        <v>100.12505199999998</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>83.857872000000015</v>
+        <v>108.24592800000001</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>87.982956000000001</v>
+        <v>113.57069399999999</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -37531,31 +37531,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>2.8254000000000001</v>
+        <v>3.6470999999999996</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -37570,31 +37570,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>0.94180000000000064</v>
+        <v>1.2156999999999982</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>3.1079400000000135</v>
+        <v>4.0118100000000112</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>4.8879419999999953</v>
+        <v>6.3094830000000002</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>8.1088980000000106</v>
+        <v>10.467177000000021</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>13.222871999999995</v>
+        <v>17.068428000000011</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>19.636529999999993</v>
+        <v>25.347345000000018</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>23.243624000000011</v>
+        <v>30.003476000000006</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -37606,31 +37606,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>4.0209999999999999</v>
+        <v>14.882</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>3.9405799999999997</v>
+        <v>14.58436</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>3.8601599999999996</v>
+        <v>14.286719999999999</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>3.6993200000000002</v>
+        <v>13.69144</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>3.37764</v>
+        <v>12.500879999999999</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>3.3374299999999999</v>
+        <v>12.35206</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>3.2168000000000001</v>
+        <v>11.9056</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -37642,31 +37642,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>0.98399999999999999</v>
+        <v>4.665</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>0.96431999999999995</v>
+        <v>4.5716999999999999</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>0.94463999999999992</v>
+        <v>4.4783999999999997</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>0.90527999999999997</v>
+        <v>4.2918000000000003</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>0.82655999999999996</v>
+        <v>3.9186000000000001</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>0.81672</v>
+        <v>3.87195</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>0.78720000000000001</v>
+        <v>3.7320000000000002</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -37741,7 +37741,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=BEL</v>
+        <v>~TFM_INS-TS: region=NLD</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -37786,7 +37786,7 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>16.350000000000001</v>
+        <v>18.54</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -37809,7 +37809,7 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>23.88</v>
+        <v>22.81</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -37970,7 +37970,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=BEL; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=NLD; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -38207,13 +38207,13 @@
         <v>106</v>
       </c>
       <c r="C56">
-        <v>0.3</v>
+        <v>0.64</v>
       </c>
       <c r="D56">
-        <v>2.08</v>
+        <v>0.7</v>
       </c>
       <c r="E56">
-        <v>4.08</v>
+        <v>0.7</v>
       </c>
       <c r="F56" t="s">
         <v>107</v>
@@ -38227,13 +38227,13 @@
         <v>106</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F57" t="s">
         <v>107</v>
@@ -38248,7 +38248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D29F710-C7D3-4024-A683-B9318EA03A10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{555BFB23-037E-4F74-BECD-BFFDBB0F6A52}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -38367,7 +38367,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>573</v>
+        <v>94.18</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -38385,7 +38385,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>45.581000000000003</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -38400,7 +38400,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>57.588000000000001</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -38451,31 +38451,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>573</v>
+        <v>94.18</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>601.65</v>
+        <v>98.88900000000001</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>670.41</v>
+        <v>110.1906</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>739.17000000000007</v>
+        <v>121.49220000000001</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>813.66</v>
+        <v>133.73560000000001</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>911.07</v>
+        <v>149.74620000000002</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>991.29</v>
+        <v>162.9314</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -38514,7 +38514,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=DEU</v>
+        <v>~TFM_INS-TS: region=BEL</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -38678,31 +38678,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>212.01</v>
+        <v>34.846600000000002</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>210.57749999999999</v>
+        <v>34.611150000000002</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>227.93940000000001</v>
+        <v>37.464804000000001</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>243.92610000000005</v>
+        <v>40.092426000000003</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>244.09799999999998</v>
+        <v>40.12068</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>264.21030000000002</v>
+        <v>43.426397999999999</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>297.387</v>
+        <v>48.879419999999996</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -38745,31 +38745,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>338.07</v>
+        <v>55.566200000000002</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>354.97349999999994</v>
+        <v>58.34451</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>395.54189999999994</v>
+        <v>65.012454000000005</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>428.71860000000004</v>
+        <v>70.465475999999995</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>471.92279999999994</v>
+        <v>77.566648000000001</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>510.19920000000008</v>
+        <v>83.857872000000015</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>535.29660000000001</v>
+        <v>87.982956000000001</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -38812,31 +38812,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>17.189999999999998</v>
+        <v>2.8254000000000001</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -38851,31 +38851,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>5.7300000000000182</v>
+        <v>0.94180000000000064</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>18.908999999999992</v>
+        <v>3.1079400000000135</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>29.738699999999994</v>
+        <v>4.8879419999999953</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>49.335299999999961</v>
+        <v>8.1088980000000106</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>80.449200000000133</v>
+        <v>13.222871999999995</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>119.47050000000002</v>
+        <v>19.636529999999993</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>141.41639999999984</v>
+        <v>23.243624000000011</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -38887,31 +38887,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>45.581000000000003</v>
+        <v>4.0209999999999999</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>44.669380000000004</v>
+        <v>3.9405799999999997</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>43.757760000000005</v>
+        <v>3.8601599999999996</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>41.934520000000006</v>
+        <v>3.6993200000000002</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>38.288040000000002</v>
+        <v>3.37764</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>37.832230000000003</v>
+        <v>3.3374299999999999</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>36.464800000000004</v>
+        <v>3.2168000000000001</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -38923,31 +38923,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>57.588000000000001</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>56.436239999999998</v>
+        <v>0.96431999999999995</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>55.284480000000002</v>
+        <v>0.94463999999999992</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>52.980960000000003</v>
+        <v>0.90527999999999997</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>48.373919999999998</v>
+        <v>0.82655999999999996</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>47.79804</v>
+        <v>0.81672</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>46.070400000000006</v>
+        <v>0.78720000000000001</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -39022,7 +39022,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=DEU</v>
+        <v>~TFM_INS-TS: region=BEL</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -39067,7 +39067,7 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>49.33</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -39090,7 +39090,7 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>76.59</v>
+        <v>23.88</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -39251,7 +39251,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=DEU; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=BEL; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -39440,19 +39440,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -39488,13 +39488,13 @@
         <v>106</v>
       </c>
       <c r="C56">
-        <v>8.3149999999999995</v>
+        <v>0.3</v>
       </c>
       <c r="D56">
-        <v>14.914999999999999</v>
+        <v>2.08</v>
       </c>
       <c r="E56">
-        <v>15.615</v>
+        <v>4.08</v>
       </c>
       <c r="F56" t="s">
         <v>107</v>
@@ -39508,13 +39508,13 @@
         <v>106</v>
       </c>
       <c r="C57">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="F57" t="s">
         <v>107</v>
@@ -39529,7 +39529,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4AB9D4-D4E4-411A-A94A-72793828AE0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B56352A-5E95-4EC4-B393-1B52600FB3BE}">
   <dimension ref="A1:AH57"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -39648,7 +39648,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>62</v>
+        <v>573</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>54</v>
@@ -39666,7 +39666,7 @@
     <row r="12" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N12" s="17">
         <f>SUMIFS(iea_data!L3:L9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>2.5449999999999999</v>
+        <v>45.581000000000003</v>
       </c>
       <c r="AF12" t="s">
         <v>7</v>
@@ -39681,7 +39681,7 @@
     <row r="13" spans="1:34" ht="14.65" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N13" s="17">
         <f>SUMIFS(iea_data!M3:M9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>4.4509999999999996</v>
+        <v>57.588000000000001</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -39732,31 +39732,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>62</v>
+        <v>573</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>65.100000000000009</v>
+        <v>601.65</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>72.539999999999992</v>
+        <v>670.41</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>79.98</v>
+        <v>739.17000000000007</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>88.039999999999992</v>
+        <v>813.66</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>98.58</v>
+        <v>911.07</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>107.26</v>
+        <v>991.29</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -39795,7 +39795,7 @@
     <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=CHE</v>
+        <v>~TFM_INS-TS: region=DEU</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -39959,31 +39959,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>22.94</v>
+        <v>212.01</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>22.785</v>
+        <v>210.57749999999999</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>24.663599999999999</v>
+        <v>227.93940000000001</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>26.393400000000003</v>
+        <v>243.92610000000005</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>26.411999999999995</v>
+        <v>244.09799999999998</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>28.588199999999997</v>
+        <v>264.21030000000002</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>32.177999999999997</v>
+        <v>297.387</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -40026,31 +40026,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>36.58</v>
+        <v>338.07</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>38.409000000000006</v>
+        <v>354.97349999999994</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>42.798599999999993</v>
+        <v>395.54189999999994</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>46.388399999999997</v>
+        <v>428.71860000000004</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>51.063199999999995</v>
+        <v>471.92279999999994</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>55.204800000000006</v>
+        <v>510.19920000000008</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>57.920400000000008</v>
+        <v>535.29660000000001</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -40093,31 +40093,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>1.8599999999999999</v>
+        <v>17.189999999999998</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -40132,31 +40132,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>0.62000000000000455</v>
+        <v>5.7300000000000182</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>2.0460000000000065</v>
+        <v>18.908999999999992</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>3.2177999999999969</v>
+        <v>29.738699999999994</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>5.3382000000000005</v>
+        <v>49.335299999999961</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>8.7048000000000059</v>
+        <v>80.449200000000133</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>12.926999999999992</v>
+        <v>119.47050000000002</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>15.301600000000008</v>
+        <v>141.41639999999984</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -40168,31 +40168,31 @@
       </c>
       <c r="O24" s="19">
         <f>N12</f>
-        <v>2.5449999999999999</v>
+        <v>45.581000000000003</v>
       </c>
       <c r="P24" s="20">
         <f>$N$12*E16</f>
-        <v>2.4941</v>
+        <v>44.669380000000004</v>
       </c>
       <c r="Q24" s="20">
         <f>$N$12*F16</f>
-        <v>2.4432</v>
+        <v>43.757760000000005</v>
       </c>
       <c r="R24" s="20">
         <f t="shared" ref="R24:U24" si="5">$N$12*G16</f>
-        <v>2.3414000000000001</v>
+        <v>41.934520000000006</v>
       </c>
       <c r="S24" s="20">
         <f t="shared" si="5"/>
-        <v>2.1377999999999999</v>
+        <v>38.288040000000002</v>
       </c>
       <c r="T24" s="20">
         <f t="shared" si="5"/>
-        <v>2.1123499999999997</v>
+        <v>37.832230000000003</v>
       </c>
       <c r="U24" s="20">
         <f t="shared" si="5"/>
-        <v>2.036</v>
+        <v>36.464800000000004</v>
       </c>
       <c r="V24" s="18" t="s">
         <v>16</v>
@@ -40204,31 +40204,31 @@
       </c>
       <c r="O25" s="19">
         <f>N13</f>
-        <v>4.4509999999999996</v>
+        <v>57.588000000000001</v>
       </c>
       <c r="P25" s="20">
         <f>$N$13*E16</f>
-        <v>4.36198</v>
+        <v>56.436239999999998</v>
       </c>
       <c r="Q25" s="20">
         <f t="shared" ref="Q25:U25" si="6">$N$13*F16</f>
-        <v>4.2729599999999994</v>
+        <v>55.284480000000002</v>
       </c>
       <c r="R25" s="20">
         <f t="shared" si="6"/>
-        <v>4.0949200000000001</v>
+        <v>52.980960000000003</v>
       </c>
       <c r="S25" s="20">
         <f t="shared" si="6"/>
-        <v>3.7388399999999997</v>
+        <v>48.373919999999998</v>
       </c>
       <c r="T25" s="20">
         <f t="shared" si="6"/>
-        <v>3.6943299999999994</v>
+        <v>47.79804</v>
       </c>
       <c r="U25" s="20">
         <f t="shared" si="6"/>
-        <v>3.5608</v>
+        <v>46.070400000000006</v>
       </c>
       <c r="V25" s="18" t="s">
         <v>16</v>
@@ -40303,7 +40303,7 @@
     <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
-        <v>~TFM_INS-TS: region=CHE</v>
+        <v>~TFM_INS-TS: region=DEU</v>
       </c>
     </row>
     <row r="29" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -40348,7 +40348,7 @@
     <row r="30" spans="2:24" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L30" s="3">
         <f>SUMIFS(iea_data!G3:G9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>33.119999999999997</v>
+        <v>49.33</v>
       </c>
       <c r="N30" t="s">
         <v>30</v>
@@ -40371,7 +40371,7 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>29.73</v>
+        <v>76.59</v>
       </c>
       <c r="N31" t="s">
         <v>32</v>
@@ -40532,7 +40532,7 @@
     <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
-        <v>~TFM_INS-TS: region=CHE; attribute=flo_cost;pset_pn=-IMP*Z</v>
+        <v>~TFM_INS-TS: region=DEU; attribute=flo_cost;pset_pn=-IMP*Z</v>
       </c>
     </row>
     <row r="46" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -40631,39 +40631,39 @@
       </c>
       <c r="D48">
         <f t="shared" si="9"/>
-        <v>16.75</v>
+        <v>15.2</v>
       </c>
       <c r="E48">
         <f t="shared" si="9"/>
-        <v>17.085000000000001</v>
+        <v>15.504</v>
       </c>
       <c r="F48">
         <f t="shared" si="9"/>
-        <v>17.755000000000003</v>
+        <v>16.111999999999998</v>
       </c>
       <c r="G48">
         <f t="shared" si="9"/>
-        <v>17.922499999999999</v>
+        <v>16.263999999999999</v>
       </c>
       <c r="H48">
         <f t="shared" si="9"/>
-        <v>18.09</v>
+        <v>16.416</v>
       </c>
       <c r="I48">
         <f t="shared" si="9"/>
-        <v>18.425000000000001</v>
+        <v>16.72</v>
       </c>
       <c r="J48">
         <f t="shared" si="9"/>
-        <v>18.760000000000002</v>
+        <v>17.024000000000001</v>
       </c>
       <c r="M48">
         <f>HLOOKUP($B48&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>15.2</v>
+        <v>13.7</v>
       </c>
       <c r="N48">
         <f>HLOOKUP($B48&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>18.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
@@ -40676,39 +40676,39 @@
       </c>
       <c r="D49">
         <f t="shared" si="9"/>
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E49">
         <f t="shared" si="9"/>
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
       <c r="F49">
         <f t="shared" si="9"/>
-        <v>61.050000000000004</v>
+        <v>58.830000000000005</v>
       </c>
       <c r="G49">
         <f t="shared" si="9"/>
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
       <c r="H49">
         <f t="shared" si="9"/>
-        <v>55.55</v>
+        <v>53.53</v>
       </c>
       <c r="I49">
         <f t="shared" si="9"/>
-        <v>57.2</v>
+        <v>55.120000000000005</v>
       </c>
       <c r="J49">
         <f t="shared" si="9"/>
-        <v>62.699999999999996</v>
+        <v>60.419999999999995</v>
       </c>
       <c r="M49">
         <f>HLOOKUP($B49&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N49">
         <f>HLOOKUP($B49&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
@@ -40721,19 +40721,19 @@
       </c>
       <c r="D50">
         <f t="shared" si="9"/>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J50">
         <f>VLOOKUP($C$15,$AF$9:$AH$16,3,FALSE)*D50</f>
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M50">
         <f>HLOOKUP($B50&amp;"_"&amp;M$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="N50">
         <f>HLOOKUP($B50&amp;"_"&amp;N$46,fuel_prices!$B$10:$I$100,MATCH($A$1,fuel_prices!$A$10:$A$100,0),FALSE)</f>
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
@@ -40769,13 +40769,13 @@
         <v>106</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>8.3149999999999995</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>14.914999999999999</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>15.615</v>
       </c>
       <c r="F56" t="s">
         <v>107</v>
@@ -40789,13 +40789,13 @@
         <v>106</v>
       </c>
       <c r="C57">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="D57">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="E57">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="F57" t="s">
         <v>107</v>
